--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,54 +8179,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129460228</v>
+        <v>129476572</v>
       </c>
       <c r="B72" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493736</v>
+        <v>493675</v>
       </c>
       <c r="R72" t="n">
-        <v>6834865</v>
+        <v>6834825</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8273,57 +8264,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129460134</v>
+        <v>129476556</v>
       </c>
       <c r="B73" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493738</v>
+        <v>493810</v>
       </c>
       <c r="R73" t="n">
-        <v>6834870</v>
+        <v>6834883</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8370,57 +8361,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460004</v>
+        <v>129476586</v>
       </c>
       <c r="B74" t="n">
-        <v>98710</v>
+        <v>78710</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493728</v>
+        <v>493684</v>
       </c>
       <c r="R74" t="n">
-        <v>6834868</v>
+        <v>6834869</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,57 +8458,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476586</v>
+        <v>129460134</v>
       </c>
       <c r="B75" t="n">
-        <v>78709</v>
+        <v>98712</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493684</v>
+        <v>493738</v>
       </c>
       <c r="R75" t="n">
-        <v>6834869</v>
+        <v>6834870</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8564,57 +8555,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129476572</v>
+        <v>129460004</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493675</v>
+        <v>493728</v>
       </c>
       <c r="R76" t="n">
-        <v>6834825</v>
+        <v>6834868</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8661,57 +8652,66 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129476556</v>
+        <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493810</v>
+        <v>493736</v>
       </c>
       <c r="R77" t="n">
-        <v>6834883</v>
+        <v>6834865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,66 +8758,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129456176</v>
+        <v>129461154</v>
       </c>
       <c r="B78" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493813</v>
+        <v>493629</v>
       </c>
       <c r="R78" t="n">
-        <v>6834955</v>
+        <v>6834827</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8876,54 +8867,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129457973</v>
+        <v>129460036</v>
       </c>
       <c r="B79" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493684</v>
+        <v>493728</v>
       </c>
       <c r="R79" t="n">
-        <v>6834986</v>
+        <v>6834868</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8985,7 +8967,7 @@
         <v>129460662</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9079,10 +9061,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129460036</v>
+        <v>129476585</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>78710</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9090,34 +9072,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493728</v>
+        <v>493700</v>
       </c>
       <c r="R81" t="n">
-        <v>6834868</v>
+        <v>6834837</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9164,57 +9146,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129461154</v>
+        <v>129476554</v>
       </c>
       <c r="B82" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493629</v>
+        <v>493648</v>
       </c>
       <c r="R82" t="n">
-        <v>6834827</v>
+        <v>6834929</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9255,63 +9246,73 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129476585</v>
+        <v>129456176</v>
       </c>
       <c r="B83" t="n">
-        <v>78709</v>
+        <v>98712</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493700</v>
+        <v>493813</v>
       </c>
       <c r="R83" t="n">
-        <v>6834837</v>
+        <v>6834955</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9358,66 +9359,66 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129476554</v>
+        <v>129457973</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>98712</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493648</v>
+        <v>493684</v>
       </c>
       <c r="R84" t="n">
-        <v>6834929</v>
+        <v>6834986</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9458,19 +9459,18 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9480,7 +9480,7 @@
         <v>129457992</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9574,45 +9574,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129457913</v>
+        <v>129476547</v>
       </c>
       <c r="B86" t="n">
-        <v>98710</v>
+        <v>79068</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493686</v>
+        <v>493722</v>
       </c>
       <c r="R86" t="n">
-        <v>6834989</v>
+        <v>6834900</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9659,66 +9659,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129457745</v>
+        <v>129476579</v>
       </c>
       <c r="B87" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493678</v>
+        <v>493687</v>
       </c>
       <c r="R87" t="n">
-        <v>6835020</v>
+        <v>6834917</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9765,69 +9756,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129460883</v>
+        <v>129476589</v>
       </c>
       <c r="B88" t="n">
-        <v>98710</v>
+        <v>92827</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493637</v>
+        <v>493641</v>
       </c>
       <c r="R88" t="n">
-        <v>6834831</v>
+        <v>6834918</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9871,57 +9853,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129476589</v>
+        <v>129457913</v>
       </c>
       <c r="B89" t="n">
-        <v>92825</v>
+        <v>98712</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493641</v>
+        <v>493686</v>
       </c>
       <c r="R89" t="n">
-        <v>6834918</v>
+        <v>6834989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9968,60 +9950,69 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129476579</v>
+        <v>129460883</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493687</v>
+        <v>493637</v>
       </c>
       <c r="R90" t="n">
-        <v>6834917</v>
+        <v>6834831</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10065,57 +10056,66 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129476547</v>
+        <v>129457745</v>
       </c>
       <c r="B91" t="n">
-        <v>79067</v>
+        <v>98712</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>493722</v>
+        <v>493678</v>
       </c>
       <c r="R91" t="n">
-        <v>6834900</v>
+        <v>6835020</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10162,66 +10162,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129476555</v>
+        <v>129476583</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>493666</v>
+        <v>493664</v>
       </c>
       <c r="R92" t="n">
-        <v>6834982</v>
+        <v>6834992</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10262,7 +10253,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10284,7 +10274,7 @@
         <v>129476532</v>
       </c>
       <c r="B93" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10381,7 +10371,7 @@
         <v>129476566</v>
       </c>
       <c r="B94" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10478,7 +10468,7 @@
         <v>129476574</v>
       </c>
       <c r="B95" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10572,45 +10562,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476583</v>
+        <v>129476555</v>
       </c>
       <c r="B96" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493664</v>
+        <v>493666</v>
       </c>
       <c r="R96" t="n">
-        <v>6834992</v>
+        <v>6834982</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10651,6 +10650,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>129476571</v>
       </c>
       <c r="B97" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10766,54 +10766,52 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129455942</v>
+        <v>129476560</v>
       </c>
       <c r="B98" t="n">
-        <v>98710</v>
+        <v>78801</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493802</v>
+        <v>493684</v>
       </c>
       <c r="R98" t="n">
-        <v>6834925</v>
+        <v>6834860</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10854,28 +10852,29 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129455841</v>
+        <v>129476578</v>
       </c>
       <c r="B99" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10903,14 +10902,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493803</v>
+        <v>493718</v>
       </c>
       <c r="R99" t="n">
-        <v>6834901</v>
+        <v>6834894</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10957,44 +10956,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129458908</v>
+        <v>129455841</v>
       </c>
       <c r="B100" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11004,10 +11003,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493702</v>
+        <v>493803</v>
       </c>
       <c r="R100" t="n">
-        <v>6834942</v>
+        <v>6834901</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11066,54 +11065,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129458098</v>
+        <v>129476537</v>
       </c>
       <c r="B101" t="n">
-        <v>98710</v>
+        <v>79634</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493682</v>
+        <v>493659</v>
       </c>
       <c r="R101" t="n">
-        <v>6834975</v>
+        <v>6834945</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11160,22 +11150,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476560</v>
+        <v>129476544</v>
       </c>
       <c r="B102" t="n">
-        <v>78800</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11183,28 +11173,29 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -11214,10 +11205,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493684</v>
+        <v>493634</v>
       </c>
       <c r="R102" t="n">
-        <v>6834860</v>
+        <v>6834983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11258,7 +11249,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11277,10 +11267,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476544</v>
+        <v>129476569</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11288,42 +11278,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493634</v>
+        <v>493626</v>
       </c>
       <c r="R103" t="n">
-        <v>6834983</v>
+        <v>6834837</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11382,45 +11364,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129476578</v>
+        <v>129455942</v>
       </c>
       <c r="B104" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493718</v>
+        <v>493802</v>
       </c>
       <c r="R104" t="n">
-        <v>6834894</v>
+        <v>6834925</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11467,57 +11458,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129476537</v>
+        <v>129458908</v>
       </c>
       <c r="B105" t="n">
-        <v>79633</v>
+        <v>98712</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493659</v>
+        <v>493702</v>
       </c>
       <c r="R105" t="n">
-        <v>6834945</v>
+        <v>6834942</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11564,57 +11555,66 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129476569</v>
+        <v>129458098</v>
       </c>
       <c r="B106" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493626</v>
+        <v>493682</v>
       </c>
       <c r="R106" t="n">
-        <v>6834837</v>
+        <v>6834975</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11661,12 +11661,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11676,7 +11676,7 @@
         <v>129456312</v>
       </c>
       <c r="B107" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>129458915</v>
       </c>
       <c r="B108" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>129476577</v>
       </c>
       <c r="B109" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11973,54 +11973,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129456198</v>
+        <v>129476568</v>
       </c>
       <c r="B110" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>493810</v>
+        <v>493619</v>
       </c>
       <c r="R110" t="n">
-        <v>6834955</v>
+        <v>6834841</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12067,44 +12058,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129458436</v>
+        <v>129461581</v>
       </c>
       <c r="B111" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12114,10 +12105,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493653</v>
+        <v>493634</v>
       </c>
       <c r="R111" t="n">
-        <v>6835020</v>
+        <v>6834920</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12179,7 +12170,7 @@
         <v>129476538</v>
       </c>
       <c r="B112" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12273,45 +12264,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129476568</v>
+        <v>129456198</v>
       </c>
       <c r="B113" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493619</v>
+        <v>493810</v>
       </c>
       <c r="R113" t="n">
-        <v>6834841</v>
+        <v>6834955</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12358,44 +12358,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129461581</v>
+        <v>129458436</v>
       </c>
       <c r="B114" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12405,10 +12405,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493634</v>
+        <v>493653</v>
       </c>
       <c r="R114" t="n">
-        <v>6834920</v>
+        <v>6835020</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12467,54 +12467,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129459774</v>
+        <v>129476558</v>
       </c>
       <c r="B115" t="n">
-        <v>98710</v>
+        <v>78801</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493729</v>
+        <v>493629</v>
       </c>
       <c r="R115" t="n">
-        <v>6834877</v>
+        <v>6834823</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12561,66 +12552,57 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129459731</v>
+        <v>129476584</v>
       </c>
       <c r="B116" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493725</v>
+        <v>493670</v>
       </c>
       <c r="R116" t="n">
-        <v>6834883</v>
+        <v>6834995</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12667,12 +12649,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12682,7 +12664,7 @@
         <v>129460271</v>
       </c>
       <c r="B117" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12779,7 +12761,7 @@
         <v>129459508</v>
       </c>
       <c r="B118" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12873,45 +12855,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129476584</v>
+        <v>129459731</v>
       </c>
       <c r="B119" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>493670</v>
+        <v>493725</v>
       </c>
       <c r="R119" t="n">
-        <v>6834995</v>
+        <v>6834883</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12958,57 +12949,66 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129476558</v>
+        <v>129459774</v>
       </c>
       <c r="B120" t="n">
-        <v>78800</v>
+        <v>98712</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>493629</v>
+        <v>493729</v>
       </c>
       <c r="R120" t="n">
-        <v>6834823</v>
+        <v>6834877</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13055,57 +13055,64 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129457707</v>
+        <v>129476559</v>
       </c>
       <c r="B121" t="n">
-        <v>98710</v>
+        <v>78801</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493815</v>
+        <v>493626</v>
       </c>
       <c r="R121" t="n">
-        <v>6834917</v>
+        <v>6834843</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13146,72 +13153,64 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129456404</v>
+        <v>129476590</v>
       </c>
       <c r="B122" t="n">
-        <v>98710</v>
+        <v>92827</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493780</v>
+        <v>493628</v>
       </c>
       <c r="R122" t="n">
-        <v>6834929</v>
+        <v>6834891</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13258,66 +13257,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129456103</v>
+        <v>129476541</v>
       </c>
       <c r="B123" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493817</v>
+        <v>493780</v>
       </c>
       <c r="R123" t="n">
-        <v>6834939</v>
+        <v>6834984</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13364,22 +13354,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129456013</v>
+        <v>129461070</v>
       </c>
       <c r="B124" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13404,26 +13394,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493806</v>
+        <v>493629</v>
       </c>
       <c r="R124" t="n">
-        <v>6834935</v>
+        <v>6834827</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13482,10 +13463,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129461070</v>
+        <v>129457707</v>
       </c>
       <c r="B125" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13517,10 +13498,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493629</v>
+        <v>493815</v>
       </c>
       <c r="R125" t="n">
-        <v>6834827</v>
+        <v>6834917</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13579,52 +13560,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129476559</v>
+        <v>129456013</v>
       </c>
       <c r="B126" t="n">
-        <v>78800</v>
+        <v>98712</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493626</v>
+        <v>493806</v>
       </c>
       <c r="R126" t="n">
-        <v>6834843</v>
+        <v>6834935</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13665,64 +13648,72 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129476590</v>
+        <v>129456404</v>
       </c>
       <c r="B127" t="n">
-        <v>92825</v>
+        <v>98712</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493628</v>
+        <v>493780</v>
       </c>
       <c r="R127" t="n">
-        <v>6834891</v>
+        <v>6834929</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13769,57 +13760,66 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129476541</v>
+        <v>129456103</v>
       </c>
       <c r="B128" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493780</v>
+        <v>493817</v>
       </c>
       <c r="R128" t="n">
-        <v>6834984</v>
+        <v>6834939</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13866,44 +13866,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129458700</v>
+        <v>129458645</v>
       </c>
       <c r="B129" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13913,13 +13913,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493675</v>
+        <v>493662</v>
       </c>
       <c r="R129" t="n">
-        <v>6834963</v>
+        <v>6834952</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13975,10 +13975,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129458645</v>
+        <v>129455888</v>
       </c>
       <c r="B130" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14010,10 +14010,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493662</v>
+        <v>493811</v>
       </c>
       <c r="R130" t="n">
-        <v>6834952</v>
+        <v>6834925</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14072,45 +14072,54 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129455888</v>
+        <v>129456470</v>
       </c>
       <c r="B131" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493811</v>
+        <v>493783</v>
       </c>
       <c r="R131" t="n">
-        <v>6834925</v>
+        <v>6834931</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14169,10 +14178,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129456470</v>
+        <v>129458700</v>
       </c>
       <c r="B132" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14197,29 +14206,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493783</v>
+        <v>493675</v>
       </c>
       <c r="R132" t="n">
-        <v>6834931</v>
+        <v>6834963</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>129476530</v>
       </c>
       <c r="B133" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>129476550</v>
       </c>
       <c r="B134" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476588</v>
+        <v>129476548</v>
       </c>
       <c r="B135" t="n">
-        <v>78709</v>
+        <v>91598</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493619</v>
+        <v>493687</v>
       </c>
       <c r="R135" t="n">
-        <v>6834998</v>
+        <v>6834930</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,10 +14566,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476573</v>
+        <v>129476588</v>
       </c>
       <c r="B136" t="n">
-        <v>79043</v>
+        <v>78710</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493661</v>
+        <v>493619</v>
       </c>
       <c r="R136" t="n">
-        <v>6834848</v>
+        <v>6834998</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14663,10 +14663,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476580</v>
+        <v>129476552</v>
       </c>
       <c r="B137" t="n">
-        <v>79043</v>
+        <v>78802</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14674,21 +14674,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493675</v>
+        <v>493629</v>
       </c>
       <c r="R137" t="n">
-        <v>6834937</v>
+        <v>6834831</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14760,45 +14760,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129476548</v>
+        <v>129458414</v>
       </c>
       <c r="B138" t="n">
-        <v>91596</v>
+        <v>98712</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493687</v>
+        <v>493670</v>
       </c>
       <c r="R138" t="n">
-        <v>6834930</v>
+        <v>6834981</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14845,66 +14845,57 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476553</v>
+        <v>129476573</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493591</v>
+        <v>493661</v>
       </c>
       <c r="R139" t="n">
-        <v>6835008</v>
+        <v>6834848</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14945,7 +14936,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14964,10 +14954,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129476552</v>
+        <v>129459901</v>
       </c>
       <c r="B140" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14975,34 +14965,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493629</v>
+        <v>493734</v>
       </c>
       <c r="R140" t="n">
-        <v>6834831</v>
+        <v>6834875</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,57 +15039,57 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129458414</v>
+        <v>129476580</v>
       </c>
       <c r="B141" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493670</v>
+        <v>493675</v>
       </c>
       <c r="R141" t="n">
-        <v>6834981</v>
+        <v>6834937</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15146,57 +15136,66 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129459901</v>
+        <v>129476553</v>
       </c>
       <c r="B142" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493734</v>
+        <v>493591</v>
       </c>
       <c r="R142" t="n">
-        <v>6834875</v>
+        <v>6835008</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15237,63 +15236,64 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129459852</v>
+        <v>129476540</v>
       </c>
       <c r="B143" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493730</v>
+        <v>493723</v>
       </c>
       <c r="R143" t="n">
-        <v>6834877</v>
+        <v>6834965</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15340,22 +15340,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129460207</v>
+        <v>129457830</v>
       </c>
       <c r="B144" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15380,17 +15380,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493738</v>
+        <v>493676</v>
       </c>
       <c r="R144" t="n">
-        <v>6834861</v>
+        <v>6835001</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15449,45 +15458,54 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129458803</v>
+        <v>129458085</v>
       </c>
       <c r="B145" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493683</v>
+        <v>493690</v>
       </c>
       <c r="R145" t="n">
-        <v>6834951</v>
+        <v>6834972</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15546,10 +15564,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129458085</v>
+        <v>129459852</v>
       </c>
       <c r="B146" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15574,26 +15592,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493690</v>
+        <v>493730</v>
       </c>
       <c r="R146" t="n">
-        <v>6834972</v>
+        <v>6834877</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15652,10 +15661,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129457830</v>
+        <v>129460207</v>
       </c>
       <c r="B147" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15680,26 +15689,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493676</v>
+        <v>493738</v>
       </c>
       <c r="R147" t="n">
-        <v>6835001</v>
+        <v>6834861</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15758,10 +15758,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129476540</v>
+        <v>129476543</v>
       </c>
       <c r="B148" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15769,34 +15769,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493723</v>
+        <v>493676</v>
       </c>
       <c r="R148" t="n">
-        <v>6834965</v>
+        <v>6834800</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15855,10 +15863,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129476543</v>
+        <v>129458803</v>
       </c>
       <c r="B149" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15866,42 +15874,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493676</v>
+        <v>493683</v>
       </c>
       <c r="R149" t="n">
-        <v>6834800</v>
+        <v>6834951</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,57 +15948,57 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129460421</v>
+        <v>129476539</v>
       </c>
       <c r="B150" t="n">
-        <v>98710</v>
+        <v>90577</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493728</v>
+        <v>493652</v>
       </c>
       <c r="R150" t="n">
-        <v>6834848</v>
+        <v>6834985</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16045,22 +16045,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476539</v>
+        <v>129476535</v>
       </c>
       <c r="B151" t="n">
-        <v>90575</v>
+        <v>79663</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16068,21 +16068,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493652</v>
+        <v>493703</v>
       </c>
       <c r="R151" t="n">
-        <v>6834985</v>
+        <v>6834865</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16154,45 +16154,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129476535</v>
+        <v>129460421</v>
       </c>
       <c r="B152" t="n">
-        <v>79662</v>
+        <v>98712</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>493703</v>
+        <v>493728</v>
       </c>
       <c r="R152" t="n">
-        <v>6834865</v>
+        <v>6834848</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16239,22 +16239,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129458972</v>
+        <v>129460288</v>
       </c>
       <c r="B153" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16279,26 +16279,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493700</v>
+        <v>493733</v>
       </c>
       <c r="R153" t="n">
-        <v>6834942</v>
+        <v>6834848</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16357,10 +16348,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129460288</v>
+        <v>129458972</v>
       </c>
       <c r="B154" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16385,17 +16376,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>493733</v>
+        <v>493700</v>
       </c>
       <c r="R154" t="n">
-        <v>6834848</v>
+        <v>6834942</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
         <v>129460467</v>
       </c>
       <c r="B155" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16551,10 +16551,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129476576</v>
+        <v>129476567</v>
       </c>
       <c r="B156" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16586,10 +16586,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493725</v>
+        <v>493634</v>
       </c>
       <c r="R156" t="n">
-        <v>6834888</v>
+        <v>6834889</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16648,10 +16648,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129476567</v>
+        <v>129476576</v>
       </c>
       <c r="B157" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16683,10 +16683,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493634</v>
+        <v>493725</v>
       </c>
       <c r="R157" t="n">
-        <v>6834889</v>
+        <v>6834888</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16745,54 +16745,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129459449</v>
+        <v>129476533</v>
       </c>
       <c r="B158" t="n">
-        <v>98710</v>
+        <v>79663</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493720</v>
+        <v>493678</v>
       </c>
       <c r="R158" t="n">
-        <v>6834910</v>
+        <v>6834780</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16839,12 +16830,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -16854,7 +16845,7 @@
         <v>129459208</v>
       </c>
       <c r="B159" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16948,10 +16939,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129458226</v>
+        <v>129476536</v>
       </c>
       <c r="B160" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16959,34 +16950,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493670</v>
+        <v>493642</v>
       </c>
       <c r="R160" t="n">
-        <v>6834981</v>
+        <v>6834998</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17033,12 +17024,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17048,7 +17039,7 @@
         <v>129457857</v>
       </c>
       <c r="B161" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17142,54 +17133,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129459953</v>
+        <v>129458226</v>
       </c>
       <c r="B162" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493729</v>
+        <v>493670</v>
       </c>
       <c r="R162" t="n">
-        <v>6834873</v>
+        <v>6834981</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17248,10 +17230,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129476562</v>
+        <v>129459449</v>
       </c>
       <c r="B163" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17278,7 +17260,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -17286,19 +17268,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493676</v>
+        <v>493720</v>
       </c>
       <c r="R163" t="n">
-        <v>6834974</v>
+        <v>6834910</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17339,64 +17318,72 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129476546</v>
+        <v>129459953</v>
       </c>
       <c r="B164" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493733</v>
+        <v>493729</v>
       </c>
       <c r="R164" t="n">
-        <v>6834961</v>
+        <v>6834873</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17443,57 +17430,69 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129476536</v>
+        <v>129476562</v>
       </c>
       <c r="B165" t="n">
-        <v>79662</v>
+        <v>98712</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493642</v>
+        <v>493676</v>
       </c>
       <c r="R165" t="n">
-        <v>6834998</v>
+        <v>6834974</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17534,6 +17533,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17552,10 +17552,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129476533</v>
+        <v>129476546</v>
       </c>
       <c r="B166" t="n">
-        <v>79662</v>
+        <v>91843</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17563,21 +17563,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493678</v>
+        <v>493733</v>
       </c>
       <c r="R166" t="n">
-        <v>6834780</v>
+        <v>6834961</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17652,7 +17652,7 @@
         <v>129476549</v>
       </c>
       <c r="B167" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17746,45 +17746,54 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476575</v>
+        <v>129459653</v>
       </c>
       <c r="B168" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493728</v>
+        <v>493740</v>
       </c>
       <c r="R168" t="n">
-        <v>6834886</v>
+        <v>6834887</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17831,57 +17840,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129476570</v>
+        <v>129459536</v>
       </c>
       <c r="B169" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493628</v>
+        <v>493723</v>
       </c>
       <c r="R169" t="n">
-        <v>6834790</v>
+        <v>6834898</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17928,57 +17937,66 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129476531</v>
+        <v>129456373</v>
       </c>
       <c r="B170" t="n">
-        <v>79662</v>
+        <v>98712</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493636</v>
+        <v>493796</v>
       </c>
       <c r="R170" t="n">
-        <v>6834906</v>
+        <v>6834937</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18025,22 +18043,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476587</v>
+        <v>129476531</v>
       </c>
       <c r="B171" t="n">
-        <v>78709</v>
+        <v>79663</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18048,21 +18066,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18072,10 +18090,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493659</v>
+        <v>493636</v>
       </c>
       <c r="R171" t="n">
-        <v>6834945</v>
+        <v>6834906</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18137,7 +18155,7 @@
         <v>129476581</v>
       </c>
       <c r="B172" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18231,45 +18249,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129459536</v>
+        <v>129476575</v>
       </c>
       <c r="B173" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493723</v>
+        <v>493728</v>
       </c>
       <c r="R173" t="n">
-        <v>6834898</v>
+        <v>6834886</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18316,66 +18334,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129459653</v>
+        <v>129476570</v>
       </c>
       <c r="B174" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493740</v>
+        <v>493628</v>
       </c>
       <c r="R174" t="n">
-        <v>6834887</v>
+        <v>6834790</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18422,66 +18431,57 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129456373</v>
+        <v>129476587</v>
       </c>
       <c r="B175" t="n">
-        <v>98710</v>
+        <v>78710</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493796</v>
+        <v>493659</v>
       </c>
       <c r="R175" t="n">
-        <v>6834937</v>
+        <v>6834945</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,22 +18528,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129460260</v>
+        <v>129459599</v>
       </c>
       <c r="B176" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18575,10 +18575,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493731</v>
+        <v>493726</v>
       </c>
       <c r="R176" t="n">
-        <v>6834851</v>
+        <v>6834891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,54 +18637,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129456055</v>
+        <v>129460260</v>
       </c>
       <c r="B177" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493817</v>
+        <v>493731</v>
       </c>
       <c r="R177" t="n">
-        <v>6834930</v>
+        <v>6834851</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18743,10 +18734,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129458467</v>
+        <v>129456055</v>
       </c>
       <c r="B178" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18773,7 +18764,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -18787,10 +18778,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493646</v>
+        <v>493817</v>
       </c>
       <c r="R178" t="n">
-        <v>6835015</v>
+        <v>6834930</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18849,32 +18840,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129459599</v>
+        <v>129459676</v>
       </c>
       <c r="B179" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18884,10 +18875,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493726</v>
+        <v>493727</v>
       </c>
       <c r="R179" t="n">
-        <v>6834891</v>
+        <v>6834879</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18946,10 +18937,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129459676</v>
+        <v>129458467</v>
       </c>
       <c r="B180" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18974,17 +18965,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493727</v>
+        <v>493646</v>
       </c>
       <c r="R180" t="n">
-        <v>6834879</v>
+        <v>6835015</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19043,7 +19043,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129476551</v>
+        <v>129476561</v>
       </c>
       <c r="B181" t="n">
         <v>78801</v>
@@ -19054,21 +19054,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19078,10 +19078,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493632</v>
+        <v>493634</v>
       </c>
       <c r="R181" t="n">
-        <v>6834827</v>
+        <v>6834985</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19140,10 +19140,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129476561</v>
+        <v>129476551</v>
       </c>
       <c r="B182" t="n">
-        <v>78800</v>
+        <v>78802</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19151,21 +19151,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19175,10 +19175,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493634</v>
+        <v>493632</v>
       </c>
       <c r="R182" t="n">
-        <v>6834985</v>
+        <v>6834827</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19240,7 +19240,7 @@
         <v>129459964</v>
       </c>
       <c r="B183" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>129459836</v>
       </c>
       <c r="B184" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,10 +8179,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476572</v>
+        <v>129476586</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8190,21 +8190,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493675</v>
+        <v>493684</v>
       </c>
       <c r="R72" t="n">
-        <v>6834825</v>
+        <v>6834869</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,45 +8276,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129476556</v>
+        <v>129460134</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493810</v>
+        <v>493738</v>
       </c>
       <c r="R73" t="n">
-        <v>6834883</v>
+        <v>6834870</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,57 +8361,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129476586</v>
+        <v>129460004</v>
       </c>
       <c r="B74" t="n">
-        <v>78710</v>
+        <v>98716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493684</v>
+        <v>493728</v>
       </c>
       <c r="R74" t="n">
-        <v>6834869</v>
+        <v>6834868</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,57 +8458,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129460134</v>
+        <v>129476572</v>
       </c>
       <c r="B75" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493738</v>
+        <v>493675</v>
       </c>
       <c r="R75" t="n">
-        <v>6834870</v>
+        <v>6834825</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8555,57 +8555,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129460004</v>
+        <v>129476556</v>
       </c>
       <c r="B76" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493728</v>
+        <v>493810</v>
       </c>
       <c r="R76" t="n">
-        <v>6834868</v>
+        <v>6834883</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8652,12 +8652,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8667,7 +8667,7 @@
         <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129461154</v>
+        <v>129476585</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8781,34 +8781,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493629</v>
+        <v>493700</v>
       </c>
       <c r="R78" t="n">
-        <v>6834827</v>
+        <v>6834837</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8855,57 +8855,66 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129460036</v>
+        <v>129456176</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493728</v>
+        <v>493813</v>
       </c>
       <c r="R79" t="n">
-        <v>6834868</v>
+        <v>6834955</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8964,45 +8973,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129460662</v>
+        <v>129457973</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493658</v>
+        <v>493684</v>
       </c>
       <c r="R80" t="n">
-        <v>6834840</v>
+        <v>6834986</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9061,10 +9079,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129476585</v>
+        <v>129461154</v>
       </c>
       <c r="B81" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9072,34 +9090,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493700</v>
+        <v>493629</v>
       </c>
       <c r="R81" t="n">
-        <v>6834837</v>
+        <v>6834827</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9146,66 +9164,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129476554</v>
+        <v>129460036</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493648</v>
+        <v>493728</v>
       </c>
       <c r="R82" t="n">
-        <v>6834929</v>
+        <v>6834868</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9246,73 +9255,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129456176</v>
+        <v>129460662</v>
       </c>
       <c r="B83" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493813</v>
+        <v>493658</v>
       </c>
       <c r="R83" t="n">
-        <v>6834955</v>
+        <v>6834840</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9371,54 +9370,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129457973</v>
+        <v>129476554</v>
       </c>
       <c r="B84" t="n">
-        <v>98712</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493684</v>
+        <v>493648</v>
       </c>
       <c r="R84" t="n">
-        <v>6834986</v>
+        <v>6834929</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9459,50 +9458,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129457992</v>
+        <v>129457913</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9512,10 +9512,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493684</v>
+        <v>493686</v>
       </c>
       <c r="R85" t="n">
-        <v>6834988</v>
+        <v>6834989</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9574,48 +9574,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129476547</v>
+        <v>129460883</v>
       </c>
       <c r="B86" t="n">
-        <v>79068</v>
+        <v>98716</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493722</v>
+        <v>493637</v>
       </c>
       <c r="R86" t="n">
-        <v>6834900</v>
+        <v>6834831</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9659,57 +9668,66 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129476579</v>
+        <v>129457745</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493687</v>
+        <v>493678</v>
       </c>
       <c r="R87" t="n">
-        <v>6834917</v>
+        <v>6835020</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9756,57 +9774,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129476589</v>
+        <v>129457992</v>
       </c>
       <c r="B88" t="n">
-        <v>92827</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493641</v>
+        <v>493684</v>
       </c>
       <c r="R88" t="n">
-        <v>6834918</v>
+        <v>6834988</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9853,57 +9871,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129457913</v>
+        <v>129476579</v>
       </c>
       <c r="B89" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493686</v>
+        <v>493687</v>
       </c>
       <c r="R89" t="n">
-        <v>6834989</v>
+        <v>6834917</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9950,69 +9968,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129460883</v>
+        <v>129476589</v>
       </c>
       <c r="B90" t="n">
-        <v>98712</v>
+        <v>92831</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493637</v>
+        <v>493641</v>
       </c>
       <c r="R90" t="n">
-        <v>6834831</v>
+        <v>6834918</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10056,66 +10065,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129457745</v>
+        <v>129476547</v>
       </c>
       <c r="B91" t="n">
-        <v>98712</v>
+        <v>79068</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>493678</v>
+        <v>493722</v>
       </c>
       <c r="R91" t="n">
-        <v>6835020</v>
+        <v>6834900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10162,12 +10162,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10271,10 +10271,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476532</v>
+        <v>129476566</v>
       </c>
       <c r="B93" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10282,21 +10282,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493619</v>
+        <v>493646</v>
       </c>
       <c r="R93" t="n">
-        <v>6834843</v>
+        <v>6834937</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476566</v>
+        <v>129476574</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493646</v>
+        <v>493702</v>
       </c>
       <c r="R94" t="n">
-        <v>6834937</v>
+        <v>6834858</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10465,10 +10465,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476574</v>
+        <v>129476532</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10476,21 +10476,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10500,10 +10500,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493702</v>
+        <v>493619</v>
       </c>
       <c r="R95" t="n">
-        <v>6834858</v>
+        <v>6834843</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10871,7 +10871,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129476578</v>
+        <v>129455841</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -10902,14 +10902,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493718</v>
+        <v>493803</v>
       </c>
       <c r="R99" t="n">
-        <v>6834894</v>
+        <v>6834901</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10956,22 +10956,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129455841</v>
+        <v>129476544</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10979,34 +10979,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493803</v>
+        <v>493634</v>
       </c>
       <c r="R100" t="n">
-        <v>6834901</v>
+        <v>6834983</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11053,57 +11061,66 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129476537</v>
+        <v>129455942</v>
       </c>
       <c r="B101" t="n">
-        <v>79634</v>
+        <v>98716</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493659</v>
+        <v>493802</v>
       </c>
       <c r="R101" t="n">
-        <v>6834945</v>
+        <v>6834925</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11150,65 +11167,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476544</v>
+        <v>129458908</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493634</v>
+        <v>493702</v>
       </c>
       <c r="R102" t="n">
-        <v>6834983</v>
+        <v>6834942</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11255,57 +11264,66 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476569</v>
+        <v>129458098</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493626</v>
+        <v>493682</v>
       </c>
       <c r="R103" t="n">
-        <v>6834837</v>
+        <v>6834975</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11352,66 +11370,57 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129455942</v>
+        <v>129476537</v>
       </c>
       <c r="B104" t="n">
-        <v>98712</v>
+        <v>79634</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493802</v>
+        <v>493659</v>
       </c>
       <c r="R104" t="n">
-        <v>6834925</v>
+        <v>6834945</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11458,57 +11467,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129458908</v>
+        <v>129476569</v>
       </c>
       <c r="B105" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493702</v>
+        <v>493626</v>
       </c>
       <c r="R105" t="n">
-        <v>6834942</v>
+        <v>6834837</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,66 +11564,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129458098</v>
+        <v>129476578</v>
       </c>
       <c r="B106" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493682</v>
+        <v>493718</v>
       </c>
       <c r="R106" t="n">
-        <v>6834975</v>
+        <v>6834894</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11661,66 +11661,57 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129456312</v>
+        <v>129458915</v>
       </c>
       <c r="B107" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493787</v>
+        <v>493698</v>
       </c>
       <c r="R107" t="n">
-        <v>6834957</v>
+        <v>6834942</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11779,7 +11770,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129458915</v>
+        <v>129476577</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -11810,14 +11801,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493698</v>
+        <v>493707</v>
       </c>
       <c r="R108" t="n">
-        <v>6834942</v>
+        <v>6834895</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11864,57 +11855,66 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129476577</v>
+        <v>129456312</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493707</v>
+        <v>493787</v>
       </c>
       <c r="R109" t="n">
-        <v>6834895</v>
+        <v>6834957</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11961,12 +11961,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12167,45 +12167,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129476538</v>
+        <v>129458436</v>
       </c>
       <c r="B112" t="n">
-        <v>79634</v>
+        <v>98716</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493627</v>
+        <v>493653</v>
       </c>
       <c r="R112" t="n">
-        <v>6834986</v>
+        <v>6835020</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12252,12 +12252,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12267,7 +12267,7 @@
         <v>129456198</v>
       </c>
       <c r="B113" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12370,45 +12370,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129458436</v>
+        <v>129476538</v>
       </c>
       <c r="B114" t="n">
-        <v>98712</v>
+        <v>79634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493653</v>
+        <v>493627</v>
       </c>
       <c r="R114" t="n">
-        <v>6835020</v>
+        <v>6834986</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,22 +12455,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129476558</v>
+        <v>129476584</v>
       </c>
       <c r="B115" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12478,21 +12478,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12502,10 +12502,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493629</v>
+        <v>493670</v>
       </c>
       <c r="R115" t="n">
-        <v>6834823</v>
+        <v>6834995</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12564,10 +12564,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476584</v>
+        <v>129476558</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12575,21 +12575,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12599,10 +12599,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493670</v>
+        <v>493629</v>
       </c>
       <c r="R116" t="n">
-        <v>6834995</v>
+        <v>6834823</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12761,7 +12761,7 @@
         <v>129459508</v>
       </c>
       <c r="B118" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>129459731</v>
       </c>
       <c r="B119" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>129459774</v>
       </c>
       <c r="B120" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>129476590</v>
       </c>
       <c r="B122" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>129476541</v>
       </c>
       <c r="B123" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>129461070</v>
       </c>
       <c r="B124" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>129457707</v>
       </c>
       <c r="B125" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>129456013</v>
       </c>
       <c r="B126" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>129456404</v>
       </c>
       <c r="B127" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>129456103</v>
       </c>
       <c r="B128" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14072,10 +14072,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129456470</v>
+        <v>129458700</v>
       </c>
       <c r="B131" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14100,29 +14100,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493783</v>
+        <v>493675</v>
       </c>
       <c r="R131" t="n">
-        <v>6834931</v>
+        <v>6834963</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14178,48 +14169,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129458700</v>
+        <v>129476550</v>
       </c>
       <c r="B132" t="n">
-        <v>98712</v>
+        <v>78802</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493675</v>
+        <v>493625</v>
       </c>
       <c r="R132" t="n">
-        <v>6834963</v>
+        <v>6834820</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14263,12 +14254,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14372,45 +14363,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129476550</v>
+        <v>129456470</v>
       </c>
       <c r="B134" t="n">
-        <v>78802</v>
+        <v>98716</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493625</v>
+        <v>493783</v>
       </c>
       <c r="R134" t="n">
-        <v>6834820</v>
+        <v>6834931</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14457,22 +14457,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476548</v>
+        <v>129476588</v>
       </c>
       <c r="B135" t="n">
-        <v>91598</v>
+        <v>78710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493687</v>
+        <v>493619</v>
       </c>
       <c r="R135" t="n">
-        <v>6834930</v>
+        <v>6834998</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,10 +14566,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476588</v>
+        <v>129476573</v>
       </c>
       <c r="B136" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493619</v>
+        <v>493661</v>
       </c>
       <c r="R136" t="n">
-        <v>6834998</v>
+        <v>6834848</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14663,10 +14663,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476552</v>
+        <v>129459901</v>
       </c>
       <c r="B137" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14674,34 +14674,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493629</v>
+        <v>493734</v>
       </c>
       <c r="R137" t="n">
-        <v>6834831</v>
+        <v>6834875</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14748,57 +14748,57 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129458414</v>
+        <v>129476580</v>
       </c>
       <c r="B138" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493670</v>
+        <v>493675</v>
       </c>
       <c r="R138" t="n">
-        <v>6834981</v>
+        <v>6834937</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14845,57 +14845,66 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476573</v>
+        <v>129476553</v>
       </c>
       <c r="B139" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493661</v>
+        <v>493591</v>
       </c>
       <c r="R139" t="n">
-        <v>6834848</v>
+        <v>6835008</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14936,6 +14945,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14954,32 +14964,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129459901</v>
+        <v>129458414</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14989,10 +14999,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493734</v>
+        <v>493670</v>
       </c>
       <c r="R140" t="n">
-        <v>6834875</v>
+        <v>6834981</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15051,10 +15061,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476580</v>
+        <v>129476552</v>
       </c>
       <c r="B141" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15062,21 +15072,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15086,10 +15096,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493675</v>
+        <v>493629</v>
       </c>
       <c r="R141" t="n">
-        <v>6834937</v>
+        <v>6834831</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15148,54 +15158,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129476553</v>
+        <v>129476548</v>
       </c>
       <c r="B142" t="n">
-        <v>8450</v>
+        <v>91602</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493591</v>
+        <v>493687</v>
       </c>
       <c r="R142" t="n">
-        <v>6835008</v>
+        <v>6834930</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15236,7 +15237,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15255,45 +15255,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129476540</v>
+        <v>129457830</v>
       </c>
       <c r="B143" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493723</v>
+        <v>493676</v>
       </c>
       <c r="R143" t="n">
-        <v>6834965</v>
+        <v>6835001</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15340,22 +15349,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129457830</v>
+        <v>129458085</v>
       </c>
       <c r="B144" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15382,7 +15391,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -15396,10 +15405,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493676</v>
+        <v>493690</v>
       </c>
       <c r="R144" t="n">
-        <v>6835001</v>
+        <v>6834972</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15458,10 +15467,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129458085</v>
+        <v>129459852</v>
       </c>
       <c r="B145" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15486,26 +15495,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493690</v>
+        <v>493730</v>
       </c>
       <c r="R145" t="n">
-        <v>6834972</v>
+        <v>6834877</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15564,10 +15564,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129459852</v>
+        <v>129460207</v>
       </c>
       <c r="B146" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15599,10 +15599,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493730</v>
+        <v>493738</v>
       </c>
       <c r="R146" t="n">
-        <v>6834877</v>
+        <v>6834861</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15661,32 +15661,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129460207</v>
+        <v>129458803</v>
       </c>
       <c r="B147" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493738</v>
+        <v>493683</v>
       </c>
       <c r="R147" t="n">
-        <v>6834861</v>
+        <v>6834951</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15863,10 +15863,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129458803</v>
+        <v>129476540</v>
       </c>
       <c r="B149" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15874,34 +15874,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493683</v>
+        <v>493723</v>
       </c>
       <c r="R149" t="n">
-        <v>6834951</v>
+        <v>6834965</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,12 +15948,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -15963,7 +15963,7 @@
         <v>129476539</v>
       </c>
       <c r="B150" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>129460421</v>
       </c>
       <c r="B152" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>129460288</v>
       </c>
       <c r="B153" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>129458972</v>
       </c>
       <c r="B154" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16745,45 +16745,54 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129476533</v>
+        <v>129459449</v>
       </c>
       <c r="B158" t="n">
-        <v>79663</v>
+        <v>98716</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493678</v>
+        <v>493720</v>
       </c>
       <c r="R158" t="n">
-        <v>6834780</v>
+        <v>6834910</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16830,57 +16839,66 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129459208</v>
+        <v>129459953</v>
       </c>
       <c r="B159" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493698</v>
+        <v>493729</v>
       </c>
       <c r="R159" t="n">
-        <v>6834943</v>
+        <v>6834873</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16939,45 +16957,57 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129476536</v>
+        <v>129476562</v>
       </c>
       <c r="B160" t="n">
-        <v>79663</v>
+        <v>98716</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493642</v>
+        <v>493676</v>
       </c>
       <c r="R160" t="n">
-        <v>6834998</v>
+        <v>6834974</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17018,6 +17048,7 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -17036,7 +17067,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129457857</v>
+        <v>129459208</v>
       </c>
       <c r="B161" t="n">
         <v>79044</v>
@@ -17071,10 +17102,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>493676</v>
+        <v>493698</v>
       </c>
       <c r="R161" t="n">
-        <v>6835001</v>
+        <v>6834943</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17133,7 +17164,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129458226</v>
+        <v>129457857</v>
       </c>
       <c r="B162" t="n">
         <v>79044</v>
@@ -17168,10 +17199,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493670</v>
+        <v>493676</v>
       </c>
       <c r="R162" t="n">
-        <v>6834981</v>
+        <v>6835001</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17230,54 +17261,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129459449</v>
+        <v>129458226</v>
       </c>
       <c r="B163" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493720</v>
+        <v>493670</v>
       </c>
       <c r="R163" t="n">
-        <v>6834910</v>
+        <v>6834981</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17336,54 +17358,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129459953</v>
+        <v>129476549</v>
       </c>
       <c r="B164" t="n">
-        <v>98712</v>
+        <v>91602</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493729</v>
+        <v>493677</v>
       </c>
       <c r="R164" t="n">
-        <v>6834873</v>
+        <v>6835005</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17430,69 +17443,57 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129476562</v>
+        <v>129476533</v>
       </c>
       <c r="B165" t="n">
-        <v>98712</v>
+        <v>79663</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493676</v>
+        <v>493678</v>
       </c>
       <c r="R165" t="n">
-        <v>6834974</v>
+        <v>6834780</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17533,7 +17534,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17552,10 +17552,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129476546</v>
+        <v>129476536</v>
       </c>
       <c r="B166" t="n">
-        <v>91843</v>
+        <v>79663</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17563,21 +17563,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493733</v>
+        <v>493642</v>
       </c>
       <c r="R166" t="n">
-        <v>6834961</v>
+        <v>6834998</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17649,10 +17649,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129476549</v>
+        <v>129476546</v>
       </c>
       <c r="B167" t="n">
-        <v>91598</v>
+        <v>91847</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17660,21 +17660,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493677</v>
+        <v>493733</v>
       </c>
       <c r="R167" t="n">
-        <v>6835005</v>
+        <v>6834961</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17746,54 +17746,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129459653</v>
+        <v>129476531</v>
       </c>
       <c r="B168" t="n">
-        <v>98712</v>
+        <v>79663</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493740</v>
+        <v>493636</v>
       </c>
       <c r="R168" t="n">
-        <v>6834887</v>
+        <v>6834906</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17840,57 +17831,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129459536</v>
+        <v>129476587</v>
       </c>
       <c r="B169" t="n">
-        <v>98712</v>
+        <v>78710</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493723</v>
+        <v>493659</v>
       </c>
       <c r="R169" t="n">
-        <v>6834898</v>
+        <v>6834945</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17937,66 +17928,57 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129456373</v>
+        <v>129476581</v>
       </c>
       <c r="B170" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493796</v>
+        <v>493677</v>
       </c>
       <c r="R170" t="n">
-        <v>6834937</v>
+        <v>6834943</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18043,22 +18025,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476531</v>
+        <v>129476575</v>
       </c>
       <c r="B171" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18066,21 +18048,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18090,10 +18072,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493636</v>
+        <v>493728</v>
       </c>
       <c r="R171" t="n">
-        <v>6834906</v>
+        <v>6834886</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18152,7 +18134,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476581</v>
+        <v>129476570</v>
       </c>
       <c r="B172" t="n">
         <v>79044</v>
@@ -18187,10 +18169,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493677</v>
+        <v>493628</v>
       </c>
       <c r="R172" t="n">
-        <v>6834943</v>
+        <v>6834790</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18249,45 +18231,54 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129476575</v>
+        <v>129459653</v>
       </c>
       <c r="B173" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493728</v>
+        <v>493740</v>
       </c>
       <c r="R173" t="n">
-        <v>6834886</v>
+        <v>6834887</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18334,57 +18325,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129476570</v>
+        <v>129459536</v>
       </c>
       <c r="B174" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493628</v>
+        <v>493723</v>
       </c>
       <c r="R174" t="n">
-        <v>6834790</v>
+        <v>6834898</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18431,57 +18422,66 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129476587</v>
+        <v>129456373</v>
       </c>
       <c r="B175" t="n">
-        <v>78710</v>
+        <v>98716</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493659</v>
+        <v>493796</v>
       </c>
       <c r="R175" t="n">
-        <v>6834945</v>
+        <v>6834937</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,12 +18528,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -18737,7 +18737,7 @@
         <v>129456055</v>
       </c>
       <c r="B178" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>129459676</v>
       </c>
       <c r="B179" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>129458467</v>
       </c>
       <c r="B180" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19140,45 +19140,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129476551</v>
+        <v>129459964</v>
       </c>
       <c r="B182" t="n">
-        <v>78802</v>
+        <v>98716</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493632</v>
+        <v>493726</v>
       </c>
       <c r="R182" t="n">
-        <v>6834827</v>
+        <v>6834867</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19225,57 +19225,57 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129459964</v>
+        <v>129476551</v>
       </c>
       <c r="B183" t="n">
-        <v>98712</v>
+        <v>78802</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493726</v>
+        <v>493632</v>
       </c>
       <c r="R183" t="n">
-        <v>6834867</v>
+        <v>6834827</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19322,12 +19322,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19337,7 +19337,7 @@
         <v>129459836</v>
       </c>
       <c r="B184" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY184"/>
+  <dimension ref="A1:AY225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8276,45 +8276,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129460134</v>
+        <v>129476572</v>
       </c>
       <c r="B73" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493738</v>
+        <v>493675</v>
       </c>
       <c r="R73" t="n">
-        <v>6834870</v>
+        <v>6834825</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,57 +8361,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460004</v>
+        <v>129476556</v>
       </c>
       <c r="B74" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493728</v>
+        <v>493810</v>
       </c>
       <c r="R74" t="n">
-        <v>6834868</v>
+        <v>6834883</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,57 +8458,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476572</v>
+        <v>129460134</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493675</v>
+        <v>493738</v>
       </c>
       <c r="R75" t="n">
-        <v>6834825</v>
+        <v>6834870</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8555,57 +8555,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129476556</v>
+        <v>129460004</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493810</v>
+        <v>493728</v>
       </c>
       <c r="R76" t="n">
-        <v>6834883</v>
+        <v>6834868</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8652,12 +8652,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8667,7 +8667,7 @@
         <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,54 +8867,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129456176</v>
+        <v>129476554</v>
       </c>
       <c r="B79" t="n">
-        <v>98716</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493813</v>
+        <v>493648</v>
       </c>
       <c r="R79" t="n">
-        <v>6834955</v>
+        <v>6834929</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8955,28 +8955,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129457973</v>
+        <v>129456176</v>
       </c>
       <c r="B80" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9003,7 +9004,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9017,10 +9018,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493684</v>
+        <v>493813</v>
       </c>
       <c r="R80" t="n">
-        <v>6834986</v>
+        <v>6834955</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9079,45 +9080,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129461154</v>
+        <v>129457973</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493629</v>
+        <v>493684</v>
       </c>
       <c r="R81" t="n">
-        <v>6834827</v>
+        <v>6834986</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9176,7 +9186,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129460036</v>
+        <v>129461154</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -9211,10 +9221,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493728</v>
+        <v>493629</v>
       </c>
       <c r="R82" t="n">
-        <v>6834868</v>
+        <v>6834827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9273,7 +9283,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129460662</v>
+        <v>129460036</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -9308,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493658</v>
+        <v>493728</v>
       </c>
       <c r="R83" t="n">
-        <v>6834840</v>
+        <v>6834868</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9370,54 +9380,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129476554</v>
+        <v>129460662</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493648</v>
+        <v>493658</v>
       </c>
       <c r="R84" t="n">
-        <v>6834929</v>
+        <v>6834840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9458,64 +9459,63 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129457913</v>
+        <v>129476579</v>
       </c>
       <c r="B85" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493686</v>
+        <v>493687</v>
       </c>
       <c r="R85" t="n">
-        <v>6834989</v>
+        <v>6834917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9562,69 +9562,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129460883</v>
+        <v>129476589</v>
       </c>
       <c r="B86" t="n">
-        <v>98716</v>
+        <v>92832</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493637</v>
+        <v>493641</v>
       </c>
       <c r="R86" t="n">
-        <v>6834831</v>
+        <v>6834918</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9668,22 +9659,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129457745</v>
+        <v>129457913</v>
       </c>
       <c r="B87" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9708,26 +9699,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493678</v>
+        <v>493686</v>
       </c>
       <c r="R87" t="n">
-        <v>6835020</v>
+        <v>6834989</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9786,48 +9768,57 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129457992</v>
+        <v>129460883</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493684</v>
+        <v>493637</v>
       </c>
       <c r="R88" t="n">
-        <v>6834988</v>
+        <v>6834831</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9883,45 +9874,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129476579</v>
+        <v>129457745</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493687</v>
+        <v>493678</v>
       </c>
       <c r="R89" t="n">
-        <v>6834917</v>
+        <v>6835020</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9968,57 +9968,57 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129476589</v>
+        <v>129457992</v>
       </c>
       <c r="B90" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493641</v>
+        <v>493684</v>
       </c>
       <c r="R90" t="n">
-        <v>6834918</v>
+        <v>6834988</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10065,12 +10065,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129476583</v>
+        <v>129476532</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>493664</v>
+        <v>493619</v>
       </c>
       <c r="R92" t="n">
-        <v>6834992</v>
+        <v>6834843</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10271,45 +10271,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476566</v>
+        <v>129476555</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493646</v>
+        <v>493666</v>
       </c>
       <c r="R93" t="n">
-        <v>6834937</v>
+        <v>6834982</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10350,6 +10359,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10368,7 +10378,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476574</v>
+        <v>129476583</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10403,10 +10413,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493702</v>
+        <v>493664</v>
       </c>
       <c r="R94" t="n">
-        <v>6834858</v>
+        <v>6834992</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10465,10 +10475,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476532</v>
+        <v>129476566</v>
       </c>
       <c r="B95" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10476,21 +10486,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10500,10 +10510,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493619</v>
+        <v>493646</v>
       </c>
       <c r="R95" t="n">
-        <v>6834843</v>
+        <v>6834937</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10562,54 +10572,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476555</v>
+        <v>129476574</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493666</v>
+        <v>493702</v>
       </c>
       <c r="R96" t="n">
-        <v>6834982</v>
+        <v>6834858</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10650,7 +10651,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476560</v>
+        <v>129476544</v>
       </c>
       <c r="B98" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10777,28 +10777,29 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -10808,10 +10809,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493684</v>
+        <v>493634</v>
       </c>
       <c r="R98" t="n">
-        <v>6834860</v>
+        <v>6834983</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10852,7 +10853,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10871,10 +10871,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129455841</v>
+        <v>129476560</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10882,34 +10882,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493803</v>
+        <v>493684</v>
       </c>
       <c r="R99" t="n">
-        <v>6834901</v>
+        <v>6834860</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10950,28 +10957,29 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476544</v>
+        <v>129476569</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10979,42 +10987,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493634</v>
+        <v>493626</v>
       </c>
       <c r="R100" t="n">
-        <v>6834983</v>
+        <v>6834837</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11073,54 +11073,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129455942</v>
+        <v>129476578</v>
       </c>
       <c r="B101" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493802</v>
+        <v>493718</v>
       </c>
       <c r="R101" t="n">
-        <v>6834925</v>
+        <v>6834894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11167,44 +11158,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129458908</v>
+        <v>129455841</v>
       </c>
       <c r="B102" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11214,10 +11205,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493702</v>
+        <v>493803</v>
       </c>
       <c r="R102" t="n">
-        <v>6834942</v>
+        <v>6834901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11276,10 +11267,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129458098</v>
+        <v>129455942</v>
       </c>
       <c r="B103" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11306,7 +11297,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11320,10 +11311,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493682</v>
+        <v>493802</v>
       </c>
       <c r="R103" t="n">
-        <v>6834975</v>
+        <v>6834925</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11382,45 +11373,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129476537</v>
+        <v>129458908</v>
       </c>
       <c r="B104" t="n">
-        <v>79634</v>
+        <v>98724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493659</v>
+        <v>493702</v>
       </c>
       <c r="R104" t="n">
-        <v>6834945</v>
+        <v>6834942</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11467,57 +11458,66 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129476569</v>
+        <v>129458098</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493626</v>
+        <v>493682</v>
       </c>
       <c r="R105" t="n">
-        <v>6834837</v>
+        <v>6834975</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11564,22 +11564,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129476578</v>
+        <v>129476537</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11587,21 +11587,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11611,10 +11611,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493718</v>
+        <v>493659</v>
       </c>
       <c r="R106" t="n">
-        <v>6834894</v>
+        <v>6834945</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11870,7 +11870,7 @@
         <v>129456312</v>
       </c>
       <c r="B109" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129458436</v>
+        <v>129456198</v>
       </c>
       <c r="B112" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12195,17 +12195,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493653</v>
+        <v>493810</v>
       </c>
       <c r="R112" t="n">
-        <v>6835020</v>
+        <v>6834955</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12264,10 +12273,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129456198</v>
+        <v>129458436</v>
       </c>
       <c r="B113" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12292,26 +12301,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493810</v>
+        <v>493653</v>
       </c>
       <c r="R113" t="n">
-        <v>6834955</v>
+        <v>6835020</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12467,10 +12467,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129476584</v>
+        <v>129476558</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12478,21 +12478,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12502,10 +12502,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493670</v>
+        <v>493629</v>
       </c>
       <c r="R115" t="n">
-        <v>6834995</v>
+        <v>6834823</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12564,10 +12564,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476558</v>
+        <v>129460271</v>
       </c>
       <c r="B116" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12575,34 +12575,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493629</v>
+        <v>493731</v>
       </c>
       <c r="R116" t="n">
-        <v>6834823</v>
+        <v>6834853</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12649,19 +12649,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129460271</v>
+        <v>129476584</v>
       </c>
       <c r="B117" t="n">
         <v>79044</v>
@@ -12692,14 +12692,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493731</v>
+        <v>493670</v>
       </c>
       <c r="R117" t="n">
-        <v>6834853</v>
+        <v>6834995</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12746,12 +12746,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12761,7 +12761,7 @@
         <v>129459508</v>
       </c>
       <c r="B118" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>129459731</v>
       </c>
       <c r="B119" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>129459774</v>
       </c>
       <c r="B120" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13067,10 +13067,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129476559</v>
+        <v>129476541</v>
       </c>
       <c r="B121" t="n">
-        <v>78801</v>
+        <v>91550</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13078,41 +13078,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493626</v>
+        <v>493780</v>
       </c>
       <c r="R121" t="n">
-        <v>6834843</v>
+        <v>6834984</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13153,7 +13146,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13172,45 +13164,52 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476590</v>
+        <v>129476559</v>
       </c>
       <c r="B122" t="n">
-        <v>92831</v>
+        <v>78801</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493628</v>
+        <v>493626</v>
       </c>
       <c r="R122" t="n">
-        <v>6834891</v>
+        <v>6834843</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13251,6 +13250,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13269,32 +13269,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129476541</v>
+        <v>129476590</v>
       </c>
       <c r="B123" t="n">
-        <v>91549</v>
+        <v>92832</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13304,10 +13304,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493780</v>
+        <v>493628</v>
       </c>
       <c r="R123" t="n">
-        <v>6834984</v>
+        <v>6834891</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13369,7 +13369,7 @@
         <v>129461070</v>
       </c>
       <c r="B124" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>129457707</v>
       </c>
       <c r="B125" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>129456013</v>
       </c>
       <c r="B126" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>129456404</v>
       </c>
       <c r="B127" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>129456103</v>
       </c>
       <c r="B128" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13878,45 +13878,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129458645</v>
+        <v>129456470</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493662</v>
+        <v>493783</v>
       </c>
       <c r="R129" t="n">
-        <v>6834952</v>
+        <v>6834931</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13975,32 +13984,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129455888</v>
+        <v>129458700</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14010,13 +14019,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493811</v>
+        <v>493675</v>
       </c>
       <c r="R130" t="n">
-        <v>6834925</v>
+        <v>6834963</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14072,48 +14081,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129458700</v>
+        <v>129476550</v>
       </c>
       <c r="B131" t="n">
-        <v>98716</v>
+        <v>78802</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493675</v>
+        <v>493625</v>
       </c>
       <c r="R131" t="n">
-        <v>6834963</v>
+        <v>6834820</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14157,22 +14166,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129476550</v>
+        <v>129458645</v>
       </c>
       <c r="B132" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14180,34 +14189,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493625</v>
+        <v>493662</v>
       </c>
       <c r="R132" t="n">
-        <v>6834820</v>
+        <v>6834952</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14254,22 +14263,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129476530</v>
+        <v>129455888</v>
       </c>
       <c r="B133" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14277,34 +14286,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493705</v>
+        <v>493811</v>
       </c>
       <c r="R133" t="n">
-        <v>6834890</v>
+        <v>6834925</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14351,66 +14360,57 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129456470</v>
+        <v>129476530</v>
       </c>
       <c r="B134" t="n">
-        <v>98716</v>
+        <v>79076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493783</v>
+        <v>493705</v>
       </c>
       <c r="R134" t="n">
-        <v>6834931</v>
+        <v>6834890</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14457,22 +14457,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476588</v>
+        <v>129476548</v>
       </c>
       <c r="B135" t="n">
-        <v>78710</v>
+        <v>91603</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493619</v>
+        <v>493687</v>
       </c>
       <c r="R135" t="n">
-        <v>6834998</v>
+        <v>6834930</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,45 +14566,54 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476573</v>
+        <v>129476553</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493661</v>
+        <v>493591</v>
       </c>
       <c r="R136" t="n">
-        <v>6834848</v>
+        <v>6835008</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14645,6 +14654,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14663,32 +14673,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129459901</v>
+        <v>129458414</v>
       </c>
       <c r="B137" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14698,10 +14708,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493734</v>
+        <v>493670</v>
       </c>
       <c r="R137" t="n">
-        <v>6834875</v>
+        <v>6834981</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14760,10 +14770,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129476580</v>
+        <v>129476588</v>
       </c>
       <c r="B138" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14771,21 +14781,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14795,10 +14805,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493675</v>
+        <v>493619</v>
       </c>
       <c r="R138" t="n">
-        <v>6834937</v>
+        <v>6834998</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14857,54 +14867,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476553</v>
+        <v>129476573</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493591</v>
+        <v>493661</v>
       </c>
       <c r="R139" t="n">
-        <v>6835008</v>
+        <v>6834848</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14945,7 +14946,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14964,32 +14964,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129458414</v>
+        <v>129459901</v>
       </c>
       <c r="B140" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14999,10 +14999,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493670</v>
+        <v>493734</v>
       </c>
       <c r="R140" t="n">
-        <v>6834981</v>
+        <v>6834875</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15061,10 +15061,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476552</v>
+        <v>129476580</v>
       </c>
       <c r="B141" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15072,21 +15072,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15096,10 +15096,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493629</v>
+        <v>493675</v>
       </c>
       <c r="R141" t="n">
-        <v>6834831</v>
+        <v>6834937</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15158,10 +15158,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129476548</v>
+        <v>129476552</v>
       </c>
       <c r="B142" t="n">
-        <v>91602</v>
+        <v>78802</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15169,21 +15169,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15193,10 +15193,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493687</v>
+        <v>493629</v>
       </c>
       <c r="R142" t="n">
-        <v>6834930</v>
+        <v>6834831</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15258,7 +15258,7 @@
         <v>129457830</v>
       </c>
       <c r="B143" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>129458085</v>
       </c>
       <c r="B144" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>129459852</v>
       </c>
       <c r="B145" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>129460207</v>
       </c>
       <c r="B146" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15661,10 +15661,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129458803</v>
+        <v>129476540</v>
       </c>
       <c r="B147" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15672,34 +15672,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493683</v>
+        <v>493723</v>
       </c>
       <c r="R147" t="n">
-        <v>6834951</v>
+        <v>6834965</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15746,22 +15746,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129476543</v>
+        <v>129458803</v>
       </c>
       <c r="B148" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15769,42 +15769,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493676</v>
+        <v>493683</v>
       </c>
       <c r="R148" t="n">
-        <v>6834800</v>
+        <v>6834951</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15851,22 +15843,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129476540</v>
+        <v>129476543</v>
       </c>
       <c r="B149" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15874,34 +15866,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493723</v>
+        <v>493676</v>
       </c>
       <c r="R149" t="n">
-        <v>6834965</v>
+        <v>6834800</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15963,7 +15963,7 @@
         <v>129476539</v>
       </c>
       <c r="B150" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>129460421</v>
       </c>
       <c r="B152" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16251,32 +16251,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129460288</v>
+        <v>129460467</v>
       </c>
       <c r="B153" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16286,10 +16286,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493733</v>
+        <v>493728</v>
       </c>
       <c r="R153" t="n">
-        <v>6834848</v>
+        <v>6834842</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16348,54 +16348,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129458972</v>
+        <v>129476567</v>
       </c>
       <c r="B154" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>493700</v>
+        <v>493634</v>
       </c>
       <c r="R154" t="n">
-        <v>6834942</v>
+        <v>6834889</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16442,19 +16433,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129460467</v>
+        <v>129476576</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -16485,14 +16476,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493728</v>
+        <v>493725</v>
       </c>
       <c r="R155" t="n">
-        <v>6834842</v>
+        <v>6834888</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16539,57 +16530,57 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129476567</v>
+        <v>129460288</v>
       </c>
       <c r="B156" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493634</v>
+        <v>493733</v>
       </c>
       <c r="R156" t="n">
-        <v>6834889</v>
+        <v>6834848</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16636,57 +16627,66 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129476576</v>
+        <v>129458972</v>
       </c>
       <c r="B157" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493725</v>
+        <v>493700</v>
       </c>
       <c r="R157" t="n">
-        <v>6834888</v>
+        <v>6834942</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16733,66 +16733,57 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129459449</v>
+        <v>129476546</v>
       </c>
       <c r="B158" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493720</v>
+        <v>493733</v>
       </c>
       <c r="R158" t="n">
-        <v>6834910</v>
+        <v>6834961</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16839,66 +16830,57 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129459953</v>
+        <v>129457857</v>
       </c>
       <c r="B159" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493729</v>
+        <v>493676</v>
       </c>
       <c r="R159" t="n">
-        <v>6834873</v>
+        <v>6835001</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16957,57 +16939,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129476562</v>
+        <v>129458226</v>
       </c>
       <c r="B160" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493676</v>
+        <v>493670</v>
       </c>
       <c r="R160" t="n">
-        <v>6834974</v>
+        <v>6834981</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17048,29 +17018,28 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129459208</v>
+        <v>129476536</v>
       </c>
       <c r="B161" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17078,34 +17047,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>493698</v>
+        <v>493642</v>
       </c>
       <c r="R161" t="n">
-        <v>6834943</v>
+        <v>6834998</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17152,22 +17121,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129457857</v>
+        <v>129476533</v>
       </c>
       <c r="B162" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17175,34 +17144,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493676</v>
+        <v>493678</v>
       </c>
       <c r="R162" t="n">
-        <v>6835001</v>
+        <v>6834780</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17249,57 +17218,66 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129458226</v>
+        <v>129459449</v>
       </c>
       <c r="B163" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493670</v>
+        <v>493720</v>
       </c>
       <c r="R163" t="n">
-        <v>6834981</v>
+        <v>6834910</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17358,45 +17336,54 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129476549</v>
+        <v>129459953</v>
       </c>
       <c r="B164" t="n">
-        <v>91602</v>
+        <v>98724</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493677</v>
+        <v>493729</v>
       </c>
       <c r="R164" t="n">
-        <v>6835005</v>
+        <v>6834873</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17443,57 +17430,69 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129476533</v>
+        <v>129476562</v>
       </c>
       <c r="B165" t="n">
-        <v>79663</v>
+        <v>98724</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493678</v>
+        <v>493676</v>
       </c>
       <c r="R165" t="n">
-        <v>6834780</v>
+        <v>6834974</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17534,6 +17533,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17552,10 +17552,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129476536</v>
+        <v>129476549</v>
       </c>
       <c r="B166" t="n">
-        <v>79663</v>
+        <v>91603</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17563,21 +17563,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493642</v>
+        <v>493677</v>
       </c>
       <c r="R166" t="n">
-        <v>6834998</v>
+        <v>6835005</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17649,10 +17649,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129476546</v>
+        <v>129459208</v>
       </c>
       <c r="B167" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17660,34 +17660,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493733</v>
+        <v>493698</v>
       </c>
       <c r="R167" t="n">
-        <v>6834961</v>
+        <v>6834943</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17734,22 +17734,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476531</v>
+        <v>129476587</v>
       </c>
       <c r="B168" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17757,21 +17757,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17781,10 +17781,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493636</v>
+        <v>493659</v>
       </c>
       <c r="R168" t="n">
-        <v>6834906</v>
+        <v>6834945</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17843,10 +17843,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129476587</v>
+        <v>129476581</v>
       </c>
       <c r="B169" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17854,21 +17854,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17878,10 +17878,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493659</v>
+        <v>493677</v>
       </c>
       <c r="R169" t="n">
-        <v>6834945</v>
+        <v>6834943</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17940,7 +17940,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129476581</v>
+        <v>129476575</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -17975,10 +17975,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493677</v>
+        <v>493728</v>
       </c>
       <c r="R170" t="n">
-        <v>6834943</v>
+        <v>6834886</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18037,7 +18037,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476575</v>
+        <v>129476570</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18072,10 +18072,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493728</v>
+        <v>493628</v>
       </c>
       <c r="R171" t="n">
-        <v>6834886</v>
+        <v>6834790</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18134,10 +18134,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476570</v>
+        <v>129476531</v>
       </c>
       <c r="B172" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18145,21 +18145,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18169,10 +18169,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493628</v>
+        <v>493636</v>
       </c>
       <c r="R172" t="n">
-        <v>6834790</v>
+        <v>6834906</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18234,7 +18234,7 @@
         <v>129459653</v>
       </c>
       <c r="B173" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>129459536</v>
       </c>
       <c r="B174" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>129456373</v>
       </c>
       <c r="B175" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129459599</v>
+        <v>129460260</v>
       </c>
       <c r="B176" t="n">
         <v>79044</v>
@@ -18575,10 +18575,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493726</v>
+        <v>493731</v>
       </c>
       <c r="R176" t="n">
-        <v>6834891</v>
+        <v>6834851</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,7 +18637,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129460260</v>
+        <v>129459599</v>
       </c>
       <c r="B177" t="n">
         <v>79044</v>
@@ -18672,10 +18672,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493731</v>
+        <v>493726</v>
       </c>
       <c r="R177" t="n">
-        <v>6834851</v>
+        <v>6834891</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18737,7 +18737,7 @@
         <v>129456055</v>
       </c>
       <c r="B178" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>129459676</v>
       </c>
       <c r="B179" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>129458467</v>
       </c>
       <c r="B180" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19043,10 +19043,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129476561</v>
+        <v>129476551</v>
       </c>
       <c r="B181" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19054,21 +19054,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19078,10 +19078,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493634</v>
+        <v>493632</v>
       </c>
       <c r="R181" t="n">
-        <v>6834985</v>
+        <v>6834827</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19140,45 +19140,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129459964</v>
+        <v>129476561</v>
       </c>
       <c r="B182" t="n">
-        <v>98716</v>
+        <v>78801</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493726</v>
+        <v>493634</v>
       </c>
       <c r="R182" t="n">
-        <v>6834867</v>
+        <v>6834985</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19225,57 +19225,57 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129476551</v>
+        <v>129459964</v>
       </c>
       <c r="B183" t="n">
-        <v>78802</v>
+        <v>98724</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493632</v>
+        <v>493726</v>
       </c>
       <c r="R183" t="n">
-        <v>6834827</v>
+        <v>6834867</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19322,12 +19322,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19337,7 +19337,7 @@
         <v>129459836</v>
       </c>
       <c r="B184" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19428,6 +19428,4150 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>129525028</v>
+      </c>
+      <c r="B185" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>493857</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6834694</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>129525359</v>
+      </c>
+      <c r="B186" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>493934</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6834670</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>129525566</v>
+      </c>
+      <c r="B187" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>493930</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6834516</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>129525479</v>
+      </c>
+      <c r="B188" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>493825</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6834594</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>129525456</v>
+      </c>
+      <c r="B189" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>493893</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6834612</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>129525603</v>
+      </c>
+      <c r="B190" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>493825</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6834572</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>129525395</v>
+      </c>
+      <c r="B191" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>493923</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6834647</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>129525463</v>
+      </c>
+      <c r="B192" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>493891</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6834621</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>129525450</v>
+      </c>
+      <c r="B193" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>493926</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6834613</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>129525020</v>
+      </c>
+      <c r="B194" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>493860</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6834704</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>129525370</v>
+      </c>
+      <c r="B195" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>493942</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6834657</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>129525895</v>
+      </c>
+      <c r="B196" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>493792</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6834620</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>129525059</v>
+      </c>
+      <c r="B197" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>493851</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6834680</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>129525089</v>
+      </c>
+      <c r="B198" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>493895</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6834684</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>129525351</v>
+      </c>
+      <c r="B199" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>493874</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6834658</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>129525466</v>
+      </c>
+      <c r="B200" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>493832</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6834595</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>129525470</v>
+      </c>
+      <c r="B201" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>493900</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6834623</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>129525496</v>
+      </c>
+      <c r="B202" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>493821</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6834572</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>129525012</v>
+      </c>
+      <c r="B203" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>493866</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6834688</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>129525041</v>
+      </c>
+      <c r="B204" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>493881</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6834662</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>129525474</v>
+      </c>
+      <c r="B205" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>493908</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6834595</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>129525022</v>
+      </c>
+      <c r="B206" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>493867</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6834661</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>129525442</v>
+      </c>
+      <c r="B207" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>493925</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6834617</v>
+      </c>
+      <c r="S207" t="n">
+        <v>10</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>129525477</v>
+      </c>
+      <c r="B208" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>493823</v>
+      </c>
+      <c r="R208" t="n">
+        <v>6834595</v>
+      </c>
+      <c r="S208" t="n">
+        <v>10</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>129525320</v>
+      </c>
+      <c r="B209" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>493859</v>
+      </c>
+      <c r="R209" t="n">
+        <v>6834674</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>129525078</v>
+      </c>
+      <c r="B210" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>493886</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6834673</v>
+      </c>
+      <c r="S210" t="n">
+        <v>10</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>129524983</v>
+      </c>
+      <c r="B211" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>493871</v>
+      </c>
+      <c r="R211" t="n">
+        <v>6834690</v>
+      </c>
+      <c r="S211" t="n">
+        <v>10</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>129525001</v>
+      </c>
+      <c r="B212" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>493870</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6834690</v>
+      </c>
+      <c r="S212" t="n">
+        <v>10</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>129525462</v>
+      </c>
+      <c r="B213" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>493832</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6834595</v>
+      </c>
+      <c r="S213" t="n">
+        <v>10</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>129525429</v>
+      </c>
+      <c r="B214" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>493788</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6834656</v>
+      </c>
+      <c r="S214" t="n">
+        <v>10</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>129525451</v>
+      </c>
+      <c r="B215" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>493788</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6834656</v>
+      </c>
+      <c r="S215" t="n">
+        <v>10</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>129525529</v>
+      </c>
+      <c r="B216" t="n">
+        <v>79076</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>185</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>493916</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6834525</v>
+      </c>
+      <c r="S216" t="n">
+        <v>10</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>129525489</v>
+      </c>
+      <c r="B217" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>493817</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6834579</v>
+      </c>
+      <c r="S217" t="n">
+        <v>10</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>129525382</v>
+      </c>
+      <c r="B218" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>493822</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6834648</v>
+      </c>
+      <c r="S218" t="n">
+        <v>10</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>129525418</v>
+      </c>
+      <c r="B219" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>493930</v>
+      </c>
+      <c r="R219" t="n">
+        <v>6834628</v>
+      </c>
+      <c r="S219" t="n">
+        <v>10</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>129525528</v>
+      </c>
+      <c r="B220" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>493826</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6834572</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>129525130</v>
+      </c>
+      <c r="B221" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>493858</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6834661</v>
+      </c>
+      <c r="S221" t="n">
+        <v>10</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>129525680</v>
+      </c>
+      <c r="B222" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>493840</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6834519</v>
+      </c>
+      <c r="S222" t="n">
+        <v>10</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>129525347</v>
+      </c>
+      <c r="B223" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>493915</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6834671</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>129525601</v>
+      </c>
+      <c r="B224" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>493922</v>
+      </c>
+      <c r="R224" t="n">
+        <v>6834518</v>
+      </c>
+      <c r="S224" t="n">
+        <v>10</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>129525445</v>
+      </c>
+      <c r="B225" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>493900</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6834610</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,45 +8179,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476586</v>
+        <v>129460134</v>
       </c>
       <c r="B72" t="n">
-        <v>78710</v>
+        <v>98724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493684</v>
+        <v>493738</v>
       </c>
       <c r="R72" t="n">
-        <v>6834869</v>
+        <v>6834870</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8264,57 +8264,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129476572</v>
+        <v>129460004</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493675</v>
+        <v>493728</v>
       </c>
       <c r="R73" t="n">
-        <v>6834825</v>
+        <v>6834868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,57 +8361,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129476556</v>
+        <v>129460228</v>
       </c>
       <c r="B74" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493810</v>
+        <v>493736</v>
       </c>
       <c r="R74" t="n">
-        <v>6834883</v>
+        <v>6834865</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,57 +8467,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129460134</v>
+        <v>129476586</v>
       </c>
       <c r="B75" t="n">
-        <v>98724</v>
+        <v>78710</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493738</v>
+        <v>493684</v>
       </c>
       <c r="R75" t="n">
-        <v>6834870</v>
+        <v>6834869</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8555,57 +8564,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129460004</v>
+        <v>129476572</v>
       </c>
       <c r="B76" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493728</v>
+        <v>493675</v>
       </c>
       <c r="R76" t="n">
-        <v>6834868</v>
+        <v>6834825</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8652,66 +8661,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129460228</v>
+        <v>129476556</v>
       </c>
       <c r="B77" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493736</v>
+        <v>493810</v>
       </c>
       <c r="R77" t="n">
-        <v>6834865</v>
+        <v>6834883</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,22 +8758,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129476585</v>
+        <v>129460036</v>
       </c>
       <c r="B78" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8781,34 +8781,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493700</v>
+        <v>493728</v>
       </c>
       <c r="R78" t="n">
-        <v>6834837</v>
+        <v>6834868</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8855,66 +8855,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129476554</v>
+        <v>129461154</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493648</v>
+        <v>493629</v>
       </c>
       <c r="R79" t="n">
-        <v>6834929</v>
+        <v>6834827</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8955,73 +8946,63 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129456176</v>
+        <v>129460662</v>
       </c>
       <c r="B80" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493813</v>
+        <v>493658</v>
       </c>
       <c r="R80" t="n">
-        <v>6834955</v>
+        <v>6834840</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9080,54 +9061,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129457973</v>
+        <v>129476585</v>
       </c>
       <c r="B81" t="n">
-        <v>98724</v>
+        <v>78710</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493684</v>
+        <v>493700</v>
       </c>
       <c r="R81" t="n">
-        <v>6834986</v>
+        <v>6834837</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9174,57 +9146,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129461154</v>
+        <v>129476554</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493629</v>
+        <v>493648</v>
       </c>
       <c r="R82" t="n">
-        <v>6834827</v>
+        <v>6834929</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9265,63 +9246,73 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129460036</v>
+        <v>129456176</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493728</v>
+        <v>493813</v>
       </c>
       <c r="R83" t="n">
-        <v>6834868</v>
+        <v>6834955</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9380,45 +9371,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129460662</v>
+        <v>129457973</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493658</v>
+        <v>493684</v>
       </c>
       <c r="R84" t="n">
-        <v>6834840</v>
+        <v>6834986</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9477,32 +9477,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129476579</v>
+        <v>129476589</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9512,10 +9512,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493687</v>
+        <v>493641</v>
       </c>
       <c r="R85" t="n">
-        <v>6834917</v>
+        <v>6834918</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9574,45 +9574,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129476589</v>
+        <v>129457992</v>
       </c>
       <c r="B86" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493641</v>
+        <v>493684</v>
       </c>
       <c r="R86" t="n">
-        <v>6834918</v>
+        <v>6834988</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9659,57 +9659,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129457913</v>
+        <v>129476547</v>
       </c>
       <c r="B87" t="n">
-        <v>98724</v>
+        <v>79068</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493686</v>
+        <v>493722</v>
       </c>
       <c r="R87" t="n">
-        <v>6834989</v>
+        <v>6834900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9756,69 +9756,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129460883</v>
+        <v>129476579</v>
       </c>
       <c r="B88" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493637</v>
+        <v>493687</v>
       </c>
       <c r="R88" t="n">
-        <v>6834831</v>
+        <v>6834917</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9862,19 +9853,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129457745</v>
+        <v>129457913</v>
       </c>
       <c r="B89" t="n">
         <v>98724</v>
@@ -9902,26 +9893,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493678</v>
+        <v>493686</v>
       </c>
       <c r="R89" t="n">
-        <v>6835020</v>
+        <v>6834989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9980,48 +9962,57 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129457992</v>
+        <v>129460883</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493684</v>
+        <v>493637</v>
       </c>
       <c r="R90" t="n">
-        <v>6834988</v>
+        <v>6834831</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10077,45 +10068,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129476547</v>
+        <v>129457745</v>
       </c>
       <c r="B91" t="n">
-        <v>79068</v>
+        <v>98724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>493722</v>
+        <v>493678</v>
       </c>
       <c r="R91" t="n">
-        <v>6834900</v>
+        <v>6835020</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10162,12 +10162,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10271,54 +10271,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476555</v>
+        <v>129476566</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493666</v>
+        <v>493646</v>
       </c>
       <c r="R93" t="n">
-        <v>6834982</v>
+        <v>6834937</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10359,7 +10350,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10378,7 +10368,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476583</v>
+        <v>129476574</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10413,10 +10403,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493664</v>
+        <v>493702</v>
       </c>
       <c r="R94" t="n">
-        <v>6834992</v>
+        <v>6834858</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10475,45 +10465,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476566</v>
+        <v>129476555</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493646</v>
+        <v>493666</v>
       </c>
       <c r="R95" t="n">
-        <v>6834937</v>
+        <v>6834982</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10554,6 +10553,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10572,7 +10572,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476574</v>
+        <v>129476583</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493702</v>
+        <v>493664</v>
       </c>
       <c r="R96" t="n">
-        <v>6834858</v>
+        <v>6834992</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10976,7 +10976,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476569</v>
+        <v>129476578</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493626</v>
+        <v>493718</v>
       </c>
       <c r="R100" t="n">
-        <v>6834837</v>
+        <v>6834894</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129476578</v>
+        <v>129455841</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11104,14 +11104,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493718</v>
+        <v>493803</v>
       </c>
       <c r="R101" t="n">
-        <v>6834894</v>
+        <v>6834901</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11158,19 +11158,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129455841</v>
+        <v>129476569</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11201,14 +11201,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493803</v>
+        <v>493626</v>
       </c>
       <c r="R102" t="n">
-        <v>6834901</v>
+        <v>6834837</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11255,66 +11255,57 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129455942</v>
+        <v>129476537</v>
       </c>
       <c r="B103" t="n">
-        <v>98724</v>
+        <v>79634</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493802</v>
+        <v>493659</v>
       </c>
       <c r="R103" t="n">
-        <v>6834925</v>
+        <v>6834945</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11361,19 +11352,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129458908</v>
+        <v>129455942</v>
       </c>
       <c r="B104" t="n">
         <v>98724</v>
@@ -11401,17 +11392,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493702</v>
+        <v>493802</v>
       </c>
       <c r="R104" t="n">
-        <v>6834942</v>
+        <v>6834925</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11470,7 +11470,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129458098</v>
+        <v>129458908</v>
       </c>
       <c r="B105" t="n">
         <v>98724</v>
@@ -11498,26 +11498,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493682</v>
+        <v>493702</v>
       </c>
       <c r="R105" t="n">
-        <v>6834975</v>
+        <v>6834942</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11576,45 +11567,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129476537</v>
+        <v>129458098</v>
       </c>
       <c r="B106" t="n">
-        <v>79634</v>
+        <v>98724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493659</v>
+        <v>493682</v>
       </c>
       <c r="R106" t="n">
-        <v>6834945</v>
+        <v>6834975</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11661,12 +11661,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11770,45 +11770,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129476577</v>
+        <v>129456312</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493707</v>
+        <v>493787</v>
       </c>
       <c r="R108" t="n">
-        <v>6834895</v>
+        <v>6834957</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11855,66 +11864,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129456312</v>
+        <v>129476577</v>
       </c>
       <c r="B109" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493787</v>
+        <v>493707</v>
       </c>
       <c r="R109" t="n">
-        <v>6834957</v>
+        <v>6834895</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11961,12 +11961,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12167,54 +12167,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129456198</v>
+        <v>129476538</v>
       </c>
       <c r="B112" t="n">
-        <v>98724</v>
+        <v>79634</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493810</v>
+        <v>493627</v>
       </c>
       <c r="R112" t="n">
-        <v>6834955</v>
+        <v>6834986</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12261,19 +12252,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129458436</v>
+        <v>129456198</v>
       </c>
       <c r="B113" t="n">
         <v>98724</v>
@@ -12301,17 +12292,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493653</v>
+        <v>493810</v>
       </c>
       <c r="R113" t="n">
-        <v>6835020</v>
+        <v>6834955</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12370,45 +12370,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129476538</v>
+        <v>129458436</v>
       </c>
       <c r="B114" t="n">
-        <v>79634</v>
+        <v>98724</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493627</v>
+        <v>493653</v>
       </c>
       <c r="R114" t="n">
-        <v>6834986</v>
+        <v>6835020</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,22 +12455,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129476558</v>
+        <v>129460271</v>
       </c>
       <c r="B115" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12478,34 +12478,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493629</v>
+        <v>493731</v>
       </c>
       <c r="R115" t="n">
-        <v>6834823</v>
+        <v>6834853</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12552,22 +12552,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129460271</v>
+        <v>129476558</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12575,34 +12575,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493731</v>
+        <v>493629</v>
       </c>
       <c r="R116" t="n">
-        <v>6834853</v>
+        <v>6834823</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12649,12 +12649,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13067,32 +13067,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129476541</v>
+        <v>129476590</v>
       </c>
       <c r="B121" t="n">
-        <v>91550</v>
+        <v>92832</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493780</v>
+        <v>493628</v>
       </c>
       <c r="R121" t="n">
-        <v>6834984</v>
+        <v>6834891</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13164,10 +13164,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476559</v>
+        <v>129476541</v>
       </c>
       <c r="B122" t="n">
-        <v>78801</v>
+        <v>91550</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13175,41 +13175,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493626</v>
+        <v>493780</v>
       </c>
       <c r="R122" t="n">
-        <v>6834843</v>
+        <v>6834984</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13250,7 +13243,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13269,45 +13261,52 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129476590</v>
+        <v>129476559</v>
       </c>
       <c r="B123" t="n">
-        <v>92832</v>
+        <v>78801</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493628</v>
+        <v>493626</v>
       </c>
       <c r="R123" t="n">
-        <v>6834891</v>
+        <v>6834843</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13348,6 +13347,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13878,54 +13878,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129456470</v>
+        <v>129476530</v>
       </c>
       <c r="B129" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493783</v>
+        <v>493705</v>
       </c>
       <c r="R129" t="n">
-        <v>6834931</v>
+        <v>6834890</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13972,44 +13963,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129458700</v>
+        <v>129455888</v>
       </c>
       <c r="B130" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14019,13 +14010,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493675</v>
+        <v>493811</v>
       </c>
       <c r="R130" t="n">
-        <v>6834963</v>
+        <v>6834925</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14081,10 +14072,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129476550</v>
+        <v>129458645</v>
       </c>
       <c r="B131" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14092,34 +14083,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493625</v>
+        <v>493662</v>
       </c>
       <c r="R131" t="n">
-        <v>6834820</v>
+        <v>6834952</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14166,57 +14157,66 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129458645</v>
+        <v>129456470</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493662</v>
+        <v>493783</v>
       </c>
       <c r="R132" t="n">
-        <v>6834952</v>
+        <v>6834931</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14275,32 +14275,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129455888</v>
+        <v>129458700</v>
       </c>
       <c r="B133" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493811</v>
+        <v>493675</v>
       </c>
       <c r="R133" t="n">
-        <v>6834925</v>
+        <v>6834963</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14372,10 +14372,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129476530</v>
+        <v>129476550</v>
       </c>
       <c r="B134" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14383,21 +14383,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493705</v>
+        <v>493625</v>
       </c>
       <c r="R134" t="n">
-        <v>6834890</v>
+        <v>6834820</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476548</v>
+        <v>129476588</v>
       </c>
       <c r="B135" t="n">
-        <v>91603</v>
+        <v>78710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493687</v>
+        <v>493619</v>
       </c>
       <c r="R135" t="n">
-        <v>6834930</v>
+        <v>6834998</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,54 +14566,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476553</v>
+        <v>129459901</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493591</v>
+        <v>493734</v>
       </c>
       <c r="R136" t="n">
-        <v>6835008</v>
+        <v>6834875</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14654,64 +14645,63 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129458414</v>
+        <v>129476548</v>
       </c>
       <c r="B137" t="n">
-        <v>98724</v>
+        <v>91603</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493670</v>
+        <v>493687</v>
       </c>
       <c r="R137" t="n">
-        <v>6834981</v>
+        <v>6834930</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14758,22 +14748,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129476588</v>
+        <v>129476573</v>
       </c>
       <c r="B138" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14781,21 +14771,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14805,10 +14795,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493619</v>
+        <v>493661</v>
       </c>
       <c r="R138" t="n">
-        <v>6834998</v>
+        <v>6834848</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14867,7 +14857,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476573</v>
+        <v>129476580</v>
       </c>
       <c r="B139" t="n">
         <v>79044</v>
@@ -14902,10 +14892,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493661</v>
+        <v>493675</v>
       </c>
       <c r="R139" t="n">
-        <v>6834848</v>
+        <v>6834937</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14964,45 +14954,54 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129459901</v>
+        <v>129476553</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493734</v>
+        <v>493591</v>
       </c>
       <c r="R140" t="n">
-        <v>6834875</v>
+        <v>6835008</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15043,28 +15042,29 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476580</v>
+        <v>129476552</v>
       </c>
       <c r="B141" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15072,21 +15072,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15096,10 +15096,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493675</v>
+        <v>493629</v>
       </c>
       <c r="R141" t="n">
-        <v>6834937</v>
+        <v>6834831</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15158,45 +15158,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129476552</v>
+        <v>129458414</v>
       </c>
       <c r="B142" t="n">
-        <v>78802</v>
+        <v>98724</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493629</v>
+        <v>493670</v>
       </c>
       <c r="R142" t="n">
-        <v>6834831</v>
+        <v>6834981</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15243,66 +15243,57 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129457830</v>
+        <v>129476540</v>
       </c>
       <c r="B143" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493676</v>
+        <v>493723</v>
       </c>
       <c r="R143" t="n">
-        <v>6835001</v>
+        <v>6834965</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,66 +15340,65 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129458085</v>
+        <v>129476543</v>
       </c>
       <c r="B144" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493690</v>
+        <v>493676</v>
       </c>
       <c r="R144" t="n">
-        <v>6834972</v>
+        <v>6834800</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15455,44 +15445,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129459852</v>
+        <v>129458803</v>
       </c>
       <c r="B145" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15502,10 +15492,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493730</v>
+        <v>493683</v>
       </c>
       <c r="R145" t="n">
-        <v>6834877</v>
+        <v>6834951</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15564,7 +15554,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129460207</v>
+        <v>129457830</v>
       </c>
       <c r="B146" t="n">
         <v>98724</v>
@@ -15592,17 +15582,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493738</v>
+        <v>493676</v>
       </c>
       <c r="R146" t="n">
-        <v>6834861</v>
+        <v>6835001</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15661,45 +15660,54 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129476540</v>
+        <v>129458085</v>
       </c>
       <c r="B147" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493723</v>
+        <v>493690</v>
       </c>
       <c r="R147" t="n">
-        <v>6834965</v>
+        <v>6834972</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15746,44 +15754,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129458803</v>
+        <v>129459852</v>
       </c>
       <c r="B148" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15793,10 +15801,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493683</v>
+        <v>493730</v>
       </c>
       <c r="R148" t="n">
-        <v>6834951</v>
+        <v>6834877</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15855,53 +15863,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129476543</v>
+        <v>129460207</v>
       </c>
       <c r="B149" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493676</v>
+        <v>493738</v>
       </c>
       <c r="R149" t="n">
-        <v>6834800</v>
+        <v>6834861</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,22 +15948,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476539</v>
+        <v>129476535</v>
       </c>
       <c r="B150" t="n">
-        <v>90582</v>
+        <v>79663</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15971,21 +15971,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493652</v>
+        <v>493703</v>
       </c>
       <c r="R150" t="n">
-        <v>6834985</v>
+        <v>6834865</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16057,10 +16057,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476535</v>
+        <v>129476539</v>
       </c>
       <c r="B151" t="n">
-        <v>79663</v>
+        <v>90582</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16068,21 +16068,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493703</v>
+        <v>493652</v>
       </c>
       <c r="R151" t="n">
-        <v>6834865</v>
+        <v>6834985</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16842,7 +16842,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129457857</v>
+        <v>129459208</v>
       </c>
       <c r="B159" t="n">
         <v>79044</v>
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493676</v>
+        <v>493698</v>
       </c>
       <c r="R159" t="n">
-        <v>6835001</v>
+        <v>6834943</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16939,10 +16939,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129458226</v>
+        <v>129476533</v>
       </c>
       <c r="B160" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16950,34 +16950,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493670</v>
+        <v>493678</v>
       </c>
       <c r="R160" t="n">
-        <v>6834981</v>
+        <v>6834780</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17024,12 +17024,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17133,10 +17133,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129476533</v>
+        <v>129458226</v>
       </c>
       <c r="B162" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17144,34 +17144,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493678</v>
+        <v>493670</v>
       </c>
       <c r="R162" t="n">
-        <v>6834780</v>
+        <v>6834981</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17218,66 +17218,57 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129459449</v>
+        <v>129457857</v>
       </c>
       <c r="B163" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493720</v>
+        <v>493676</v>
       </c>
       <c r="R163" t="n">
-        <v>6834910</v>
+        <v>6835001</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17336,54 +17327,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129459953</v>
+        <v>129476549</v>
       </c>
       <c r="B164" t="n">
-        <v>98724</v>
+        <v>91603</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493729</v>
+        <v>493677</v>
       </c>
       <c r="R164" t="n">
-        <v>6834873</v>
+        <v>6835005</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17430,19 +17412,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129476562</v>
+        <v>129459449</v>
       </c>
       <c r="B165" t="n">
         <v>98724</v>
@@ -17472,7 +17454,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -17480,19 +17462,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493676</v>
+        <v>493720</v>
       </c>
       <c r="R165" t="n">
-        <v>6834974</v>
+        <v>6834910</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17533,64 +17512,72 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129476549</v>
+        <v>129459953</v>
       </c>
       <c r="B166" t="n">
-        <v>91603</v>
+        <v>98724</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493677</v>
+        <v>493729</v>
       </c>
       <c r="R166" t="n">
-        <v>6835005</v>
+        <v>6834873</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17637,57 +17624,69 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129459208</v>
+        <v>129476562</v>
       </c>
       <c r="B167" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493698</v>
+        <v>493676</v>
       </c>
       <c r="R167" t="n">
-        <v>6834943</v>
+        <v>6834974</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17728,18 +17727,19 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -18037,10 +18037,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476570</v>
+        <v>129476531</v>
       </c>
       <c r="B171" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18048,21 +18048,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18072,10 +18072,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493628</v>
+        <v>493636</v>
       </c>
       <c r="R171" t="n">
-        <v>6834790</v>
+        <v>6834906</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18134,10 +18134,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476531</v>
+        <v>129476570</v>
       </c>
       <c r="B172" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18145,21 +18145,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18169,10 +18169,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493636</v>
+        <v>493628</v>
       </c>
       <c r="R172" t="n">
-        <v>6834906</v>
+        <v>6834790</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18540,7 +18540,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129460260</v>
+        <v>129459599</v>
       </c>
       <c r="B176" t="n">
         <v>79044</v>
@@ -18575,10 +18575,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493731</v>
+        <v>493726</v>
       </c>
       <c r="R176" t="n">
-        <v>6834851</v>
+        <v>6834891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,7 +18637,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129459599</v>
+        <v>129460260</v>
       </c>
       <c r="B177" t="n">
         <v>79044</v>
@@ -18672,10 +18672,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493726</v>
+        <v>493731</v>
       </c>
       <c r="R177" t="n">
-        <v>6834891</v>
+        <v>6834851</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19043,10 +19043,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129476551</v>
+        <v>129476561</v>
       </c>
       <c r="B181" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19054,21 +19054,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19078,10 +19078,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493632</v>
+        <v>493634</v>
       </c>
       <c r="R181" t="n">
-        <v>6834827</v>
+        <v>6834985</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19140,10 +19140,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129476561</v>
+        <v>129476551</v>
       </c>
       <c r="B182" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19151,21 +19151,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19175,10 +19175,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493634</v>
+        <v>493632</v>
       </c>
       <c r="R182" t="n">
-        <v>6834985</v>
+        <v>6834827</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19731,45 +19731,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129525479</v>
+        <v>129525456</v>
       </c>
       <c r="B188" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>493825</v>
+        <v>493893</v>
       </c>
       <c r="R188" t="n">
-        <v>6834594</v>
+        <v>6834612</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19816,57 +19816,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129525456</v>
+        <v>129525479</v>
       </c>
       <c r="B189" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>493893</v>
+        <v>493825</v>
       </c>
       <c r="R189" t="n">
-        <v>6834612</v>
+        <v>6834594</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19913,12 +19913,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -20331,7 +20331,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129525020</v>
+        <v>129525370</v>
       </c>
       <c r="B194" t="n">
         <v>98724</v>
@@ -20359,26 +20359,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>493860</v>
+        <v>493942</v>
       </c>
       <c r="R194" t="n">
-        <v>6834704</v>
+        <v>6834657</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20425,19 +20416,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129525370</v>
+        <v>129525020</v>
       </c>
       <c r="B195" t="n">
         <v>98724</v>
@@ -20465,17 +20456,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>493942</v>
+        <v>493860</v>
       </c>
       <c r="R195" t="n">
-        <v>6834657</v>
+        <v>6834704</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20522,57 +20522,66 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129525895</v>
+        <v>129525059</v>
       </c>
       <c r="B196" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>493792</v>
+        <v>493851</v>
       </c>
       <c r="R196" t="n">
-        <v>6834620</v>
+        <v>6834680</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20631,54 +20640,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129525059</v>
+        <v>129525895</v>
       </c>
       <c r="B197" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>493851</v>
+        <v>493792</v>
       </c>
       <c r="R197" t="n">
-        <v>6834680</v>
+        <v>6834620</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20737,54 +20737,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129525089</v>
+        <v>129525351</v>
       </c>
       <c r="B198" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>493895</v>
+        <v>493874</v>
       </c>
       <c r="R198" t="n">
-        <v>6834684</v>
+        <v>6834658</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20831,57 +20822,66 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129525351</v>
+        <v>129525089</v>
       </c>
       <c r="B199" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>493874</v>
+        <v>493895</v>
       </c>
       <c r="R199" t="n">
-        <v>6834658</v>
+        <v>6834684</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20928,12 +20928,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
@@ -21664,10 +21664,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525442</v>
+        <v>129525320</v>
       </c>
       <c r="B207" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21675,34 +21675,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493925</v>
+        <v>493859</v>
       </c>
       <c r="R207" t="n">
-        <v>6834617</v>
+        <v>6834674</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21737,6 +21737,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD207" t="b">
         <v>0</v>
       </c>
@@ -21749,12 +21754,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
@@ -21867,45 +21872,54 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129525320</v>
+        <v>129525078</v>
       </c>
       <c r="B209" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>493859</v>
+        <v>493886</v>
       </c>
       <c r="R209" t="n">
-        <v>6834674</v>
+        <v>6834673</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21940,11 +21954,6 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
@@ -21957,19 +21966,19 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129525078</v>
+        <v>129524983</v>
       </c>
       <c r="B210" t="n">
         <v>98724</v>
@@ -22013,10 +22022,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493886</v>
+        <v>493871</v>
       </c>
       <c r="R210" t="n">
-        <v>6834673</v>
+        <v>6834690</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22075,54 +22084,45 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129524983</v>
+        <v>129525442</v>
       </c>
       <c r="B211" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493871</v>
+        <v>493925</v>
       </c>
       <c r="R211" t="n">
-        <v>6834690</v>
+        <v>6834617</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22675,54 +22675,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129525489</v>
+        <v>129525382</v>
       </c>
       <c r="B217" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>493817</v>
+        <v>493822</v>
       </c>
       <c r="R217" t="n">
-        <v>6834579</v>
+        <v>6834648</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22781,45 +22772,54 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129525382</v>
+        <v>129525489</v>
       </c>
       <c r="B218" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>493822</v>
+        <v>493817</v>
       </c>
       <c r="R218" t="n">
-        <v>6834648</v>
+        <v>6834579</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22878,54 +22878,45 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129525418</v>
+        <v>129525130</v>
       </c>
       <c r="B219" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>493930</v>
+        <v>493858</v>
       </c>
       <c r="R219" t="n">
-        <v>6834628</v>
+        <v>6834661</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22972,19 +22963,19 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129525528</v>
+        <v>129525418</v>
       </c>
       <c r="B220" t="n">
         <v>98724</v>
@@ -23012,17 +23003,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>493826</v>
+        <v>493930</v>
       </c>
       <c r="R220" t="n">
-        <v>6834572</v>
+        <v>6834628</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23069,44 +23069,44 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129525130</v>
+        <v>129525528</v>
       </c>
       <c r="B221" t="n">
-        <v>92832</v>
+        <v>98724</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23116,10 +23116,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>493858</v>
+        <v>493826</v>
       </c>
       <c r="R221" t="n">
-        <v>6834661</v>
+        <v>6834572</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23381,7 +23381,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129525601</v>
+        <v>129525445</v>
       </c>
       <c r="B224" t="n">
         <v>79044</v>
@@ -23416,10 +23416,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>493922</v>
+        <v>493900</v>
       </c>
       <c r="R224" t="n">
-        <v>6834518</v>
+        <v>6834610</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23478,7 +23478,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129525445</v>
+        <v>129525601</v>
       </c>
       <c r="B225" t="n">
         <v>79044</v>
@@ -23513,10 +23513,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>493900</v>
+        <v>493922</v>
       </c>
       <c r="R225" t="n">
-        <v>6834610</v>
+        <v>6834518</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -9061,45 +9061,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129476585</v>
+        <v>129476554</v>
       </c>
       <c r="B81" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493700</v>
+        <v>493648</v>
       </c>
       <c r="R81" t="n">
-        <v>6834837</v>
+        <v>6834929</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9140,6 +9149,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9158,54 +9168,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129476554</v>
+        <v>129476585</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493648</v>
+        <v>493700</v>
       </c>
       <c r="R82" t="n">
-        <v>6834929</v>
+        <v>6834837</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9246,7 +9247,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476544</v>
+        <v>129476569</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10777,42 +10777,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493634</v>
+        <v>493626</v>
       </c>
       <c r="R98" t="n">
-        <v>6834983</v>
+        <v>6834837</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11170,45 +11162,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476569</v>
+        <v>129455942</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493626</v>
+        <v>493802</v>
       </c>
       <c r="R102" t="n">
-        <v>6834837</v>
+        <v>6834925</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11255,57 +11256,57 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476537</v>
+        <v>129458908</v>
       </c>
       <c r="B103" t="n">
-        <v>79634</v>
+        <v>98724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493659</v>
+        <v>493702</v>
       </c>
       <c r="R103" t="n">
-        <v>6834945</v>
+        <v>6834942</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11352,19 +11353,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129455942</v>
+        <v>129458098</v>
       </c>
       <c r="B104" t="n">
         <v>98724</v>
@@ -11394,7 +11395,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11408,10 +11409,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493802</v>
+        <v>493682</v>
       </c>
       <c r="R104" t="n">
-        <v>6834925</v>
+        <v>6834975</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11470,45 +11471,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129458908</v>
+        <v>129476544</v>
       </c>
       <c r="B105" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493702</v>
+        <v>493634</v>
       </c>
       <c r="R105" t="n">
-        <v>6834942</v>
+        <v>6834983</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,66 +11564,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129458098</v>
+        <v>129476537</v>
       </c>
       <c r="B106" t="n">
-        <v>98724</v>
+        <v>79634</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493682</v>
+        <v>493659</v>
       </c>
       <c r="R106" t="n">
-        <v>6834975</v>
+        <v>6834945</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11661,57 +11661,66 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129458915</v>
+        <v>129456312</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493698</v>
+        <v>493787</v>
       </c>
       <c r="R107" t="n">
-        <v>6834942</v>
+        <v>6834957</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11770,54 +11779,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129456312</v>
+        <v>129458915</v>
       </c>
       <c r="B108" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493787</v>
+        <v>493698</v>
       </c>
       <c r="R108" t="n">
-        <v>6834957</v>
+        <v>6834942</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11973,7 +11973,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129476568</v>
+        <v>129461581</v>
       </c>
       <c r="B110" t="n">
         <v>79044</v>
@@ -12004,14 +12004,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>493619</v>
+        <v>493634</v>
       </c>
       <c r="R110" t="n">
-        <v>6834841</v>
+        <v>6834920</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12058,19 +12058,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129461581</v>
+        <v>129476568</v>
       </c>
       <c r="B111" t="n">
         <v>79044</v>
@@ -12101,14 +12101,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493634</v>
+        <v>493619</v>
       </c>
       <c r="R111" t="n">
-        <v>6834920</v>
+        <v>6834841</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12155,12 +12155,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13067,45 +13067,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129476590</v>
+        <v>129461070</v>
       </c>
       <c r="B121" t="n">
-        <v>92832</v>
+        <v>98724</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493628</v>
+        <v>493629</v>
       </c>
       <c r="R121" t="n">
-        <v>6834891</v>
+        <v>6834827</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13152,57 +13152,57 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476541</v>
+        <v>129457707</v>
       </c>
       <c r="B122" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493780</v>
+        <v>493815</v>
       </c>
       <c r="R122" t="n">
-        <v>6834984</v>
+        <v>6834917</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13249,64 +13249,66 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129476559</v>
+        <v>129456013</v>
       </c>
       <c r="B123" t="n">
-        <v>78801</v>
+        <v>98724</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493626</v>
+        <v>493806</v>
       </c>
       <c r="R123" t="n">
-        <v>6834843</v>
+        <v>6834935</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13347,26 +13349,25 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129461070</v>
+        <v>129456404</v>
       </c>
       <c r="B124" t="n">
         <v>98724</v>
@@ -13394,17 +13395,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493629</v>
+        <v>493780</v>
       </c>
       <c r="R124" t="n">
-        <v>6834827</v>
+        <v>6834929</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13463,7 +13473,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129457707</v>
+        <v>129456103</v>
       </c>
       <c r="B125" t="n">
         <v>98724</v>
@@ -13491,17 +13501,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493815</v>
+        <v>493817</v>
       </c>
       <c r="R125" t="n">
-        <v>6834917</v>
+        <v>6834939</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13560,54 +13579,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129456013</v>
+        <v>129476590</v>
       </c>
       <c r="B126" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493806</v>
+        <v>493628</v>
       </c>
       <c r="R126" t="n">
-        <v>6834935</v>
+        <v>6834891</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13654,66 +13664,57 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129456404</v>
+        <v>129476541</v>
       </c>
       <c r="B127" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
         <v>493780</v>
       </c>
       <c r="R127" t="n">
-        <v>6834929</v>
+        <v>6834984</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13760,66 +13761,64 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129456103</v>
+        <v>129476559</v>
       </c>
       <c r="B128" t="n">
-        <v>98724</v>
+        <v>78801</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493817</v>
+        <v>493626</v>
       </c>
       <c r="R128" t="n">
-        <v>6834939</v>
+        <v>6834843</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13860,28 +13859,29 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129476530</v>
+        <v>129476550</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,21 +13889,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493705</v>
+        <v>493625</v>
       </c>
       <c r="R129" t="n">
-        <v>6834890</v>
+        <v>6834820</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13975,45 +13975,54 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129455888</v>
+        <v>129456470</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493811</v>
+        <v>493783</v>
       </c>
       <c r="R130" t="n">
-        <v>6834925</v>
+        <v>6834931</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14072,32 +14081,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129458645</v>
+        <v>129458700</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14107,13 +14116,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493662</v>
+        <v>493675</v>
       </c>
       <c r="R131" t="n">
-        <v>6834952</v>
+        <v>6834963</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14169,54 +14178,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129456470</v>
+        <v>129476530</v>
       </c>
       <c r="B132" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493783</v>
+        <v>493705</v>
       </c>
       <c r="R132" t="n">
-        <v>6834931</v>
+        <v>6834890</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14263,44 +14263,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129458700</v>
+        <v>129455888</v>
       </c>
       <c r="B133" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493675</v>
+        <v>493811</v>
       </c>
       <c r="R133" t="n">
-        <v>6834963</v>
+        <v>6834925</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14372,10 +14372,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129476550</v>
+        <v>129458645</v>
       </c>
       <c r="B134" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14383,34 +14383,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493625</v>
+        <v>493662</v>
       </c>
       <c r="R134" t="n">
-        <v>6834820</v>
+        <v>6834952</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14457,57 +14457,66 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476588</v>
+        <v>129476553</v>
       </c>
       <c r="B135" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493619</v>
+        <v>493591</v>
       </c>
       <c r="R135" t="n">
-        <v>6834998</v>
+        <v>6835008</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14548,6 +14557,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14566,10 +14576,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129459901</v>
+        <v>129476552</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,34 +14587,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493734</v>
+        <v>493629</v>
       </c>
       <c r="R136" t="n">
-        <v>6834875</v>
+        <v>6834831</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14651,22 +14661,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476548</v>
+        <v>129459901</v>
       </c>
       <c r="B137" t="n">
-        <v>91603</v>
+        <v>79044</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14674,34 +14684,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493687</v>
+        <v>493734</v>
       </c>
       <c r="R137" t="n">
-        <v>6834930</v>
+        <v>6834875</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14748,22 +14758,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129476573</v>
+        <v>129476548</v>
       </c>
       <c r="B138" t="n">
-        <v>79044</v>
+        <v>91603</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14771,21 +14781,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14795,10 +14805,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493661</v>
+        <v>493687</v>
       </c>
       <c r="R138" t="n">
-        <v>6834848</v>
+        <v>6834930</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14857,10 +14867,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476580</v>
+        <v>129476588</v>
       </c>
       <c r="B139" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14868,21 +14878,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14892,10 +14902,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493675</v>
+        <v>493619</v>
       </c>
       <c r="R139" t="n">
-        <v>6834937</v>
+        <v>6834998</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14954,54 +14964,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129476553</v>
+        <v>129476573</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493591</v>
+        <v>493661</v>
       </c>
       <c r="R140" t="n">
-        <v>6835008</v>
+        <v>6834848</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15042,7 +15043,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15061,10 +15061,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476552</v>
+        <v>129476580</v>
       </c>
       <c r="B141" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15072,21 +15072,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15096,10 +15096,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493629</v>
+        <v>493675</v>
       </c>
       <c r="R141" t="n">
-        <v>6834831</v>
+        <v>6834937</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15255,10 +15255,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129476540</v>
+        <v>129476543</v>
       </c>
       <c r="B143" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15266,34 +15266,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493723</v>
+        <v>493676</v>
       </c>
       <c r="R143" t="n">
-        <v>6834965</v>
+        <v>6834800</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15352,10 +15360,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129476543</v>
+        <v>129458803</v>
       </c>
       <c r="B144" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15363,42 +15371,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493676</v>
+        <v>493683</v>
       </c>
       <c r="R144" t="n">
-        <v>6834800</v>
+        <v>6834951</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15445,57 +15445,66 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129458803</v>
+        <v>129457830</v>
       </c>
       <c r="B145" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493683</v>
+        <v>493676</v>
       </c>
       <c r="R145" t="n">
-        <v>6834951</v>
+        <v>6835001</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15554,7 +15563,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129457830</v>
+        <v>129458085</v>
       </c>
       <c r="B146" t="n">
         <v>98724</v>
@@ -15584,7 +15593,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -15598,10 +15607,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493676</v>
+        <v>493690</v>
       </c>
       <c r="R146" t="n">
-        <v>6835001</v>
+        <v>6834972</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15660,7 +15669,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129458085</v>
+        <v>129459852</v>
       </c>
       <c r="B147" t="n">
         <v>98724</v>
@@ -15688,26 +15697,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493690</v>
+        <v>493730</v>
       </c>
       <c r="R147" t="n">
-        <v>6834972</v>
+        <v>6834877</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15766,7 +15766,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129459852</v>
+        <v>129460207</v>
       </c>
       <c r="B148" t="n">
         <v>98724</v>
@@ -15801,10 +15801,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493730</v>
+        <v>493738</v>
       </c>
       <c r="R148" t="n">
-        <v>6834877</v>
+        <v>6834861</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15863,45 +15863,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129460207</v>
+        <v>129476540</v>
       </c>
       <c r="B149" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493738</v>
+        <v>493723</v>
       </c>
       <c r="R149" t="n">
-        <v>6834861</v>
+        <v>6834965</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,12 +15948,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16251,32 +16251,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129460467</v>
+        <v>129460288</v>
       </c>
       <c r="B153" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16286,10 +16286,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493728</v>
+        <v>493733</v>
       </c>
       <c r="R153" t="n">
-        <v>6834842</v>
+        <v>6834848</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16348,45 +16348,54 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129476567</v>
+        <v>129458972</v>
       </c>
       <c r="B154" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>493634</v>
+        <v>493700</v>
       </c>
       <c r="R154" t="n">
-        <v>6834889</v>
+        <v>6834942</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16433,19 +16442,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129476576</v>
+        <v>129460467</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -16476,14 +16485,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493725</v>
+        <v>493728</v>
       </c>
       <c r="R155" t="n">
-        <v>6834888</v>
+        <v>6834842</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16530,57 +16539,57 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129460288</v>
+        <v>129476567</v>
       </c>
       <c r="B156" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493733</v>
+        <v>493634</v>
       </c>
       <c r="R156" t="n">
-        <v>6834848</v>
+        <v>6834889</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16627,66 +16636,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129458972</v>
+        <v>129476576</v>
       </c>
       <c r="B157" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493700</v>
+        <v>493725</v>
       </c>
       <c r="R157" t="n">
-        <v>6834942</v>
+        <v>6834888</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16733,12 +16733,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -17327,45 +17327,54 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129476549</v>
+        <v>129459449</v>
       </c>
       <c r="B164" t="n">
-        <v>91603</v>
+        <v>98724</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493677</v>
+        <v>493720</v>
       </c>
       <c r="R164" t="n">
-        <v>6835005</v>
+        <v>6834910</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17412,19 +17421,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129459449</v>
+        <v>129459953</v>
       </c>
       <c r="B165" t="n">
         <v>98724</v>
@@ -17454,7 +17463,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -17468,10 +17477,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493720</v>
+        <v>493729</v>
       </c>
       <c r="R165" t="n">
-        <v>6834910</v>
+        <v>6834873</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17530,7 +17539,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129459953</v>
+        <v>129476562</v>
       </c>
       <c r="B166" t="n">
         <v>98724</v>
@@ -17560,7 +17569,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -17568,16 +17577,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493729</v>
+        <v>493676</v>
       </c>
       <c r="R166" t="n">
-        <v>6834873</v>
+        <v>6834974</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17618,75 +17630,64 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129476562</v>
+        <v>129476549</v>
       </c>
       <c r="B167" t="n">
-        <v>98724</v>
+        <v>91603</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493676</v>
+        <v>493677</v>
       </c>
       <c r="R167" t="n">
-        <v>6834974</v>
+        <v>6835005</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17727,7 +17728,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -18540,45 +18540,54 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129459599</v>
+        <v>129456055</v>
       </c>
       <c r="B176" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493726</v>
+        <v>493817</v>
       </c>
       <c r="R176" t="n">
-        <v>6834891</v>
+        <v>6834930</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,32 +18646,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129460260</v>
+        <v>129459676</v>
       </c>
       <c r="B177" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18672,10 +18681,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493731</v>
+        <v>493727</v>
       </c>
       <c r="R177" t="n">
-        <v>6834851</v>
+        <v>6834879</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18734,7 +18743,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129456055</v>
+        <v>129458467</v>
       </c>
       <c r="B178" t="n">
         <v>98724</v>
@@ -18764,7 +18773,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -18778,10 +18787,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493817</v>
+        <v>493646</v>
       </c>
       <c r="R178" t="n">
-        <v>6834930</v>
+        <v>6835015</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18840,32 +18849,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129459676</v>
+        <v>129459599</v>
       </c>
       <c r="B179" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18875,10 +18884,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493727</v>
+        <v>493726</v>
       </c>
       <c r="R179" t="n">
-        <v>6834879</v>
+        <v>6834891</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18937,54 +18946,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129458467</v>
+        <v>129460260</v>
       </c>
       <c r="B180" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493646</v>
+        <v>493731</v>
       </c>
       <c r="R180" t="n">
-        <v>6835015</v>
+        <v>6834851</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19431,45 +19431,54 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129525028</v>
+        <v>129525359</v>
       </c>
       <c r="B185" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>493857</v>
+        <v>493934</v>
       </c>
       <c r="R185" t="n">
-        <v>6834694</v>
+        <v>6834670</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19516,66 +19525,57 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129525359</v>
+        <v>129525028</v>
       </c>
       <c r="B186" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>493934</v>
+        <v>493857</v>
       </c>
       <c r="R186" t="n">
-        <v>6834670</v>
+        <v>6834694</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19622,12 +19622,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
@@ -19925,7 +19925,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129525603</v>
+        <v>129525395</v>
       </c>
       <c r="B190" t="n">
         <v>98724</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -19965,14 +19965,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>493825</v>
+        <v>493923</v>
       </c>
       <c r="R190" t="n">
-        <v>6834572</v>
+        <v>6834647</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20019,19 +20019,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129525395</v>
+        <v>129525603</v>
       </c>
       <c r="B191" t="n">
         <v>98724</v>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -20071,14 +20071,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>493923</v>
+        <v>493825</v>
       </c>
       <c r="R191" t="n">
-        <v>6834647</v>
+        <v>6834572</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20125,12 +20125,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -21664,45 +21664,54 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525320</v>
+        <v>129525477</v>
       </c>
       <c r="B207" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493859</v>
+        <v>493823</v>
       </c>
       <c r="R207" t="n">
-        <v>6834674</v>
+        <v>6834595</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21735,11 +21744,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21766,7 +21770,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129525477</v>
+        <v>129525078</v>
       </c>
       <c r="B208" t="n">
         <v>98724</v>
@@ -21796,7 +21800,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -21806,14 +21810,14 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493823</v>
+        <v>493886</v>
       </c>
       <c r="R208" t="n">
-        <v>6834595</v>
+        <v>6834673</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21860,19 +21864,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129525078</v>
+        <v>129524983</v>
       </c>
       <c r="B209" t="n">
         <v>98724</v>
@@ -21916,10 +21920,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>493886</v>
+        <v>493871</v>
       </c>
       <c r="R209" t="n">
-        <v>6834673</v>
+        <v>6834690</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21978,54 +21982,45 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129524983</v>
+        <v>129525442</v>
       </c>
       <c r="B210" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493871</v>
+        <v>493925</v>
       </c>
       <c r="R210" t="n">
-        <v>6834690</v>
+        <v>6834617</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22084,10 +22079,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525442</v>
+        <v>129525320</v>
       </c>
       <c r="B211" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22095,34 +22090,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493925</v>
+        <v>493859</v>
       </c>
       <c r="R211" t="n">
-        <v>6834617</v>
+        <v>6834674</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22157,6 +22152,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
@@ -22169,66 +22169,57 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525001</v>
+        <v>129525462</v>
       </c>
       <c r="B212" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493870</v>
+        <v>493832</v>
       </c>
       <c r="R212" t="n">
-        <v>6834690</v>
+        <v>6834595</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22287,32 +22278,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525462</v>
+        <v>129525429</v>
       </c>
       <c r="B213" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22322,10 +22313,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>493832</v>
+        <v>493788</v>
       </c>
       <c r="R213" t="n">
-        <v>6834595</v>
+        <v>6834656</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22384,45 +22375,54 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525429</v>
+        <v>129525001</v>
       </c>
       <c r="B214" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>493788</v>
+        <v>493870</v>
       </c>
       <c r="R214" t="n">
-        <v>6834656</v>
+        <v>6834690</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23178,45 +23178,54 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129525680</v>
+        <v>129525347</v>
       </c>
       <c r="B222" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>493840</v>
+        <v>493915</v>
       </c>
       <c r="R222" t="n">
-        <v>6834519</v>
+        <v>6834671</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23263,66 +23272,57 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129525347</v>
+        <v>129525680</v>
       </c>
       <c r="B223" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>493915</v>
+        <v>493840</v>
       </c>
       <c r="R223" t="n">
-        <v>6834671</v>
+        <v>6834519</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23369,12 +23369,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,45 +8179,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129460134</v>
+        <v>129476586</v>
       </c>
       <c r="B72" t="n">
-        <v>98724</v>
+        <v>78710</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493738</v>
+        <v>493684</v>
       </c>
       <c r="R72" t="n">
-        <v>6834870</v>
+        <v>6834869</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8264,22 +8264,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129460004</v>
+        <v>129460134</v>
       </c>
       <c r="B73" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493728</v>
+        <v>493738</v>
       </c>
       <c r="R73" t="n">
-        <v>6834868</v>
+        <v>6834870</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8373,10 +8373,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460228</v>
+        <v>129460004</v>
       </c>
       <c r="B74" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8401,26 +8401,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493736</v>
+        <v>493728</v>
       </c>
       <c r="R74" t="n">
-        <v>6834865</v>
+        <v>6834868</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8479,10 +8470,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476586</v>
+        <v>129476572</v>
       </c>
       <c r="B75" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8490,21 +8481,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8514,10 +8505,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493684</v>
+        <v>493675</v>
       </c>
       <c r="R75" t="n">
-        <v>6834869</v>
+        <v>6834825</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,10 +8567,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129476572</v>
+        <v>129476556</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8587,21 +8578,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8611,10 +8602,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493675</v>
+        <v>493810</v>
       </c>
       <c r="R76" t="n">
-        <v>6834825</v>
+        <v>6834883</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8673,45 +8664,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129476556</v>
+        <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493810</v>
+        <v>493736</v>
       </c>
       <c r="R77" t="n">
-        <v>6834883</v>
+        <v>6834865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,22 +8758,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129460036</v>
+        <v>129476585</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8781,34 +8781,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493728</v>
+        <v>493700</v>
       </c>
       <c r="R78" t="n">
-        <v>6834868</v>
+        <v>6834837</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8855,19 +8855,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129461154</v>
+        <v>129460662</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493629</v>
+        <v>493658</v>
       </c>
       <c r="R79" t="n">
-        <v>6834827</v>
+        <v>6834840</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129460662</v>
+        <v>129460036</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493658</v>
+        <v>493728</v>
       </c>
       <c r="R80" t="n">
-        <v>6834840</v>
+        <v>6834868</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9168,10 +9168,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129476585</v>
+        <v>129461154</v>
       </c>
       <c r="B82" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9179,34 +9179,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493700</v>
+        <v>493629</v>
       </c>
       <c r="R82" t="n">
-        <v>6834837</v>
+        <v>6834827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9253,12 +9253,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9268,7 +9268,7 @@
         <v>129456176</v>
       </c>
       <c r="B83" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>129457973</v>
       </c>
       <c r="B84" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9477,10 +9477,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129476589</v>
+        <v>129476547</v>
       </c>
       <c r="B85" t="n">
-        <v>92832</v>
+        <v>79068</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9488,21 +9488,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9512,10 +9512,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493641</v>
+        <v>493722</v>
       </c>
       <c r="R85" t="n">
-        <v>6834918</v>
+        <v>6834900</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9574,45 +9574,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129457992</v>
+        <v>129476589</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493684</v>
+        <v>493641</v>
       </c>
       <c r="R86" t="n">
-        <v>6834988</v>
+        <v>6834918</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9659,57 +9659,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129476547</v>
+        <v>129457992</v>
       </c>
       <c r="B87" t="n">
-        <v>79068</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493722</v>
+        <v>493684</v>
       </c>
       <c r="R87" t="n">
-        <v>6834900</v>
+        <v>6834988</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9756,12 +9756,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9868,7 +9868,7 @@
         <v>129457913</v>
       </c>
       <c r="B89" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>129460883</v>
       </c>
       <c r="B90" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>129457745</v>
       </c>
       <c r="B91" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476566</v>
+        <v>129476574</v>
       </c>
       <c r="B93" t="n">
         <v>79044</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493646</v>
+        <v>493702</v>
       </c>
       <c r="R93" t="n">
-        <v>6834937</v>
+        <v>6834858</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476574</v>
+        <v>129476566</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493702</v>
+        <v>493646</v>
       </c>
       <c r="R94" t="n">
-        <v>6834858</v>
+        <v>6834937</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10465,54 +10465,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476555</v>
+        <v>129476583</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493666</v>
+        <v>493664</v>
       </c>
       <c r="R95" t="n">
-        <v>6834982</v>
+        <v>6834992</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10553,7 +10544,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10572,45 +10562,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476583</v>
+        <v>129476555</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493664</v>
+        <v>493666</v>
       </c>
       <c r="R96" t="n">
-        <v>6834992</v>
+        <v>6834982</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10651,6 +10650,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10766,7 +10766,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476569</v>
+        <v>129455841</v>
       </c>
       <c r="B98" t="n">
         <v>79044</v>
@@ -10797,14 +10797,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493626</v>
+        <v>493803</v>
       </c>
       <c r="R98" t="n">
-        <v>6834837</v>
+        <v>6834901</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10851,22 +10851,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129476560</v>
+        <v>129476578</v>
       </c>
       <c r="B99" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10874,41 +10874,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493684</v>
+        <v>493718</v>
       </c>
       <c r="R99" t="n">
-        <v>6834860</v>
+        <v>6834894</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10949,7 +10942,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10968,10 +10960,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476578</v>
+        <v>129476544</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10979,34 +10971,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493718</v>
+        <v>493634</v>
       </c>
       <c r="R100" t="n">
-        <v>6834894</v>
+        <v>6834983</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11065,10 +11065,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129455841</v>
+        <v>129476560</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11076,34 +11076,41 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493803</v>
+        <v>493684</v>
       </c>
       <c r="R101" t="n">
-        <v>6834901</v>
+        <v>6834860</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11144,72 +11151,64 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129455942</v>
+        <v>129476569</v>
       </c>
       <c r="B102" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493802</v>
+        <v>493626</v>
       </c>
       <c r="R102" t="n">
-        <v>6834925</v>
+        <v>6834837</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11256,12 +11255,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11271,7 +11270,7 @@
         <v>129458908</v>
       </c>
       <c r="B103" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11368,7 +11367,7 @@
         <v>129458098</v>
       </c>
       <c r="B104" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11471,53 +11470,54 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129476544</v>
+        <v>129455942</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493634</v>
+        <v>493802</v>
       </c>
       <c r="R105" t="n">
-        <v>6834983</v>
+        <v>6834925</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11564,12 +11564,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11673,54 +11673,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129456312</v>
+        <v>129458915</v>
       </c>
       <c r="B107" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493787</v>
+        <v>493698</v>
       </c>
       <c r="R107" t="n">
-        <v>6834957</v>
+        <v>6834942</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11779,7 +11770,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129458915</v>
+        <v>129476577</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -11810,14 +11801,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493698</v>
+        <v>493707</v>
       </c>
       <c r="R108" t="n">
-        <v>6834942</v>
+        <v>6834895</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11864,57 +11855,66 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129476577</v>
+        <v>129456312</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493707</v>
+        <v>493787</v>
       </c>
       <c r="R109" t="n">
-        <v>6834895</v>
+        <v>6834957</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11961,12 +11961,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12167,45 +12167,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129476538</v>
+        <v>129456198</v>
       </c>
       <c r="B112" t="n">
-        <v>79634</v>
+        <v>98727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493627</v>
+        <v>493810</v>
       </c>
       <c r="R112" t="n">
-        <v>6834986</v>
+        <v>6834955</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12252,22 +12261,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129456198</v>
+        <v>129458436</v>
       </c>
       <c r="B113" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12292,26 +12301,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493810</v>
+        <v>493653</v>
       </c>
       <c r="R113" t="n">
-        <v>6834955</v>
+        <v>6835020</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12370,45 +12370,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129458436</v>
+        <v>129476538</v>
       </c>
       <c r="B114" t="n">
-        <v>98724</v>
+        <v>79634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493653</v>
+        <v>493627</v>
       </c>
       <c r="R114" t="n">
-        <v>6835020</v>
+        <v>6834986</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,22 +12455,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129460271</v>
+        <v>129476558</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12478,34 +12478,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493731</v>
+        <v>493629</v>
       </c>
       <c r="R115" t="n">
-        <v>6834853</v>
+        <v>6834823</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12552,22 +12552,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476558</v>
+        <v>129476584</v>
       </c>
       <c r="B116" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12575,21 +12575,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12599,10 +12599,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493629</v>
+        <v>493670</v>
       </c>
       <c r="R116" t="n">
-        <v>6834823</v>
+        <v>6834995</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12661,7 +12661,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129476584</v>
+        <v>129460271</v>
       </c>
       <c r="B117" t="n">
         <v>79044</v>
@@ -12692,14 +12692,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493670</v>
+        <v>493731</v>
       </c>
       <c r="R117" t="n">
-        <v>6834995</v>
+        <v>6834853</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12746,12 +12746,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12761,7 +12761,7 @@
         <v>129459508</v>
       </c>
       <c r="B118" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12855,10 +12855,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129459731</v>
+        <v>129459774</v>
       </c>
       <c r="B119" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12899,10 +12899,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>493725</v>
+        <v>493729</v>
       </c>
       <c r="R119" t="n">
-        <v>6834883</v>
+        <v>6834877</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12961,10 +12961,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129459774</v>
+        <v>129459731</v>
       </c>
       <c r="B120" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>493729</v>
+        <v>493725</v>
       </c>
       <c r="R120" t="n">
-        <v>6834877</v>
+        <v>6834883</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13067,10 +13067,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129461070</v>
+        <v>129456013</v>
       </c>
       <c r="B121" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13095,17 +13095,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493629</v>
+        <v>493806</v>
       </c>
       <c r="R121" t="n">
-        <v>6834827</v>
+        <v>6834935</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13164,10 +13173,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129457707</v>
+        <v>129461070</v>
       </c>
       <c r="B122" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13199,10 +13208,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493815</v>
+        <v>493629</v>
       </c>
       <c r="R122" t="n">
-        <v>6834917</v>
+        <v>6834827</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13261,10 +13270,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129456013</v>
+        <v>129457707</v>
       </c>
       <c r="B123" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13289,26 +13298,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493806</v>
+        <v>493815</v>
       </c>
       <c r="R123" t="n">
-        <v>6834935</v>
+        <v>6834917</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13370,7 +13370,7 @@
         <v>129456404</v>
       </c>
       <c r="B124" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>129456103</v>
       </c>
       <c r="B125" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13579,32 +13579,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129476590</v>
+        <v>129476541</v>
       </c>
       <c r="B126" t="n">
-        <v>92832</v>
+        <v>91553</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13614,10 +13614,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493628</v>
+        <v>493780</v>
       </c>
       <c r="R126" t="n">
-        <v>6834891</v>
+        <v>6834984</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13676,10 +13676,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129476541</v>
+        <v>129476559</v>
       </c>
       <c r="B127" t="n">
-        <v>91550</v>
+        <v>78801</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13687,34 +13687,41 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493780</v>
+        <v>493626</v>
       </c>
       <c r="R127" t="n">
-        <v>6834984</v>
+        <v>6834843</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13755,6 +13762,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13773,52 +13781,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129476559</v>
+        <v>129476590</v>
       </c>
       <c r="B128" t="n">
-        <v>78801</v>
+        <v>92835</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493626</v>
+        <v>493628</v>
       </c>
       <c r="R128" t="n">
-        <v>6834843</v>
+        <v>6834891</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13859,7 +13860,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129476550</v>
+        <v>129476530</v>
       </c>
       <c r="B129" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,21 +13889,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493625</v>
+        <v>493705</v>
       </c>
       <c r="R129" t="n">
-        <v>6834820</v>
+        <v>6834890</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13975,54 +13975,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129456470</v>
+        <v>129455888</v>
       </c>
       <c r="B130" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493783</v>
+        <v>493811</v>
       </c>
       <c r="R130" t="n">
-        <v>6834931</v>
+        <v>6834925</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14081,32 +14072,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129458700</v>
+        <v>129458645</v>
       </c>
       <c r="B131" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14116,13 +14107,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493675</v>
+        <v>493662</v>
       </c>
       <c r="R131" t="n">
-        <v>6834963</v>
+        <v>6834952</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14178,45 +14169,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129476530</v>
+        <v>129456470</v>
       </c>
       <c r="B132" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493705</v>
+        <v>493783</v>
       </c>
       <c r="R132" t="n">
-        <v>6834890</v>
+        <v>6834931</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14263,44 +14263,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129455888</v>
+        <v>129458700</v>
       </c>
       <c r="B133" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493811</v>
+        <v>493675</v>
       </c>
       <c r="R133" t="n">
-        <v>6834925</v>
+        <v>6834963</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14372,10 +14372,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129458645</v>
+        <v>129476550</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14383,34 +14383,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493662</v>
+        <v>493625</v>
       </c>
       <c r="R134" t="n">
-        <v>6834952</v>
+        <v>6834820</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14457,12 +14457,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14576,10 +14576,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476552</v>
+        <v>129476588</v>
       </c>
       <c r="B136" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493629</v>
+        <v>493619</v>
       </c>
       <c r="R136" t="n">
-        <v>6834831</v>
+        <v>6834998</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14673,7 +14673,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129459901</v>
+        <v>129476580</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -14704,14 +14704,14 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493734</v>
+        <v>493675</v>
       </c>
       <c r="R137" t="n">
-        <v>6834875</v>
+        <v>6834937</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14758,22 +14758,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129476548</v>
+        <v>129476573</v>
       </c>
       <c r="B138" t="n">
-        <v>91603</v>
+        <v>79044</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14781,21 +14781,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14805,10 +14805,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493687</v>
+        <v>493661</v>
       </c>
       <c r="R138" t="n">
-        <v>6834930</v>
+        <v>6834848</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14867,10 +14867,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476588</v>
+        <v>129459901</v>
       </c>
       <c r="B139" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14878,34 +14878,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493619</v>
+        <v>493734</v>
       </c>
       <c r="R139" t="n">
-        <v>6834998</v>
+        <v>6834875</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14952,57 +14952,57 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129476573</v>
+        <v>129458414</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493661</v>
+        <v>493670</v>
       </c>
       <c r="R140" t="n">
-        <v>6834848</v>
+        <v>6834981</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,22 +15049,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476580</v>
+        <v>129476552</v>
       </c>
       <c r="B141" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15072,21 +15072,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15096,10 +15096,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493675</v>
+        <v>493629</v>
       </c>
       <c r="R141" t="n">
-        <v>6834937</v>
+        <v>6834831</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15158,45 +15158,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129458414</v>
+        <v>129476548</v>
       </c>
       <c r="B142" t="n">
-        <v>98724</v>
+        <v>91606</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493670</v>
+        <v>493687</v>
       </c>
       <c r="R142" t="n">
-        <v>6834981</v>
+        <v>6834930</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15243,22 +15243,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129476543</v>
+        <v>129476540</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15266,42 +15266,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493676</v>
+        <v>493723</v>
       </c>
       <c r="R143" t="n">
-        <v>6834800</v>
+        <v>6834965</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15460,7 +15452,7 @@
         <v>129457830</v>
       </c>
       <c r="B145" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15563,10 +15555,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129458085</v>
+        <v>129459852</v>
       </c>
       <c r="B146" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15591,26 +15583,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493690</v>
+        <v>493730</v>
       </c>
       <c r="R146" t="n">
-        <v>6834972</v>
+        <v>6834877</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15669,45 +15652,53 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129459852</v>
+        <v>129476543</v>
       </c>
       <c r="B147" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493730</v>
+        <v>493676</v>
       </c>
       <c r="R147" t="n">
-        <v>6834877</v>
+        <v>6834800</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15754,22 +15745,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129460207</v>
+        <v>129458085</v>
       </c>
       <c r="B148" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15794,17 +15785,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493738</v>
+        <v>493690</v>
       </c>
       <c r="R148" t="n">
-        <v>6834861</v>
+        <v>6834972</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15863,45 +15863,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129476540</v>
+        <v>129460207</v>
       </c>
       <c r="B149" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493723</v>
+        <v>493738</v>
       </c>
       <c r="R149" t="n">
-        <v>6834965</v>
+        <v>6834861</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,22 +15948,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476535</v>
+        <v>129476539</v>
       </c>
       <c r="B150" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15971,21 +15971,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493703</v>
+        <v>493652</v>
       </c>
       <c r="R150" t="n">
-        <v>6834865</v>
+        <v>6834985</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16057,10 +16057,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476539</v>
+        <v>129476535</v>
       </c>
       <c r="B151" t="n">
-        <v>90582</v>
+        <v>79663</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16068,21 +16068,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493652</v>
+        <v>493703</v>
       </c>
       <c r="R151" t="n">
-        <v>6834985</v>
+        <v>6834865</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16157,7 +16157,7 @@
         <v>129460421</v>
       </c>
       <c r="B152" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16251,45 +16251,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129460288</v>
+        <v>129476576</v>
       </c>
       <c r="B153" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493733</v>
+        <v>493725</v>
       </c>
       <c r="R153" t="n">
-        <v>6834848</v>
+        <v>6834888</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16336,66 +16336,57 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129458972</v>
+        <v>129460467</v>
       </c>
       <c r="B154" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>493700</v>
+        <v>493728</v>
       </c>
       <c r="R154" t="n">
-        <v>6834942</v>
+        <v>6834842</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16454,7 +16445,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129460467</v>
+        <v>129476567</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -16485,14 +16476,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493728</v>
+        <v>493634</v>
       </c>
       <c r="R155" t="n">
-        <v>6834842</v>
+        <v>6834889</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16539,57 +16530,57 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129476567</v>
+        <v>129460288</v>
       </c>
       <c r="B156" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493634</v>
+        <v>493733</v>
       </c>
       <c r="R156" t="n">
-        <v>6834889</v>
+        <v>6834848</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16636,57 +16627,66 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129476576</v>
+        <v>129458972</v>
       </c>
       <c r="B157" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493725</v>
+        <v>493700</v>
       </c>
       <c r="R157" t="n">
-        <v>6834888</v>
+        <v>6834942</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16733,12 +16733,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16748,7 +16748,7 @@
         <v>129476546</v>
       </c>
       <c r="B158" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129459208</v>
+        <v>129476549</v>
       </c>
       <c r="B159" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16853,34 +16853,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493698</v>
+        <v>493677</v>
       </c>
       <c r="R159" t="n">
-        <v>6834943</v>
+        <v>6835005</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16927,12 +16927,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -17133,7 +17133,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129458226</v>
+        <v>129457857</v>
       </c>
       <c r="B162" t="n">
         <v>79044</v>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493670</v>
+        <v>493676</v>
       </c>
       <c r="R162" t="n">
-        <v>6834981</v>
+        <v>6835001</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17230,7 +17230,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129457857</v>
+        <v>129459208</v>
       </c>
       <c r="B163" t="n">
         <v>79044</v>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493676</v>
+        <v>493698</v>
       </c>
       <c r="R163" t="n">
-        <v>6835001</v>
+        <v>6834943</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17327,54 +17327,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129459449</v>
+        <v>129458226</v>
       </c>
       <c r="B164" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493720</v>
+        <v>493670</v>
       </c>
       <c r="R164" t="n">
-        <v>6834910</v>
+        <v>6834981</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17433,10 +17424,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129459953</v>
+        <v>129459449</v>
       </c>
       <c r="B165" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17463,7 +17454,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -17477,10 +17468,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493729</v>
+        <v>493720</v>
       </c>
       <c r="R165" t="n">
-        <v>6834873</v>
+        <v>6834910</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17539,10 +17530,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129476562</v>
+        <v>129459953</v>
       </c>
       <c r="B166" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17569,7 +17560,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -17577,19 +17568,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493676</v>
+        <v>493729</v>
       </c>
       <c r="R166" t="n">
-        <v>6834974</v>
+        <v>6834873</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17630,64 +17618,75 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129476549</v>
+        <v>129476562</v>
       </c>
       <c r="B167" t="n">
-        <v>91603</v>
+        <v>98727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493677</v>
+        <v>493676</v>
       </c>
       <c r="R167" t="n">
-        <v>6835005</v>
+        <v>6834974</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17728,6 +17727,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17746,10 +17746,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476587</v>
+        <v>129476531</v>
       </c>
       <c r="B168" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17757,21 +17757,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17781,10 +17781,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493659</v>
+        <v>493636</v>
       </c>
       <c r="R168" t="n">
-        <v>6834945</v>
+        <v>6834906</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18037,10 +18037,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476531</v>
+        <v>129476570</v>
       </c>
       <c r="B171" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18048,21 +18048,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18072,10 +18072,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493636</v>
+        <v>493628</v>
       </c>
       <c r="R171" t="n">
-        <v>6834906</v>
+        <v>6834790</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18134,10 +18134,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476570</v>
+        <v>129476587</v>
       </c>
       <c r="B172" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18145,21 +18145,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18169,10 +18169,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493628</v>
+        <v>493659</v>
       </c>
       <c r="R172" t="n">
-        <v>6834790</v>
+        <v>6834945</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18234,7 +18234,7 @@
         <v>129459653</v>
       </c>
       <c r="B173" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>129459536</v>
       </c>
       <c r="B174" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>129456373</v>
       </c>
       <c r="B175" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18540,54 +18540,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129456055</v>
+        <v>129459599</v>
       </c>
       <c r="B176" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493817</v>
+        <v>493726</v>
       </c>
       <c r="R176" t="n">
-        <v>6834930</v>
+        <v>6834891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18646,32 +18637,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129459676</v>
+        <v>129460260</v>
       </c>
       <c r="B177" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18681,10 +18672,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493727</v>
+        <v>493731</v>
       </c>
       <c r="R177" t="n">
-        <v>6834879</v>
+        <v>6834851</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18743,10 +18734,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129458467</v>
+        <v>129459676</v>
       </c>
       <c r="B178" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18771,26 +18762,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493646</v>
+        <v>493727</v>
       </c>
       <c r="R178" t="n">
-        <v>6835015</v>
+        <v>6834879</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18849,45 +18831,54 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129459599</v>
+        <v>129458467</v>
       </c>
       <c r="B179" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493726</v>
+        <v>493646</v>
       </c>
       <c r="R179" t="n">
-        <v>6834891</v>
+        <v>6835015</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18946,45 +18937,54 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129460260</v>
+        <v>129456055</v>
       </c>
       <c r="B180" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493731</v>
+        <v>493817</v>
       </c>
       <c r="R180" t="n">
-        <v>6834851</v>
+        <v>6834930</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19240,7 +19240,7 @@
         <v>129459964</v>
       </c>
       <c r="B183" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>129459836</v>
       </c>
       <c r="B184" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19431,54 +19431,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129525359</v>
+        <v>129525028</v>
       </c>
       <c r="B185" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>493934</v>
+        <v>493857</v>
       </c>
       <c r="R185" t="n">
-        <v>6834670</v>
+        <v>6834694</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19525,57 +19516,66 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129525028</v>
+        <v>129525359</v>
       </c>
       <c r="B186" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>493857</v>
+        <v>493934</v>
       </c>
       <c r="R186" t="n">
-        <v>6834694</v>
+        <v>6834670</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19622,12 +19622,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
@@ -19831,7 +19831,7 @@
         <v>129525479</v>
       </c>
       <c r="B189" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19925,10 +19925,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129525395</v>
+        <v>129525603</v>
       </c>
       <c r="B190" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -19965,14 +19965,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>493923</v>
+        <v>493825</v>
       </c>
       <c r="R190" t="n">
-        <v>6834647</v>
+        <v>6834572</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20019,22 +20019,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129525603</v>
+        <v>129525395</v>
       </c>
       <c r="B191" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -20071,14 +20071,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>493825</v>
+        <v>493923</v>
       </c>
       <c r="R191" t="n">
-        <v>6834572</v>
+        <v>6834647</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20125,12 +20125,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -20334,7 +20334,7 @@
         <v>129525370</v>
       </c>
       <c r="B194" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>129525020</v>
       </c>
       <c r="B195" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20534,54 +20534,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129525059</v>
+        <v>129525895</v>
       </c>
       <c r="B196" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>493851</v>
+        <v>493792</v>
       </c>
       <c r="R196" t="n">
-        <v>6834680</v>
+        <v>6834620</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20640,45 +20631,54 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129525895</v>
+        <v>129525059</v>
       </c>
       <c r="B197" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>493792</v>
+        <v>493851</v>
       </c>
       <c r="R197" t="n">
-        <v>6834620</v>
+        <v>6834680</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20837,7 +20837,7 @@
         <v>129525089</v>
       </c>
       <c r="B199" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>129525466</v>
       </c>
       <c r="B200" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>129525496</v>
       </c>
       <c r="B202" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21240,10 +21240,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129525012</v>
+        <v>129525041</v>
       </c>
       <c r="B203" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -21280,14 +21280,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>493866</v>
+        <v>493881</v>
       </c>
       <c r="R203" t="n">
-        <v>6834688</v>
+        <v>6834662</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21334,22 +21334,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129525041</v>
+        <v>129525012</v>
       </c>
       <c r="B204" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -21386,14 +21386,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>493881</v>
+        <v>493866</v>
       </c>
       <c r="R204" t="n">
-        <v>6834662</v>
+        <v>6834688</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21440,22 +21440,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129525474</v>
+        <v>129525022</v>
       </c>
       <c r="B205" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>493908</v>
+        <v>493867</v>
       </c>
       <c r="R205" t="n">
-        <v>6834595</v>
+        <v>6834661</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21558,10 +21558,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129525022</v>
+        <v>129525474</v>
       </c>
       <c r="B206" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>493867</v>
+        <v>493908</v>
       </c>
       <c r="R206" t="n">
-        <v>6834661</v>
+        <v>6834595</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21664,54 +21664,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525477</v>
+        <v>129525320</v>
       </c>
       <c r="B207" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493823</v>
+        <v>493859</v>
       </c>
       <c r="R207" t="n">
-        <v>6834595</v>
+        <v>6834674</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21744,6 +21735,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21773,7 +21769,7 @@
         <v>129525078</v>
       </c>
       <c r="B208" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21879,7 +21875,7 @@
         <v>129524983</v>
       </c>
       <c r="B209" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22079,45 +22075,54 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525320</v>
+        <v>129525477</v>
       </c>
       <c r="B211" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493859</v>
+        <v>493823</v>
       </c>
       <c r="R211" t="n">
-        <v>6834674</v>
+        <v>6834595</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22150,11 +22155,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22181,45 +22181,54 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525462</v>
+        <v>129525001</v>
       </c>
       <c r="B212" t="n">
-        <v>92832</v>
+        <v>98727</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493832</v>
+        <v>493870</v>
       </c>
       <c r="R212" t="n">
-        <v>6834595</v>
+        <v>6834690</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22278,32 +22287,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525429</v>
+        <v>129525451</v>
       </c>
       <c r="B213" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22375,54 +22384,45 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525001</v>
+        <v>129525429</v>
       </c>
       <c r="B214" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>493870</v>
+        <v>493788</v>
       </c>
       <c r="R214" t="n">
-        <v>6834690</v>
+        <v>6834656</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22481,32 +22481,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129525451</v>
+        <v>129525462</v>
       </c>
       <c r="B215" t="n">
-        <v>98724</v>
+        <v>92835</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22516,10 +22516,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>493788</v>
+        <v>493832</v>
       </c>
       <c r="R215" t="n">
-        <v>6834656</v>
+        <v>6834595</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22775,7 +22775,7 @@
         <v>129525489</v>
       </c>
       <c r="B218" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22878,45 +22878,54 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129525130</v>
+        <v>129525418</v>
       </c>
       <c r="B219" t="n">
-        <v>92832</v>
+        <v>98727</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>493858</v>
+        <v>493930</v>
       </c>
       <c r="R219" t="n">
-        <v>6834661</v>
+        <v>6834628</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22963,22 +22972,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129525418</v>
+        <v>129525528</v>
       </c>
       <c r="B220" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23003,26 +23012,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>493930</v>
+        <v>493826</v>
       </c>
       <c r="R220" t="n">
-        <v>6834628</v>
+        <v>6834572</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23069,44 +23069,44 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129525528</v>
+        <v>129525130</v>
       </c>
       <c r="B221" t="n">
-        <v>98724</v>
+        <v>92835</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23116,10 +23116,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>493826</v>
+        <v>493858</v>
       </c>
       <c r="R221" t="n">
-        <v>6834572</v>
+        <v>6834661</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23181,7 +23181,7 @@
         <v>129525347</v>
       </c>
       <c r="B222" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129525445</v>
+        <v>129525601</v>
       </c>
       <c r="B224" t="n">
         <v>79044</v>
@@ -23416,10 +23416,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>493900</v>
+        <v>493922</v>
       </c>
       <c r="R224" t="n">
-        <v>6834610</v>
+        <v>6834518</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23478,7 +23478,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129525601</v>
+        <v>129525445</v>
       </c>
       <c r="B225" t="n">
         <v>79044</v>
@@ -23513,10 +23513,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>493922</v>
+        <v>493900</v>
       </c>
       <c r="R225" t="n">
-        <v>6834518</v>
+        <v>6834610</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,45 +8179,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476586</v>
+        <v>129460004</v>
       </c>
       <c r="B72" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493684</v>
+        <v>493728</v>
       </c>
       <c r="R72" t="n">
-        <v>6834869</v>
+        <v>6834868</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8264,19 +8264,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129460134</v>
+        <v>129460228</v>
       </c>
       <c r="B73" t="n">
         <v>98727</v>
@@ -8304,17 +8304,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493738</v>
+        <v>493736</v>
       </c>
       <c r="R73" t="n">
-        <v>6834870</v>
+        <v>6834865</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8373,7 +8382,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460004</v>
+        <v>129460134</v>
       </c>
       <c r="B74" t="n">
         <v>98727</v>
@@ -8408,10 +8417,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493728</v>
+        <v>493738</v>
       </c>
       <c r="R74" t="n">
-        <v>6834868</v>
+        <v>6834870</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8470,10 +8479,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476572</v>
+        <v>129476586</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8481,21 +8490,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8505,10 +8514,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493675</v>
+        <v>493684</v>
       </c>
       <c r="R75" t="n">
-        <v>6834825</v>
+        <v>6834869</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8567,10 +8576,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129476556</v>
+        <v>129476572</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8578,21 +8587,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8602,10 +8611,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493810</v>
+        <v>493675</v>
       </c>
       <c r="R76" t="n">
-        <v>6834883</v>
+        <v>6834825</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8664,54 +8673,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129460228</v>
+        <v>129476556</v>
       </c>
       <c r="B77" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493736</v>
+        <v>493810</v>
       </c>
       <c r="R77" t="n">
-        <v>6834865</v>
+        <v>6834883</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,57 +8758,66 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129476585</v>
+        <v>129476554</v>
       </c>
       <c r="B78" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493700</v>
+        <v>493648</v>
       </c>
       <c r="R78" t="n">
-        <v>6834837</v>
+        <v>6834929</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,6 +8858,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8867,45 +8877,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129460662</v>
+        <v>129457973</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493658</v>
+        <v>493684</v>
       </c>
       <c r="R79" t="n">
-        <v>6834840</v>
+        <v>6834986</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8964,45 +8983,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129460036</v>
+        <v>129456176</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493728</v>
+        <v>493813</v>
       </c>
       <c r="R80" t="n">
-        <v>6834868</v>
+        <v>6834955</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9061,54 +9089,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129476554</v>
+        <v>129476585</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493648</v>
+        <v>493700</v>
       </c>
       <c r="R81" t="n">
-        <v>6834929</v>
+        <v>6834837</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9149,7 +9168,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9265,54 +9283,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129456176</v>
+        <v>129460036</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493813</v>
+        <v>493728</v>
       </c>
       <c r="R83" t="n">
-        <v>6834955</v>
+        <v>6834868</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9371,54 +9380,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129457973</v>
+        <v>129460662</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493684</v>
+        <v>493658</v>
       </c>
       <c r="R84" t="n">
-        <v>6834986</v>
+        <v>6834840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9477,10 +9477,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129476547</v>
+        <v>129476589</v>
       </c>
       <c r="B85" t="n">
-        <v>79068</v>
+        <v>92835</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9488,21 +9488,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9512,10 +9512,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493722</v>
+        <v>493641</v>
       </c>
       <c r="R85" t="n">
-        <v>6834900</v>
+        <v>6834918</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9574,45 +9574,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129476589</v>
+        <v>129457992</v>
       </c>
       <c r="B86" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493641</v>
+        <v>493684</v>
       </c>
       <c r="R86" t="n">
-        <v>6834918</v>
+        <v>6834988</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9659,57 +9659,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129457992</v>
+        <v>129476547</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>79068</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493684</v>
+        <v>493722</v>
       </c>
       <c r="R87" t="n">
-        <v>6834988</v>
+        <v>6834900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9756,12 +9756,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129457913</v>
+        <v>129460883</v>
       </c>
       <c r="B89" t="n">
         <v>98727</v>
@@ -9893,20 +9893,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493686</v>
+        <v>493637</v>
       </c>
       <c r="R89" t="n">
-        <v>6834989</v>
+        <v>6834831</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9962,7 +9971,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129460883</v>
+        <v>129457913</v>
       </c>
       <c r="B90" t="n">
         <v>98727</v>
@@ -9990,29 +9999,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493637</v>
+        <v>493686</v>
       </c>
       <c r="R90" t="n">
-        <v>6834831</v>
+        <v>6834989</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129476532</v>
+        <v>129476583</v>
       </c>
       <c r="B92" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>493619</v>
+        <v>493664</v>
       </c>
       <c r="R92" t="n">
-        <v>6834843</v>
+        <v>6834992</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476574</v>
+        <v>129476566</v>
       </c>
       <c r="B93" t="n">
         <v>79044</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493702</v>
+        <v>493646</v>
       </c>
       <c r="R93" t="n">
-        <v>6834858</v>
+        <v>6834937</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476566</v>
+        <v>129476574</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493646</v>
+        <v>493702</v>
       </c>
       <c r="R94" t="n">
-        <v>6834937</v>
+        <v>6834858</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10465,10 +10465,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476583</v>
+        <v>129476532</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10476,21 +10476,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10500,10 +10500,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493664</v>
+        <v>493619</v>
       </c>
       <c r="R95" t="n">
-        <v>6834992</v>
+        <v>6834843</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10766,45 +10766,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129455841</v>
+        <v>129455942</v>
       </c>
       <c r="B98" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493803</v>
+        <v>493802</v>
       </c>
       <c r="R98" t="n">
-        <v>6834901</v>
+        <v>6834925</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10863,45 +10872,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129476578</v>
+        <v>129458098</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493718</v>
+        <v>493682</v>
       </c>
       <c r="R99" t="n">
-        <v>6834894</v>
+        <v>6834975</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10948,65 +10966,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476544</v>
+        <v>129458908</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493634</v>
+        <v>493702</v>
       </c>
       <c r="R100" t="n">
-        <v>6834983</v>
+        <v>6834942</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11053,22 +11063,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129476560</v>
+        <v>129476537</v>
       </c>
       <c r="B101" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11076,41 +11086,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493684</v>
+        <v>493659</v>
       </c>
       <c r="R101" t="n">
-        <v>6834860</v>
+        <v>6834945</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11151,7 +11154,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11170,10 +11172,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476569</v>
+        <v>129476544</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11181,34 +11183,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493626</v>
+        <v>493634</v>
       </c>
       <c r="R102" t="n">
-        <v>6834837</v>
+        <v>6834983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11267,45 +11277,52 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129458908</v>
+        <v>129476560</v>
       </c>
       <c r="B103" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493702</v>
+        <v>493684</v>
       </c>
       <c r="R103" t="n">
-        <v>6834942</v>
+        <v>6834860</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11346,72 +11363,64 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129458098</v>
+        <v>129476569</v>
       </c>
       <c r="B104" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493682</v>
+        <v>493626</v>
       </c>
       <c r="R104" t="n">
-        <v>6834975</v>
+        <v>6834837</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11458,66 +11467,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129455942</v>
+        <v>129476578</v>
       </c>
       <c r="B105" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493802</v>
+        <v>493718</v>
       </c>
       <c r="R105" t="n">
-        <v>6834925</v>
+        <v>6834894</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11564,22 +11564,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129476537</v>
+        <v>129455841</v>
       </c>
       <c r="B106" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11587,34 +11587,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493659</v>
+        <v>493803</v>
       </c>
       <c r="R106" t="n">
-        <v>6834945</v>
+        <v>6834901</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11661,19 +11661,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129458915</v>
+        <v>129476577</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -11704,14 +11704,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493698</v>
+        <v>493707</v>
       </c>
       <c r="R107" t="n">
-        <v>6834942</v>
+        <v>6834895</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11758,19 +11758,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129476577</v>
+        <v>129458915</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -11801,14 +11801,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493707</v>
+        <v>493698</v>
       </c>
       <c r="R108" t="n">
-        <v>6834895</v>
+        <v>6834942</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11855,12 +11855,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11973,7 +11973,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129461581</v>
+        <v>129476568</v>
       </c>
       <c r="B110" t="n">
         <v>79044</v>
@@ -12004,14 +12004,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>493634</v>
+        <v>493619</v>
       </c>
       <c r="R110" t="n">
-        <v>6834920</v>
+        <v>6834841</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12058,19 +12058,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129476568</v>
+        <v>129461581</v>
       </c>
       <c r="B111" t="n">
         <v>79044</v>
@@ -12101,14 +12101,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493619</v>
+        <v>493634</v>
       </c>
       <c r="R111" t="n">
-        <v>6834841</v>
+        <v>6834920</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12155,66 +12155,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129456198</v>
+        <v>129476538</v>
       </c>
       <c r="B112" t="n">
-        <v>98727</v>
+        <v>79634</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493810</v>
+        <v>493627</v>
       </c>
       <c r="R112" t="n">
-        <v>6834955</v>
+        <v>6834986</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12261,19 +12252,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129458436</v>
+        <v>129456198</v>
       </c>
       <c r="B113" t="n">
         <v>98727</v>
@@ -12301,17 +12292,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493653</v>
+        <v>493810</v>
       </c>
       <c r="R113" t="n">
-        <v>6835020</v>
+        <v>6834955</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12370,45 +12370,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129476538</v>
+        <v>129458436</v>
       </c>
       <c r="B114" t="n">
-        <v>79634</v>
+        <v>98727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493627</v>
+        <v>493653</v>
       </c>
       <c r="R114" t="n">
-        <v>6834986</v>
+        <v>6835020</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,12 +12455,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12564,7 +12564,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476584</v>
+        <v>129460271</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12595,14 +12595,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493670</v>
+        <v>493731</v>
       </c>
       <c r="R116" t="n">
-        <v>6834995</v>
+        <v>6834853</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12649,19 +12649,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129460271</v>
+        <v>129476584</v>
       </c>
       <c r="B117" t="n">
         <v>79044</v>
@@ -12692,14 +12692,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493731</v>
+        <v>493670</v>
       </c>
       <c r="R117" t="n">
-        <v>6834853</v>
+        <v>6834995</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12746,12 +12746,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12855,7 +12855,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129459774</v>
+        <v>129459731</v>
       </c>
       <c r="B119" t="n">
         <v>98727</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12899,10 +12899,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>493729</v>
+        <v>493725</v>
       </c>
       <c r="R119" t="n">
-        <v>6834877</v>
+        <v>6834883</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12961,7 +12961,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129459731</v>
+        <v>129459774</v>
       </c>
       <c r="B120" t="n">
         <v>98727</v>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>493725</v>
+        <v>493729</v>
       </c>
       <c r="R120" t="n">
-        <v>6834883</v>
+        <v>6834877</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13067,54 +13067,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129456013</v>
+        <v>129476590</v>
       </c>
       <c r="B121" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493806</v>
+        <v>493628</v>
       </c>
       <c r="R121" t="n">
-        <v>6834935</v>
+        <v>6834891</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13161,57 +13152,64 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129461070</v>
+        <v>129476559</v>
       </c>
       <c r="B122" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493629</v>
+        <v>493626</v>
       </c>
       <c r="R122" t="n">
-        <v>6834827</v>
+        <v>6834843</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13252,63 +13250,64 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129457707</v>
+        <v>129476541</v>
       </c>
       <c r="B123" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493815</v>
+        <v>493780</v>
       </c>
       <c r="R123" t="n">
-        <v>6834917</v>
+        <v>6834984</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13355,19 +13354,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129456404</v>
+        <v>129457707</v>
       </c>
       <c r="B124" t="n">
         <v>98727</v>
@@ -13395,26 +13394,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493780</v>
+        <v>493815</v>
       </c>
       <c r="R124" t="n">
-        <v>6834929</v>
+        <v>6834917</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13473,7 +13463,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129456103</v>
+        <v>129456404</v>
       </c>
       <c r="B125" t="n">
         <v>98727</v>
@@ -13503,7 +13493,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -13517,10 +13507,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493817</v>
+        <v>493780</v>
       </c>
       <c r="R125" t="n">
-        <v>6834939</v>
+        <v>6834929</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13579,45 +13569,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129476541</v>
+        <v>129456013</v>
       </c>
       <c r="B126" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493780</v>
+        <v>493806</v>
       </c>
       <c r="R126" t="n">
-        <v>6834984</v>
+        <v>6834935</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13664,64 +13663,66 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129476559</v>
+        <v>129456103</v>
       </c>
       <c r="B127" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493626</v>
+        <v>493817</v>
       </c>
       <c r="R127" t="n">
-        <v>6834843</v>
+        <v>6834939</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13762,64 +13763,63 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129476590</v>
+        <v>129461070</v>
       </c>
       <c r="B128" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493628</v>
+        <v>493629</v>
       </c>
       <c r="R128" t="n">
-        <v>6834891</v>
+        <v>6834827</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13866,22 +13866,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129476530</v>
+        <v>129458645</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,34 +13889,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493705</v>
+        <v>493662</v>
       </c>
       <c r="R129" t="n">
-        <v>6834890</v>
+        <v>6834952</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13963,12 +13963,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14072,10 +14072,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129458645</v>
+        <v>129476530</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14083,34 +14083,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493662</v>
+        <v>493705</v>
       </c>
       <c r="R131" t="n">
-        <v>6834952</v>
+        <v>6834890</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,12 +14157,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -14469,54 +14469,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476553</v>
+        <v>129476552</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493591</v>
+        <v>493629</v>
       </c>
       <c r="R135" t="n">
-        <v>6835008</v>
+        <v>6834831</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14557,7 +14548,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14673,10 +14663,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476580</v>
+        <v>129476548</v>
       </c>
       <c r="B137" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14684,21 +14674,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14708,10 +14698,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493675</v>
+        <v>493687</v>
       </c>
       <c r="R137" t="n">
-        <v>6834937</v>
+        <v>6834930</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14964,45 +14954,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129458414</v>
+        <v>129476580</v>
       </c>
       <c r="B140" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493670</v>
+        <v>493675</v>
       </c>
       <c r="R140" t="n">
-        <v>6834981</v>
+        <v>6834937</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,57 +15039,66 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476552</v>
+        <v>129476553</v>
       </c>
       <c r="B141" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493629</v>
+        <v>493591</v>
       </c>
       <c r="R141" t="n">
-        <v>6834831</v>
+        <v>6835008</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15140,6 +15139,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15158,45 +15158,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129476548</v>
+        <v>129458414</v>
       </c>
       <c r="B142" t="n">
-        <v>91606</v>
+        <v>98727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493687</v>
+        <v>493670</v>
       </c>
       <c r="R142" t="n">
-        <v>6834930</v>
+        <v>6834981</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15243,22 +15243,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129476540</v>
+        <v>129458803</v>
       </c>
       <c r="B143" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15266,34 +15266,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493723</v>
+        <v>493683</v>
       </c>
       <c r="R143" t="n">
-        <v>6834965</v>
+        <v>6834951</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15340,22 +15340,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129458803</v>
+        <v>129476543</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15363,34 +15363,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493683</v>
+        <v>493676</v>
       </c>
       <c r="R144" t="n">
-        <v>6834951</v>
+        <v>6834800</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15437,66 +15445,57 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129457830</v>
+        <v>129476540</v>
       </c>
       <c r="B145" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493676</v>
+        <v>493723</v>
       </c>
       <c r="R145" t="n">
-        <v>6835001</v>
+        <v>6834965</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15543,12 +15542,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15652,53 +15651,54 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129476543</v>
+        <v>129458085</v>
       </c>
       <c r="B147" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493676</v>
+        <v>493690</v>
       </c>
       <c r="R147" t="n">
-        <v>6834800</v>
+        <v>6834972</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15745,19 +15745,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129458085</v>
+        <v>129457830</v>
       </c>
       <c r="B148" t="n">
         <v>98727</v>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -15801,10 +15801,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493690</v>
+        <v>493676</v>
       </c>
       <c r="R148" t="n">
-        <v>6834972</v>
+        <v>6835001</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15960,10 +15960,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476539</v>
+        <v>129476535</v>
       </c>
       <c r="B150" t="n">
-        <v>90585</v>
+        <v>79663</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15971,21 +15971,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493652</v>
+        <v>493703</v>
       </c>
       <c r="R150" t="n">
-        <v>6834985</v>
+        <v>6834865</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16057,10 +16057,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476535</v>
+        <v>129476539</v>
       </c>
       <c r="B151" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16068,21 +16068,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493703</v>
+        <v>493652</v>
       </c>
       <c r="R151" t="n">
-        <v>6834865</v>
+        <v>6834985</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16251,7 +16251,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129476576</v>
+        <v>129476567</v>
       </c>
       <c r="B153" t="n">
         <v>79044</v>
@@ -16286,10 +16286,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493725</v>
+        <v>493634</v>
       </c>
       <c r="R153" t="n">
-        <v>6834888</v>
+        <v>6834889</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16445,7 +16445,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129476567</v>
+        <v>129476576</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -16480,10 +16480,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493634</v>
+        <v>493725</v>
       </c>
       <c r="R155" t="n">
-        <v>6834889</v>
+        <v>6834888</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16745,10 +16745,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129476546</v>
+        <v>129476549</v>
       </c>
       <c r="B158" t="n">
-        <v>91851</v>
+        <v>91606</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16756,21 +16756,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16780,10 +16780,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493733</v>
+        <v>493677</v>
       </c>
       <c r="R158" t="n">
-        <v>6834961</v>
+        <v>6835005</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16842,10 +16842,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129476549</v>
+        <v>129476546</v>
       </c>
       <c r="B159" t="n">
-        <v>91606</v>
+        <v>91851</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16853,21 +16853,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493677</v>
+        <v>493733</v>
       </c>
       <c r="R159" t="n">
-        <v>6835005</v>
+        <v>6834961</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16939,10 +16939,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129476533</v>
+        <v>129459208</v>
       </c>
       <c r="B160" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16950,34 +16950,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493678</v>
+        <v>493698</v>
       </c>
       <c r="R160" t="n">
-        <v>6834780</v>
+        <v>6834943</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17024,22 +17024,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129476536</v>
+        <v>129457857</v>
       </c>
       <c r="B161" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17047,34 +17047,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>493642</v>
+        <v>493676</v>
       </c>
       <c r="R161" t="n">
-        <v>6834998</v>
+        <v>6835001</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17121,22 +17121,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129457857</v>
+        <v>129476536</v>
       </c>
       <c r="B162" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17144,34 +17144,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493676</v>
+        <v>493642</v>
       </c>
       <c r="R162" t="n">
-        <v>6835001</v>
+        <v>6834998</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17218,19 +17218,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129459208</v>
+        <v>129458226</v>
       </c>
       <c r="B163" t="n">
         <v>79044</v>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493698</v>
+        <v>493670</v>
       </c>
       <c r="R163" t="n">
-        <v>6834943</v>
+        <v>6834981</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17327,10 +17327,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129458226</v>
+        <v>129476533</v>
       </c>
       <c r="B164" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,34 +17338,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493670</v>
+        <v>493678</v>
       </c>
       <c r="R164" t="n">
-        <v>6834981</v>
+        <v>6834780</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17412,19 +17412,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129459449</v>
+        <v>129476562</v>
       </c>
       <c r="B165" t="n">
         <v>98727</v>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -17462,16 +17462,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493720</v>
+        <v>493676</v>
       </c>
       <c r="R165" t="n">
-        <v>6834910</v>
+        <v>6834974</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17512,25 +17515,26 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129459953</v>
+        <v>129459449</v>
       </c>
       <c r="B166" t="n">
         <v>98727</v>
@@ -17560,7 +17564,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -17574,10 +17578,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493729</v>
+        <v>493720</v>
       </c>
       <c r="R166" t="n">
-        <v>6834873</v>
+        <v>6834910</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17636,7 +17640,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129476562</v>
+        <v>129459953</v>
       </c>
       <c r="B167" t="n">
         <v>98727</v>
@@ -17666,7 +17670,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -17674,19 +17678,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493676</v>
+        <v>493729</v>
       </c>
       <c r="R167" t="n">
-        <v>6834974</v>
+        <v>6834873</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17727,64 +17728,72 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476531</v>
+        <v>129456373</v>
       </c>
       <c r="B168" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493636</v>
+        <v>493796</v>
       </c>
       <c r="R168" t="n">
-        <v>6834906</v>
+        <v>6834937</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17831,57 +17840,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129476581</v>
+        <v>129459536</v>
       </c>
       <c r="B169" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493677</v>
+        <v>493723</v>
       </c>
       <c r="R169" t="n">
-        <v>6834943</v>
+        <v>6834898</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17928,57 +17937,66 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129476575</v>
+        <v>129459653</v>
       </c>
       <c r="B170" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493728</v>
+        <v>493740</v>
       </c>
       <c r="R170" t="n">
-        <v>6834886</v>
+        <v>6834887</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18025,19 +18043,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476570</v>
+        <v>129476581</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18072,10 +18090,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493628</v>
+        <v>493677</v>
       </c>
       <c r="R171" t="n">
-        <v>6834790</v>
+        <v>6834943</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18134,10 +18152,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476587</v>
+        <v>129476575</v>
       </c>
       <c r="B172" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18145,21 +18163,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18169,10 +18187,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493659</v>
+        <v>493728</v>
       </c>
       <c r="R172" t="n">
-        <v>6834945</v>
+        <v>6834886</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18231,54 +18249,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129459653</v>
+        <v>129476570</v>
       </c>
       <c r="B173" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493740</v>
+        <v>493628</v>
       </c>
       <c r="R173" t="n">
-        <v>6834887</v>
+        <v>6834790</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18325,57 +18334,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129459536</v>
+        <v>129476587</v>
       </c>
       <c r="B174" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493723</v>
+        <v>493659</v>
       </c>
       <c r="R174" t="n">
-        <v>6834898</v>
+        <v>6834945</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18422,66 +18431,57 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129456373</v>
+        <v>129476531</v>
       </c>
       <c r="B175" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493796</v>
+        <v>493636</v>
       </c>
       <c r="R175" t="n">
-        <v>6834937</v>
+        <v>6834906</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,57 +18528,66 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129459599</v>
+        <v>129456055</v>
       </c>
       <c r="B176" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493726</v>
+        <v>493817</v>
       </c>
       <c r="R176" t="n">
-        <v>6834891</v>
+        <v>6834930</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,32 +18646,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129460260</v>
+        <v>129459676</v>
       </c>
       <c r="B177" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18672,10 +18681,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493731</v>
+        <v>493727</v>
       </c>
       <c r="R177" t="n">
-        <v>6834851</v>
+        <v>6834879</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18734,7 +18743,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129459676</v>
+        <v>129458467</v>
       </c>
       <c r="B178" t="n">
         <v>98727</v>
@@ -18762,17 +18771,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493727</v>
+        <v>493646</v>
       </c>
       <c r="R178" t="n">
-        <v>6834879</v>
+        <v>6835015</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18831,54 +18849,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129458467</v>
+        <v>129459599</v>
       </c>
       <c r="B179" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493646</v>
+        <v>493726</v>
       </c>
       <c r="R179" t="n">
-        <v>6835015</v>
+        <v>6834891</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18937,54 +18946,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129456055</v>
+        <v>129460260</v>
       </c>
       <c r="B180" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493817</v>
+        <v>493731</v>
       </c>
       <c r="R180" t="n">
-        <v>6834930</v>
+        <v>6834851</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19140,45 +19140,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129476551</v>
+        <v>129459964</v>
       </c>
       <c r="B182" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493632</v>
+        <v>493726</v>
       </c>
       <c r="R182" t="n">
-        <v>6834827</v>
+        <v>6834867</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19225,57 +19225,57 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129459964</v>
+        <v>129476551</v>
       </c>
       <c r="B183" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493726</v>
+        <v>493632</v>
       </c>
       <c r="R183" t="n">
-        <v>6834867</v>
+        <v>6834827</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19322,12 +19322,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19634,7 +19634,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129525566</v>
+        <v>129525456</v>
       </c>
       <c r="B187" t="n">
         <v>79044</v>
@@ -19669,10 +19669,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>493930</v>
+        <v>493893</v>
       </c>
       <c r="R187" t="n">
-        <v>6834516</v>
+        <v>6834612</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19731,45 +19731,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129525456</v>
+        <v>129525479</v>
       </c>
       <c r="B188" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>493893</v>
+        <v>493825</v>
       </c>
       <c r="R188" t="n">
-        <v>6834612</v>
+        <v>6834594</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19816,57 +19816,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129525479</v>
+        <v>129525566</v>
       </c>
       <c r="B189" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>493825</v>
+        <v>493930</v>
       </c>
       <c r="R189" t="n">
-        <v>6834594</v>
+        <v>6834516</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19913,19 +19913,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129525603</v>
+        <v>129525395</v>
       </c>
       <c r="B190" t="n">
         <v>98727</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -19965,14 +19965,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>493825</v>
+        <v>493923</v>
       </c>
       <c r="R190" t="n">
-        <v>6834572</v>
+        <v>6834647</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20019,19 +20019,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129525395</v>
+        <v>129525603</v>
       </c>
       <c r="B191" t="n">
         <v>98727</v>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -20071,14 +20071,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>493923</v>
+        <v>493825</v>
       </c>
       <c r="R191" t="n">
-        <v>6834647</v>
+        <v>6834572</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20125,12 +20125,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -20331,7 +20331,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129525370</v>
+        <v>129525020</v>
       </c>
       <c r="B194" t="n">
         <v>98727</v>
@@ -20359,17 +20359,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>493942</v>
+        <v>493860</v>
       </c>
       <c r="R194" t="n">
-        <v>6834657</v>
+        <v>6834704</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20416,19 +20425,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129525020</v>
+        <v>129525370</v>
       </c>
       <c r="B195" t="n">
         <v>98727</v>
@@ -20456,26 +20465,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>493860</v>
+        <v>493942</v>
       </c>
       <c r="R195" t="n">
-        <v>6834704</v>
+        <v>6834657</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20522,57 +20522,66 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129525895</v>
+        <v>129525059</v>
       </c>
       <c r="B196" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>493792</v>
+        <v>493851</v>
       </c>
       <c r="R196" t="n">
-        <v>6834620</v>
+        <v>6834680</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20631,54 +20640,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129525059</v>
+        <v>129525895</v>
       </c>
       <c r="B197" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>493851</v>
+        <v>493792</v>
       </c>
       <c r="R197" t="n">
-        <v>6834680</v>
+        <v>6834620</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20834,7 +20834,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129525089</v>
+        <v>129525466</v>
       </c>
       <c r="B199" t="n">
         <v>98727</v>
@@ -20862,26 +20862,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>493895</v>
+        <v>493832</v>
       </c>
       <c r="R199" t="n">
-        <v>6834684</v>
+        <v>6834595</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20928,19 +20919,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129525466</v>
+        <v>129525089</v>
       </c>
       <c r="B200" t="n">
         <v>98727</v>
@@ -20968,17 +20959,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>493832</v>
+        <v>493895</v>
       </c>
       <c r="R200" t="n">
-        <v>6834595</v>
+        <v>6834684</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21025,57 +21025,66 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129525470</v>
+        <v>129525496</v>
       </c>
       <c r="B201" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>493900</v>
+        <v>493821</v>
       </c>
       <c r="R201" t="n">
-        <v>6834623</v>
+        <v>6834572</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21122,66 +21131,57 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129525496</v>
+        <v>129525470</v>
       </c>
       <c r="B202" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>493821</v>
+        <v>493900</v>
       </c>
       <c r="R202" t="n">
-        <v>6834572</v>
+        <v>6834623</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21228,12 +21228,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
@@ -21664,10 +21664,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525320</v>
+        <v>129525442</v>
       </c>
       <c r="B207" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21675,34 +21675,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493859</v>
+        <v>493925</v>
       </c>
       <c r="R207" t="n">
-        <v>6834674</v>
+        <v>6834617</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21737,11 +21737,6 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD207" t="b">
         <v>0</v>
       </c>
@@ -21754,19 +21749,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129525078</v>
+        <v>129525477</v>
       </c>
       <c r="B208" t="n">
         <v>98727</v>
@@ -21796,7 +21791,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -21806,14 +21801,14 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493886</v>
+        <v>493823</v>
       </c>
       <c r="R208" t="n">
-        <v>6834673</v>
+        <v>6834595</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21860,12 +21855,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
@@ -21978,45 +21973,54 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129525442</v>
+        <v>129525078</v>
       </c>
       <c r="B210" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493925</v>
+        <v>493886</v>
       </c>
       <c r="R210" t="n">
-        <v>6834617</v>
+        <v>6834673</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22075,54 +22079,45 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525477</v>
+        <v>129525320</v>
       </c>
       <c r="B211" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493823</v>
+        <v>493859</v>
       </c>
       <c r="R211" t="n">
-        <v>6834595</v>
+        <v>6834674</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22155,6 +22150,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22181,54 +22181,45 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525001</v>
+        <v>129525462</v>
       </c>
       <c r="B212" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493870</v>
+        <v>493832</v>
       </c>
       <c r="R212" t="n">
-        <v>6834690</v>
+        <v>6834595</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22287,7 +22278,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525451</v>
+        <v>129525001</v>
       </c>
       <c r="B213" t="n">
         <v>98727</v>
@@ -22315,17 +22306,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>493788</v>
+        <v>493870</v>
       </c>
       <c r="R213" t="n">
-        <v>6834656</v>
+        <v>6834690</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22384,32 +22384,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525429</v>
+        <v>129525451</v>
       </c>
       <c r="B214" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22481,32 +22481,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129525462</v>
+        <v>129525429</v>
       </c>
       <c r="B215" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22516,10 +22516,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>493832</v>
+        <v>493788</v>
       </c>
       <c r="R215" t="n">
-        <v>6834595</v>
+        <v>6834656</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22878,54 +22878,45 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129525418</v>
+        <v>129525130</v>
       </c>
       <c r="B219" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>493930</v>
+        <v>493858</v>
       </c>
       <c r="R219" t="n">
-        <v>6834628</v>
+        <v>6834661</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22972,19 +22963,19 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129525528</v>
+        <v>129525418</v>
       </c>
       <c r="B220" t="n">
         <v>98727</v>
@@ -23012,17 +23003,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>493826</v>
+        <v>493930</v>
       </c>
       <c r="R220" t="n">
-        <v>6834572</v>
+        <v>6834628</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23069,44 +23069,44 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129525130</v>
+        <v>129525528</v>
       </c>
       <c r="B221" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23116,10 +23116,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>493858</v>
+        <v>493826</v>
       </c>
       <c r="R221" t="n">
-        <v>6834661</v>
+        <v>6834572</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23178,54 +23178,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129525347</v>
+        <v>129525680</v>
       </c>
       <c r="B222" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>493915</v>
+        <v>493840</v>
       </c>
       <c r="R222" t="n">
-        <v>6834671</v>
+        <v>6834519</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23272,57 +23263,66 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129525680</v>
+        <v>129525347</v>
       </c>
       <c r="B223" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>493840</v>
+        <v>493915</v>
       </c>
       <c r="R223" t="n">
-        <v>6834519</v>
+        <v>6834671</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23369,12 +23369,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,45 +8179,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129460004</v>
+        <v>129476586</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493728</v>
+        <v>493684</v>
       </c>
       <c r="R72" t="n">
-        <v>6834868</v>
+        <v>6834869</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8264,66 +8264,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129460228</v>
+        <v>129476556</v>
       </c>
       <c r="B73" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493736</v>
+        <v>493810</v>
       </c>
       <c r="R73" t="n">
-        <v>6834865</v>
+        <v>6834883</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8370,57 +8361,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460134</v>
+        <v>129476572</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493738</v>
+        <v>493675</v>
       </c>
       <c r="R74" t="n">
-        <v>6834870</v>
+        <v>6834825</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,57 +8458,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476586</v>
+        <v>129460134</v>
       </c>
       <c r="B75" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493684</v>
+        <v>493738</v>
       </c>
       <c r="R75" t="n">
-        <v>6834869</v>
+        <v>6834870</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8564,57 +8555,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129476572</v>
+        <v>129460004</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493675</v>
+        <v>493728</v>
       </c>
       <c r="R76" t="n">
-        <v>6834825</v>
+        <v>6834868</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8661,57 +8652,66 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129476556</v>
+        <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493810</v>
+        <v>493736</v>
       </c>
       <c r="R77" t="n">
-        <v>6834883</v>
+        <v>6834865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,66 +8758,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129476554</v>
+        <v>129476585</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493648</v>
+        <v>493700</v>
       </c>
       <c r="R78" t="n">
-        <v>6834929</v>
+        <v>6834837</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8858,7 +8849,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8877,54 +8867,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129457973</v>
+        <v>129461154</v>
       </c>
       <c r="B79" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493684</v>
+        <v>493629</v>
       </c>
       <c r="R79" t="n">
-        <v>6834986</v>
+        <v>6834827</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8983,54 +8964,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129456176</v>
+        <v>129460036</v>
       </c>
       <c r="B80" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493813</v>
+        <v>493728</v>
       </c>
       <c r="R80" t="n">
-        <v>6834955</v>
+        <v>6834868</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9089,10 +9061,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129476585</v>
+        <v>129460662</v>
       </c>
       <c r="B81" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9100,34 +9072,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493700</v>
+        <v>493658</v>
       </c>
       <c r="R81" t="n">
-        <v>6834837</v>
+        <v>6834840</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9174,57 +9146,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129461154</v>
+        <v>129476554</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493629</v>
+        <v>493648</v>
       </c>
       <c r="R82" t="n">
-        <v>6834827</v>
+        <v>6834929</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9265,63 +9246,73 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129460036</v>
+        <v>129456176</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493728</v>
+        <v>493813</v>
       </c>
       <c r="R83" t="n">
-        <v>6834868</v>
+        <v>6834955</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9380,45 +9371,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129460662</v>
+        <v>129457973</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493658</v>
+        <v>493684</v>
       </c>
       <c r="R84" t="n">
-        <v>6834840</v>
+        <v>6834986</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9477,45 +9477,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129476589</v>
+        <v>129457992</v>
       </c>
       <c r="B85" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493641</v>
+        <v>493684</v>
       </c>
       <c r="R85" t="n">
-        <v>6834918</v>
+        <v>6834988</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9562,57 +9562,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129457992</v>
+        <v>129476547</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>79068</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493684</v>
+        <v>493722</v>
       </c>
       <c r="R86" t="n">
-        <v>6834988</v>
+        <v>6834900</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9659,44 +9659,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129476547</v>
+        <v>129476579</v>
       </c>
       <c r="B87" t="n">
-        <v>79068</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493722</v>
+        <v>493687</v>
       </c>
       <c r="R87" t="n">
-        <v>6834900</v>
+        <v>6834917</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9768,32 +9768,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129476579</v>
+        <v>129476589</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493687</v>
+        <v>493641</v>
       </c>
       <c r="R88" t="n">
-        <v>6834917</v>
+        <v>6834918</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9865,7 +9865,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129460883</v>
+        <v>129457913</v>
       </c>
       <c r="B89" t="n">
         <v>98727</v>
@@ -9893,29 +9893,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493637</v>
+        <v>493686</v>
       </c>
       <c r="R89" t="n">
-        <v>6834831</v>
+        <v>6834989</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9971,7 +9962,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129457913</v>
+        <v>129460883</v>
       </c>
       <c r="B90" t="n">
         <v>98727</v>
@@ -9999,20 +9990,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493686</v>
+        <v>493637</v>
       </c>
       <c r="R90" t="n">
-        <v>6834989</v>
+        <v>6834831</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10271,10 +10271,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476566</v>
+        <v>129476532</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10282,21 +10282,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493646</v>
+        <v>493619</v>
       </c>
       <c r="R93" t="n">
-        <v>6834937</v>
+        <v>6834843</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476574</v>
+        <v>129476566</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493702</v>
+        <v>493646</v>
       </c>
       <c r="R94" t="n">
-        <v>6834858</v>
+        <v>6834937</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10465,10 +10465,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476532</v>
+        <v>129476574</v>
       </c>
       <c r="B95" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10476,21 +10476,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10500,10 +10500,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493619</v>
+        <v>493702</v>
       </c>
       <c r="R95" t="n">
-        <v>6834843</v>
+        <v>6834858</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10766,54 +10766,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129455942</v>
+        <v>129476537</v>
       </c>
       <c r="B98" t="n">
-        <v>98727</v>
+        <v>79634</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493802</v>
+        <v>493659</v>
       </c>
       <c r="R98" t="n">
-        <v>6834925</v>
+        <v>6834945</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10860,66 +10851,64 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129458098</v>
+        <v>129476560</v>
       </c>
       <c r="B99" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493682</v>
+        <v>493684</v>
       </c>
       <c r="R99" t="n">
-        <v>6834975</v>
+        <v>6834860</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10960,63 +10949,64 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129458908</v>
+        <v>129476569</v>
       </c>
       <c r="B100" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493702</v>
+        <v>493626</v>
       </c>
       <c r="R100" t="n">
-        <v>6834942</v>
+        <v>6834837</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11063,22 +11053,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129476537</v>
+        <v>129476578</v>
       </c>
       <c r="B101" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11086,21 +11076,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11110,10 +11100,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493659</v>
+        <v>493718</v>
       </c>
       <c r="R101" t="n">
-        <v>6834945</v>
+        <v>6834894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11172,10 +11162,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476544</v>
+        <v>129455841</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11183,42 +11173,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493634</v>
+        <v>493803</v>
       </c>
       <c r="R102" t="n">
-        <v>6834983</v>
+        <v>6834901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11265,22 +11247,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476560</v>
+        <v>129476544</v>
       </c>
       <c r="B103" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11288,28 +11270,29 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11319,10 +11302,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493684</v>
+        <v>493634</v>
       </c>
       <c r="R103" t="n">
-        <v>6834860</v>
+        <v>6834983</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11363,7 +11346,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11382,45 +11364,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129476569</v>
+        <v>129455942</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493626</v>
+        <v>493802</v>
       </c>
       <c r="R104" t="n">
-        <v>6834837</v>
+        <v>6834925</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11467,57 +11458,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129476578</v>
+        <v>129458908</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493718</v>
+        <v>493702</v>
       </c>
       <c r="R105" t="n">
-        <v>6834894</v>
+        <v>6834942</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11564,57 +11555,66 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129455841</v>
+        <v>129458098</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493803</v>
+        <v>493682</v>
       </c>
       <c r="R106" t="n">
-        <v>6834901</v>
+        <v>6834975</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11673,45 +11673,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129476577</v>
+        <v>129456312</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493707</v>
+        <v>493787</v>
       </c>
       <c r="R107" t="n">
-        <v>6834895</v>
+        <v>6834957</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11758,12 +11767,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11867,54 +11876,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129456312</v>
+        <v>129476577</v>
       </c>
       <c r="B109" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493787</v>
+        <v>493707</v>
       </c>
       <c r="R109" t="n">
-        <v>6834957</v>
+        <v>6834895</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11961,12 +11961,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12167,45 +12167,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129476538</v>
+        <v>129456198</v>
       </c>
       <c r="B112" t="n">
-        <v>79634</v>
+        <v>98727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493627</v>
+        <v>493810</v>
       </c>
       <c r="R112" t="n">
-        <v>6834986</v>
+        <v>6834955</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12252,19 +12261,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129456198</v>
+        <v>129458436</v>
       </c>
       <c r="B113" t="n">
         <v>98727</v>
@@ -12292,26 +12301,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493810</v>
+        <v>493653</v>
       </c>
       <c r="R113" t="n">
-        <v>6834955</v>
+        <v>6835020</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12370,45 +12370,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129458436</v>
+        <v>129476538</v>
       </c>
       <c r="B114" t="n">
-        <v>98727</v>
+        <v>79634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493653</v>
+        <v>493627</v>
       </c>
       <c r="R114" t="n">
-        <v>6835020</v>
+        <v>6834986</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,12 +12455,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13164,10 +13164,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476559</v>
+        <v>129476541</v>
       </c>
       <c r="B122" t="n">
-        <v>78801</v>
+        <v>91553</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13175,41 +13175,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493626</v>
+        <v>493780</v>
       </c>
       <c r="R122" t="n">
-        <v>6834843</v>
+        <v>6834984</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13250,7 +13243,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13269,10 +13261,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129476541</v>
+        <v>129476559</v>
       </c>
       <c r="B123" t="n">
-        <v>91553</v>
+        <v>78801</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13280,34 +13272,41 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493780</v>
+        <v>493626</v>
       </c>
       <c r="R123" t="n">
-        <v>6834984</v>
+        <v>6834843</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13348,6 +13347,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129457707</v>
+        <v>129461070</v>
       </c>
       <c r="B124" t="n">
         <v>98727</v>
@@ -13401,10 +13401,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493815</v>
+        <v>493629</v>
       </c>
       <c r="R124" t="n">
-        <v>6834917</v>
+        <v>6834827</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13463,7 +13463,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129456404</v>
+        <v>129457707</v>
       </c>
       <c r="B125" t="n">
         <v>98727</v>
@@ -13491,26 +13491,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493780</v>
+        <v>493815</v>
       </c>
       <c r="R125" t="n">
-        <v>6834929</v>
+        <v>6834917</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13675,7 +13666,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129456103</v>
+        <v>129456404</v>
       </c>
       <c r="B127" t="n">
         <v>98727</v>
@@ -13705,7 +13696,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13719,10 +13710,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493817</v>
+        <v>493780</v>
       </c>
       <c r="R127" t="n">
-        <v>6834939</v>
+        <v>6834929</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13781,7 +13772,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129461070</v>
+        <v>129456103</v>
       </c>
       <c r="B128" t="n">
         <v>98727</v>
@@ -13809,17 +13800,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493629</v>
+        <v>493817</v>
       </c>
       <c r="R128" t="n">
-        <v>6834827</v>
+        <v>6834939</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129458645</v>
+        <v>129476530</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,34 +13889,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493662</v>
+        <v>493705</v>
       </c>
       <c r="R129" t="n">
-        <v>6834952</v>
+        <v>6834890</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13963,19 +13963,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129455888</v>
+        <v>129458645</v>
       </c>
       <c r="B130" t="n">
         <v>79044</v>
@@ -14010,10 +14010,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493811</v>
+        <v>493662</v>
       </c>
       <c r="R130" t="n">
-        <v>6834925</v>
+        <v>6834952</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14072,10 +14072,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129476530</v>
+        <v>129455888</v>
       </c>
       <c r="B131" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14083,34 +14083,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493705</v>
+        <v>493811</v>
       </c>
       <c r="R131" t="n">
-        <v>6834890</v>
+        <v>6834925</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,12 +14157,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476552</v>
+        <v>129459901</v>
       </c>
       <c r="B135" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,34 +14480,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493629</v>
+        <v>493734</v>
       </c>
       <c r="R135" t="n">
-        <v>6834831</v>
+        <v>6834875</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14554,22 +14554,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476588</v>
+        <v>129476580</v>
       </c>
       <c r="B136" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493619</v>
+        <v>493675</v>
       </c>
       <c r="R136" t="n">
-        <v>6834998</v>
+        <v>6834937</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14760,10 +14760,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129476573</v>
+        <v>129476588</v>
       </c>
       <c r="B138" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14771,21 +14771,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14795,10 +14795,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493661</v>
+        <v>493619</v>
       </c>
       <c r="R138" t="n">
-        <v>6834848</v>
+        <v>6834998</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14857,7 +14857,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129459901</v>
+        <v>129476573</v>
       </c>
       <c r="B139" t="n">
         <v>79044</v>
@@ -14888,14 +14888,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493734</v>
+        <v>493661</v>
       </c>
       <c r="R139" t="n">
-        <v>6834875</v>
+        <v>6834848</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14942,57 +14942,66 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129476580</v>
+        <v>129476553</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493675</v>
+        <v>493591</v>
       </c>
       <c r="R140" t="n">
-        <v>6834937</v>
+        <v>6835008</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15033,6 +15042,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15051,54 +15061,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476553</v>
+        <v>129458414</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>98727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493591</v>
+        <v>493670</v>
       </c>
       <c r="R141" t="n">
-        <v>6835008</v>
+        <v>6834981</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15139,64 +15140,63 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129458414</v>
+        <v>129476552</v>
       </c>
       <c r="B142" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493670</v>
+        <v>493629</v>
       </c>
       <c r="R142" t="n">
-        <v>6834981</v>
+        <v>6834831</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15243,22 +15243,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129458803</v>
+        <v>129476540</v>
       </c>
       <c r="B143" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15266,34 +15266,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493683</v>
+        <v>493723</v>
       </c>
       <c r="R143" t="n">
-        <v>6834951</v>
+        <v>6834965</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15340,22 +15340,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129476543</v>
+        <v>129458803</v>
       </c>
       <c r="B144" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15363,42 +15363,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493676</v>
+        <v>493683</v>
       </c>
       <c r="R144" t="n">
-        <v>6834800</v>
+        <v>6834951</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15445,22 +15437,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129476540</v>
+        <v>129476543</v>
       </c>
       <c r="B145" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15468,34 +15460,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493723</v>
+        <v>493676</v>
       </c>
       <c r="R145" t="n">
-        <v>6834965</v>
+        <v>6834800</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15554,7 +15554,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129459852</v>
+        <v>129457830</v>
       </c>
       <c r="B146" t="n">
         <v>98727</v>
@@ -15582,17 +15582,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493730</v>
+        <v>493676</v>
       </c>
       <c r="R146" t="n">
-        <v>6834877</v>
+        <v>6835001</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15757,7 +15766,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129457830</v>
+        <v>129459852</v>
       </c>
       <c r="B148" t="n">
         <v>98727</v>
@@ -15785,26 +15794,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493676</v>
+        <v>493730</v>
       </c>
       <c r="R148" t="n">
-        <v>6835001</v>
+        <v>6834877</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15960,45 +15960,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476535</v>
+        <v>129460421</v>
       </c>
       <c r="B150" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493703</v>
+        <v>493728</v>
       </c>
       <c r="R150" t="n">
-        <v>6834865</v>
+        <v>6834848</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16045,12 +16045,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16154,45 +16154,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129460421</v>
+        <v>129476535</v>
       </c>
       <c r="B152" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>493728</v>
+        <v>493703</v>
       </c>
       <c r="R152" t="n">
-        <v>6834848</v>
+        <v>6834865</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16239,19 +16239,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129476567</v>
+        <v>129460467</v>
       </c>
       <c r="B153" t="n">
         <v>79044</v>
@@ -16282,14 +16282,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493634</v>
+        <v>493728</v>
       </c>
       <c r="R153" t="n">
-        <v>6834889</v>
+        <v>6834842</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16336,19 +16336,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129460467</v>
+        <v>129476567</v>
       </c>
       <c r="B154" t="n">
         <v>79044</v>
@@ -16379,14 +16379,14 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>493728</v>
+        <v>493634</v>
       </c>
       <c r="R154" t="n">
-        <v>6834842</v>
+        <v>6834889</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16433,12 +16433,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
@@ -17036,10 +17036,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129457857</v>
+        <v>129476533</v>
       </c>
       <c r="B161" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17047,34 +17047,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>493676</v>
+        <v>493678</v>
       </c>
       <c r="R161" t="n">
-        <v>6835001</v>
+        <v>6834780</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17121,12 +17121,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17327,10 +17327,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129476533</v>
+        <v>129457857</v>
       </c>
       <c r="B164" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,34 +17338,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493678</v>
+        <v>493676</v>
       </c>
       <c r="R164" t="n">
-        <v>6834780</v>
+        <v>6835001</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17412,19 +17412,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129476562</v>
+        <v>129459449</v>
       </c>
       <c r="B165" t="n">
         <v>98727</v>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -17462,19 +17462,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493676</v>
+        <v>493720</v>
       </c>
       <c r="R165" t="n">
-        <v>6834974</v>
+        <v>6834910</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17515,26 +17512,25 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129459449</v>
+        <v>129459953</v>
       </c>
       <c r="B166" t="n">
         <v>98727</v>
@@ -17564,7 +17560,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -17578,10 +17574,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493720</v>
+        <v>493729</v>
       </c>
       <c r="R166" t="n">
-        <v>6834910</v>
+        <v>6834873</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17640,7 +17636,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129459953</v>
+        <v>129476562</v>
       </c>
       <c r="B167" t="n">
         <v>98727</v>
@@ -17670,7 +17666,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -17678,16 +17674,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493729</v>
+        <v>493676</v>
       </c>
       <c r="R167" t="n">
-        <v>6834873</v>
+        <v>6834974</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17728,72 +17727,64 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129456373</v>
+        <v>129476531</v>
       </c>
       <c r="B168" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493796</v>
+        <v>493636</v>
       </c>
       <c r="R168" t="n">
-        <v>6834937</v>
+        <v>6834906</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17840,57 +17831,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129459536</v>
+        <v>129476581</v>
       </c>
       <c r="B169" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493723</v>
+        <v>493677</v>
       </c>
       <c r="R169" t="n">
-        <v>6834898</v>
+        <v>6834943</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17937,66 +17928,57 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129459653</v>
+        <v>129476575</v>
       </c>
       <c r="B170" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493740</v>
+        <v>493728</v>
       </c>
       <c r="R170" t="n">
-        <v>6834887</v>
+        <v>6834886</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18043,19 +18025,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476581</v>
+        <v>129476570</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18090,10 +18072,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493677</v>
+        <v>493628</v>
       </c>
       <c r="R171" t="n">
-        <v>6834943</v>
+        <v>6834790</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18152,10 +18134,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476575</v>
+        <v>129476587</v>
       </c>
       <c r="B172" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18163,21 +18145,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18187,10 +18169,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493728</v>
+        <v>493659</v>
       </c>
       <c r="R172" t="n">
-        <v>6834886</v>
+        <v>6834945</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18249,45 +18231,54 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129476570</v>
+        <v>129459653</v>
       </c>
       <c r="B173" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493628</v>
+        <v>493740</v>
       </c>
       <c r="R173" t="n">
-        <v>6834790</v>
+        <v>6834887</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18334,57 +18325,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129476587</v>
+        <v>129459536</v>
       </c>
       <c r="B174" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493659</v>
+        <v>493723</v>
       </c>
       <c r="R174" t="n">
-        <v>6834945</v>
+        <v>6834898</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18431,57 +18422,66 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129476531</v>
+        <v>129456373</v>
       </c>
       <c r="B175" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493636</v>
+        <v>493796</v>
       </c>
       <c r="R175" t="n">
-        <v>6834906</v>
+        <v>6834937</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,66 +18528,57 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129456055</v>
+        <v>129459599</v>
       </c>
       <c r="B176" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493817</v>
+        <v>493726</v>
       </c>
       <c r="R176" t="n">
-        <v>6834930</v>
+        <v>6834891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18646,32 +18637,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129459676</v>
+        <v>129460260</v>
       </c>
       <c r="B177" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18681,10 +18672,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493727</v>
+        <v>493731</v>
       </c>
       <c r="R177" t="n">
-        <v>6834879</v>
+        <v>6834851</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18743,7 +18734,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129458467</v>
+        <v>129456055</v>
       </c>
       <c r="B178" t="n">
         <v>98727</v>
@@ -18773,7 +18764,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -18787,10 +18778,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493646</v>
+        <v>493817</v>
       </c>
       <c r="R178" t="n">
-        <v>6835015</v>
+        <v>6834930</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18849,32 +18840,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129459599</v>
+        <v>129459676</v>
       </c>
       <c r="B179" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18884,10 +18875,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493726</v>
+        <v>493727</v>
       </c>
       <c r="R179" t="n">
-        <v>6834891</v>
+        <v>6834879</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18946,45 +18937,54 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129460260</v>
+        <v>129458467</v>
       </c>
       <c r="B180" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493731</v>
+        <v>493646</v>
       </c>
       <c r="R180" t="n">
-        <v>6834851</v>
+        <v>6835015</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19043,45 +19043,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129476561</v>
+        <v>129459964</v>
       </c>
       <c r="B181" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493634</v>
+        <v>493726</v>
       </c>
       <c r="R181" t="n">
-        <v>6834985</v>
+        <v>6834867</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19128,57 +19128,57 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129459964</v>
+        <v>129476551</v>
       </c>
       <c r="B182" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493726</v>
+        <v>493632</v>
       </c>
       <c r="R182" t="n">
-        <v>6834867</v>
+        <v>6834827</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19225,22 +19225,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129476551</v>
+        <v>129476561</v>
       </c>
       <c r="B183" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19248,21 +19248,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19272,10 +19272,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493632</v>
+        <v>493634</v>
       </c>
       <c r="R183" t="n">
-        <v>6834827</v>
+        <v>6834985</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19634,7 +19634,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129525456</v>
+        <v>129525566</v>
       </c>
       <c r="B187" t="n">
         <v>79044</v>
@@ -19669,10 +19669,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>493893</v>
+        <v>493930</v>
       </c>
       <c r="R187" t="n">
-        <v>6834612</v>
+        <v>6834516</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19731,45 +19731,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129525479</v>
+        <v>129525456</v>
       </c>
       <c r="B188" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>493825</v>
+        <v>493893</v>
       </c>
       <c r="R188" t="n">
-        <v>6834594</v>
+        <v>6834612</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19816,57 +19816,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129525566</v>
+        <v>129525479</v>
       </c>
       <c r="B189" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>493930</v>
+        <v>493825</v>
       </c>
       <c r="R189" t="n">
-        <v>6834516</v>
+        <v>6834594</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19913,19 +19913,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129525395</v>
+        <v>129525603</v>
       </c>
       <c r="B190" t="n">
         <v>98727</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -19965,14 +19965,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>493923</v>
+        <v>493825</v>
       </c>
       <c r="R190" t="n">
-        <v>6834647</v>
+        <v>6834572</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20019,19 +20019,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129525603</v>
+        <v>129525395</v>
       </c>
       <c r="B191" t="n">
         <v>98727</v>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -20071,14 +20071,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>493825</v>
+        <v>493923</v>
       </c>
       <c r="R191" t="n">
-        <v>6834572</v>
+        <v>6834647</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20125,12 +20125,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -20534,54 +20534,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129525059</v>
+        <v>129525895</v>
       </c>
       <c r="B196" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>493851</v>
+        <v>493792</v>
       </c>
       <c r="R196" t="n">
-        <v>6834680</v>
+        <v>6834620</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20640,45 +20631,54 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129525895</v>
+        <v>129525059</v>
       </c>
       <c r="B197" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>493792</v>
+        <v>493851</v>
       </c>
       <c r="R197" t="n">
-        <v>6834620</v>
+        <v>6834680</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20834,7 +20834,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129525466</v>
+        <v>129525089</v>
       </c>
       <c r="B199" t="n">
         <v>98727</v>
@@ -20862,17 +20862,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>493832</v>
+        <v>493895</v>
       </c>
       <c r="R199" t="n">
-        <v>6834595</v>
+        <v>6834684</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20919,19 +20928,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129525089</v>
+        <v>129525466</v>
       </c>
       <c r="B200" t="n">
         <v>98727</v>
@@ -20959,26 +20968,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>493895</v>
+        <v>493832</v>
       </c>
       <c r="R200" t="n">
-        <v>6834684</v>
+        <v>6834595</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21025,66 +21025,57 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129525496</v>
+        <v>129525470</v>
       </c>
       <c r="B201" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>493821</v>
+        <v>493900</v>
       </c>
       <c r="R201" t="n">
-        <v>6834572</v>
+        <v>6834623</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21131,57 +21122,66 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129525470</v>
+        <v>129525496</v>
       </c>
       <c r="B202" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>493900</v>
+        <v>493821</v>
       </c>
       <c r="R202" t="n">
-        <v>6834623</v>
+        <v>6834572</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21228,12 +21228,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
@@ -21452,7 +21452,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129525022</v>
+        <v>129525474</v>
       </c>
       <c r="B205" t="n">
         <v>98727</v>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>493867</v>
+        <v>493908</v>
       </c>
       <c r="R205" t="n">
-        <v>6834661</v>
+        <v>6834595</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21558,7 +21558,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129525474</v>
+        <v>129525022</v>
       </c>
       <c r="B206" t="n">
         <v>98727</v>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>493908</v>
+        <v>493867</v>
       </c>
       <c r="R206" t="n">
-        <v>6834595</v>
+        <v>6834661</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21761,54 +21761,45 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129525477</v>
+        <v>129525320</v>
       </c>
       <c r="B208" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493823</v>
+        <v>493859</v>
       </c>
       <c r="R208" t="n">
-        <v>6834595</v>
+        <v>6834674</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21841,6 +21832,11 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21867,7 +21863,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129524983</v>
+        <v>129525078</v>
       </c>
       <c r="B209" t="n">
         <v>98727</v>
@@ -21911,10 +21907,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>493871</v>
+        <v>493886</v>
       </c>
       <c r="R209" t="n">
-        <v>6834690</v>
+        <v>6834673</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21973,7 +21969,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129525078</v>
+        <v>129524983</v>
       </c>
       <c r="B210" t="n">
         <v>98727</v>
@@ -22017,10 +22013,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493886</v>
+        <v>493871</v>
       </c>
       <c r="R210" t="n">
-        <v>6834673</v>
+        <v>6834690</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22079,45 +22075,54 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525320</v>
+        <v>129525477</v>
       </c>
       <c r="B211" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493859</v>
+        <v>493823</v>
       </c>
       <c r="R211" t="n">
-        <v>6834674</v>
+        <v>6834595</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22150,11 +22155,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22181,45 +22181,54 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525462</v>
+        <v>129525001</v>
       </c>
       <c r="B212" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493832</v>
+        <v>493870</v>
       </c>
       <c r="R212" t="n">
-        <v>6834595</v>
+        <v>6834690</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22278,7 +22287,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525001</v>
+        <v>129525451</v>
       </c>
       <c r="B213" t="n">
         <v>98727</v>
@@ -22306,26 +22315,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>493870</v>
+        <v>493788</v>
       </c>
       <c r="R213" t="n">
-        <v>6834690</v>
+        <v>6834656</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22384,32 +22384,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525451</v>
+        <v>129525462</v>
       </c>
       <c r="B214" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22419,10 +22419,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>493788</v>
+        <v>493832</v>
       </c>
       <c r="R214" t="n">
-        <v>6834656</v>
+        <v>6834595</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,10 +8179,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476586</v>
+        <v>129476572</v>
       </c>
       <c r="B72" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8190,21 +8190,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493684</v>
+        <v>493675</v>
       </c>
       <c r="R72" t="n">
-        <v>6834869</v>
+        <v>6834825</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,45 +8276,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129476556</v>
+        <v>129460134</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493810</v>
+        <v>493738</v>
       </c>
       <c r="R73" t="n">
-        <v>6834883</v>
+        <v>6834870</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,57 +8361,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129476572</v>
+        <v>129460004</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493675</v>
+        <v>493728</v>
       </c>
       <c r="R74" t="n">
-        <v>6834825</v>
+        <v>6834868</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,19 +8458,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129460134</v>
+        <v>129460228</v>
       </c>
       <c r="B75" t="n">
         <v>98727</v>
@@ -8498,17 +8498,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493738</v>
+        <v>493736</v>
       </c>
       <c r="R75" t="n">
-        <v>6834870</v>
+        <v>6834865</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8567,45 +8576,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129460004</v>
+        <v>129476556</v>
       </c>
       <c r="B76" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493728</v>
+        <v>493810</v>
       </c>
       <c r="R76" t="n">
-        <v>6834868</v>
+        <v>6834883</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8652,66 +8661,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129460228</v>
+        <v>129476586</v>
       </c>
       <c r="B77" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493736</v>
+        <v>493684</v>
       </c>
       <c r="R77" t="n">
-        <v>6834865</v>
+        <v>6834869</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,22 +8758,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129476585</v>
+        <v>129461154</v>
       </c>
       <c r="B78" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8781,34 +8781,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493700</v>
+        <v>493629</v>
       </c>
       <c r="R78" t="n">
-        <v>6834837</v>
+        <v>6834827</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8855,19 +8855,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129461154</v>
+        <v>129460036</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493629</v>
+        <v>493728</v>
       </c>
       <c r="R79" t="n">
-        <v>6834827</v>
+        <v>6834868</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8964,45 +8964,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129460036</v>
+        <v>129476554</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493728</v>
+        <v>493648</v>
       </c>
       <c r="R80" t="n">
-        <v>6834868</v>
+        <v>6834929</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9043,63 +9052,73 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129460662</v>
+        <v>129456176</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493658</v>
+        <v>493813</v>
       </c>
       <c r="R81" t="n">
-        <v>6834840</v>
+        <v>6834955</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9158,54 +9177,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129476554</v>
+        <v>129460662</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493648</v>
+        <v>493658</v>
       </c>
       <c r="R82" t="n">
-        <v>6834929</v>
+        <v>6834840</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9246,73 +9256,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129456176</v>
+        <v>129476585</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493813</v>
+        <v>493700</v>
       </c>
       <c r="R83" t="n">
-        <v>6834955</v>
+        <v>6834837</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9359,12 +9359,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9477,45 +9477,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129457992</v>
+        <v>129476589</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493684</v>
+        <v>493641</v>
       </c>
       <c r="R85" t="n">
-        <v>6834988</v>
+        <v>6834918</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9562,57 +9562,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129476547</v>
+        <v>129457992</v>
       </c>
       <c r="B86" t="n">
-        <v>79068</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493722</v>
+        <v>493684</v>
       </c>
       <c r="R86" t="n">
-        <v>6834900</v>
+        <v>6834988</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9659,44 +9659,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129476579</v>
+        <v>129476547</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>79068</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493687</v>
+        <v>493722</v>
       </c>
       <c r="R87" t="n">
-        <v>6834917</v>
+        <v>6834900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9768,32 +9768,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129476589</v>
+        <v>129476579</v>
       </c>
       <c r="B88" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493641</v>
+        <v>493687</v>
       </c>
       <c r="R88" t="n">
-        <v>6834918</v>
+        <v>6834917</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10271,10 +10271,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476532</v>
+        <v>129476566</v>
       </c>
       <c r="B93" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10282,21 +10282,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493619</v>
+        <v>493646</v>
       </c>
       <c r="R93" t="n">
-        <v>6834843</v>
+        <v>6834937</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476566</v>
+        <v>129476574</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493646</v>
+        <v>493702</v>
       </c>
       <c r="R94" t="n">
-        <v>6834937</v>
+        <v>6834858</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10465,45 +10465,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476574</v>
+        <v>129476555</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493702</v>
+        <v>493666</v>
       </c>
       <c r="R95" t="n">
-        <v>6834858</v>
+        <v>6834982</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10544,6 +10553,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10562,54 +10572,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476555</v>
+        <v>129476532</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493666</v>
+        <v>493619</v>
       </c>
       <c r="R96" t="n">
-        <v>6834982</v>
+        <v>6834843</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10650,7 +10651,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476537</v>
+        <v>129476560</v>
       </c>
       <c r="B98" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10777,34 +10777,41 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493659</v>
+        <v>493684</v>
       </c>
       <c r="R98" t="n">
-        <v>6834945</v>
+        <v>6834860</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10845,6 +10852,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10863,10 +10871,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129476560</v>
+        <v>129476569</v>
       </c>
       <c r="B99" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10874,41 +10882,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493684</v>
+        <v>493626</v>
       </c>
       <c r="R99" t="n">
-        <v>6834860</v>
+        <v>6834837</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10949,7 +10950,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10968,7 +10968,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476569</v>
+        <v>129476578</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493626</v>
+        <v>493718</v>
       </c>
       <c r="R100" t="n">
-        <v>6834837</v>
+        <v>6834894</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11065,7 +11065,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129476578</v>
+        <v>129455841</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11096,14 +11096,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493718</v>
+        <v>493803</v>
       </c>
       <c r="R101" t="n">
-        <v>6834894</v>
+        <v>6834901</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11150,22 +11150,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129455841</v>
+        <v>129476544</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11173,34 +11173,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493803</v>
+        <v>493634</v>
       </c>
       <c r="R102" t="n">
-        <v>6834901</v>
+        <v>6834983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11247,22 +11255,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476544</v>
+        <v>129476537</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>79634</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11270,42 +11278,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493634</v>
+        <v>493659</v>
       </c>
       <c r="R103" t="n">
-        <v>6834983</v>
+        <v>6834945</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11673,54 +11673,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129456312</v>
+        <v>129458915</v>
       </c>
       <c r="B107" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493787</v>
+        <v>493698</v>
       </c>
       <c r="R107" t="n">
-        <v>6834957</v>
+        <v>6834942</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11779,7 +11770,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129458915</v>
+        <v>129476577</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -11810,14 +11801,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493698</v>
+        <v>493707</v>
       </c>
       <c r="R108" t="n">
-        <v>6834942</v>
+        <v>6834895</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11864,57 +11855,66 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129476577</v>
+        <v>129456312</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493707</v>
+        <v>493787</v>
       </c>
       <c r="R109" t="n">
-        <v>6834895</v>
+        <v>6834957</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11961,57 +11961,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129476568</v>
+        <v>129458436</v>
       </c>
       <c r="B110" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>493619</v>
+        <v>493653</v>
       </c>
       <c r="R110" t="n">
-        <v>6834841</v>
+        <v>6835020</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12058,22 +12058,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129461581</v>
+        <v>129476538</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12081,34 +12081,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493634</v>
+        <v>493627</v>
       </c>
       <c r="R111" t="n">
-        <v>6834920</v>
+        <v>6834986</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12155,66 +12155,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129456198</v>
+        <v>129476568</v>
       </c>
       <c r="B112" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493810</v>
+        <v>493619</v>
       </c>
       <c r="R112" t="n">
-        <v>6834955</v>
+        <v>6834841</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12261,44 +12252,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129458436</v>
+        <v>129461581</v>
       </c>
       <c r="B113" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12308,10 +12299,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493653</v>
+        <v>493634</v>
       </c>
       <c r="R113" t="n">
-        <v>6835020</v>
+        <v>6834920</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12370,45 +12361,54 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129476538</v>
+        <v>129456198</v>
       </c>
       <c r="B114" t="n">
-        <v>79634</v>
+        <v>98727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493627</v>
+        <v>493810</v>
       </c>
       <c r="R114" t="n">
-        <v>6834986</v>
+        <v>6834955</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,12 +12455,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129459508</v>
+        <v>129459731</v>
       </c>
       <c r="B118" t="n">
         <v>98727</v>
@@ -12786,17 +12786,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>493729</v>
+        <v>493725</v>
       </c>
       <c r="R118" t="n">
-        <v>6834899</v>
+        <v>6834883</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12855,7 +12864,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129459731</v>
+        <v>129459774</v>
       </c>
       <c r="B119" t="n">
         <v>98727</v>
@@ -12885,7 +12894,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12899,10 +12908,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>493725</v>
+        <v>493729</v>
       </c>
       <c r="R119" t="n">
-        <v>6834883</v>
+        <v>6834877</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12961,7 +12970,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129459774</v>
+        <v>129459508</v>
       </c>
       <c r="B120" t="n">
         <v>98727</v>
@@ -12989,16 +12998,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
@@ -13008,7 +13008,7 @@
         <v>493729</v>
       </c>
       <c r="R120" t="n">
-        <v>6834877</v>
+        <v>6834899</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129461070</v>
+        <v>129456013</v>
       </c>
       <c r="B124" t="n">
         <v>98727</v>
@@ -13394,17 +13394,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493629</v>
+        <v>493806</v>
       </c>
       <c r="R124" t="n">
-        <v>6834827</v>
+        <v>6834935</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13463,7 +13472,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129457707</v>
+        <v>129456404</v>
       </c>
       <c r="B125" t="n">
         <v>98727</v>
@@ -13491,17 +13500,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493815</v>
+        <v>493780</v>
       </c>
       <c r="R125" t="n">
-        <v>6834917</v>
+        <v>6834929</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13560,7 +13578,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129456013</v>
+        <v>129456103</v>
       </c>
       <c r="B126" t="n">
         <v>98727</v>
@@ -13590,7 +13608,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13604,10 +13622,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493806</v>
+        <v>493817</v>
       </c>
       <c r="R126" t="n">
-        <v>6834935</v>
+        <v>6834939</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13666,7 +13684,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129456404</v>
+        <v>129461070</v>
       </c>
       <c r="B127" t="n">
         <v>98727</v>
@@ -13694,26 +13712,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493780</v>
+        <v>493629</v>
       </c>
       <c r="R127" t="n">
-        <v>6834929</v>
+        <v>6834827</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13772,7 +13781,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129456103</v>
+        <v>129457707</v>
       </c>
       <c r="B128" t="n">
         <v>98727</v>
@@ -13800,26 +13809,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493817</v>
+        <v>493815</v>
       </c>
       <c r="R128" t="n">
-        <v>6834939</v>
+        <v>6834917</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129476530</v>
+        <v>129458645</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,34 +13889,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493705</v>
+        <v>493662</v>
       </c>
       <c r="R129" t="n">
-        <v>6834890</v>
+        <v>6834952</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13963,19 +13963,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129458645</v>
+        <v>129455888</v>
       </c>
       <c r="B130" t="n">
         <v>79044</v>
@@ -14010,10 +14010,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493662</v>
+        <v>493811</v>
       </c>
       <c r="R130" t="n">
-        <v>6834952</v>
+        <v>6834925</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14072,10 +14072,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129455888</v>
+        <v>129476550</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14083,34 +14083,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493811</v>
+        <v>493625</v>
       </c>
       <c r="R131" t="n">
-        <v>6834925</v>
+        <v>6834820</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,66 +14157,57 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129456470</v>
+        <v>129476530</v>
       </c>
       <c r="B132" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493783</v>
+        <v>493705</v>
       </c>
       <c r="R132" t="n">
-        <v>6834931</v>
+        <v>6834890</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14263,19 +14254,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129458700</v>
+        <v>129456470</v>
       </c>
       <c r="B133" t="n">
         <v>98727</v>
@@ -14303,20 +14294,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493675</v>
+        <v>493783</v>
       </c>
       <c r="R133" t="n">
-        <v>6834963</v>
+        <v>6834931</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14372,48 +14372,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129476550</v>
+        <v>129458700</v>
       </c>
       <c r="B134" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493625</v>
+        <v>493675</v>
       </c>
       <c r="R134" t="n">
-        <v>6834820</v>
+        <v>6834963</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14457,22 +14457,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129459901</v>
+        <v>129476548</v>
       </c>
       <c r="B135" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,34 +14480,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493734</v>
+        <v>493687</v>
       </c>
       <c r="R135" t="n">
-        <v>6834875</v>
+        <v>6834930</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14554,22 +14554,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476580</v>
+        <v>129476588</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493675</v>
+        <v>493619</v>
       </c>
       <c r="R136" t="n">
-        <v>6834937</v>
+        <v>6834998</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14663,10 +14663,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476548</v>
+        <v>129476573</v>
       </c>
       <c r="B137" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14674,21 +14674,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493687</v>
+        <v>493661</v>
       </c>
       <c r="R137" t="n">
-        <v>6834930</v>
+        <v>6834848</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14760,10 +14760,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129476588</v>
+        <v>129459901</v>
       </c>
       <c r="B138" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14771,34 +14771,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493619</v>
+        <v>493734</v>
       </c>
       <c r="R138" t="n">
-        <v>6834998</v>
+        <v>6834875</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14845,19 +14845,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476573</v>
+        <v>129476580</v>
       </c>
       <c r="B139" t="n">
         <v>79044</v>
@@ -14892,10 +14892,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493661</v>
+        <v>493675</v>
       </c>
       <c r="R139" t="n">
-        <v>6834848</v>
+        <v>6834937</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15255,45 +15255,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129476540</v>
+        <v>129458085</v>
       </c>
       <c r="B143" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493723</v>
+        <v>493690</v>
       </c>
       <c r="R143" t="n">
-        <v>6834965</v>
+        <v>6834972</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15340,44 +15349,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129458803</v>
+        <v>129459852</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15387,10 +15396,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493683</v>
+        <v>493730</v>
       </c>
       <c r="R144" t="n">
-        <v>6834951</v>
+        <v>6834877</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15449,53 +15458,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129476543</v>
+        <v>129460207</v>
       </c>
       <c r="B145" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493676</v>
+        <v>493738</v>
       </c>
       <c r="R145" t="n">
-        <v>6834800</v>
+        <v>6834861</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15542,66 +15543,65 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129457830</v>
+        <v>129476543</v>
       </c>
       <c r="B146" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>493676</v>
       </c>
       <c r="R146" t="n">
-        <v>6835001</v>
+        <v>6834800</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15648,66 +15648,57 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129458085</v>
+        <v>129458803</v>
       </c>
       <c r="B147" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493690</v>
+        <v>493683</v>
       </c>
       <c r="R147" t="n">
-        <v>6834972</v>
+        <v>6834951</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15766,45 +15757,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129459852</v>
+        <v>129476540</v>
       </c>
       <c r="B148" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493730</v>
+        <v>493723</v>
       </c>
       <c r="R148" t="n">
-        <v>6834877</v>
+        <v>6834965</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15851,19 +15842,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129460207</v>
+        <v>129457830</v>
       </c>
       <c r="B149" t="n">
         <v>98727</v>
@@ -15891,17 +15882,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493738</v>
+        <v>493676</v>
       </c>
       <c r="R149" t="n">
-        <v>6834861</v>
+        <v>6835001</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15960,45 +15960,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129460421</v>
+        <v>129476535</v>
       </c>
       <c r="B150" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493728</v>
+        <v>493703</v>
       </c>
       <c r="R150" t="n">
-        <v>6834848</v>
+        <v>6834865</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16045,12 +16045,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16154,45 +16154,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129476535</v>
+        <v>129460421</v>
       </c>
       <c r="B152" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>493703</v>
+        <v>493728</v>
       </c>
       <c r="R152" t="n">
-        <v>6834865</v>
+        <v>6834848</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16239,12 +16239,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16745,10 +16745,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129476549</v>
+        <v>129459208</v>
       </c>
       <c r="B158" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16756,34 +16756,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493677</v>
+        <v>493698</v>
       </c>
       <c r="R158" t="n">
-        <v>6835005</v>
+        <v>6834943</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16830,22 +16830,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129476546</v>
+        <v>129457857</v>
       </c>
       <c r="B159" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16853,34 +16853,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493733</v>
+        <v>493676</v>
       </c>
       <c r="R159" t="n">
-        <v>6834961</v>
+        <v>6835001</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16927,19 +16927,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129459208</v>
+        <v>129458226</v>
       </c>
       <c r="B160" t="n">
         <v>79044</v>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493698</v>
+        <v>493670</v>
       </c>
       <c r="R160" t="n">
-        <v>6834943</v>
+        <v>6834981</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17230,45 +17230,57 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129458226</v>
+        <v>129476562</v>
       </c>
       <c r="B163" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493670</v>
+        <v>493676</v>
       </c>
       <c r="R163" t="n">
-        <v>6834981</v>
+        <v>6834974</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17309,63 +17321,73 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129457857</v>
+        <v>129459449</v>
       </c>
       <c r="B164" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493676</v>
+        <v>493720</v>
       </c>
       <c r="R164" t="n">
-        <v>6835001</v>
+        <v>6834910</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17424,7 +17446,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129459449</v>
+        <v>129459953</v>
       </c>
       <c r="B165" t="n">
         <v>98727</v>
@@ -17454,7 +17476,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -17468,10 +17490,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493720</v>
+        <v>493729</v>
       </c>
       <c r="R165" t="n">
-        <v>6834910</v>
+        <v>6834873</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17530,54 +17552,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129459953</v>
+        <v>129476549</v>
       </c>
       <c r="B166" t="n">
-        <v>98727</v>
+        <v>91606</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493729</v>
+        <v>493677</v>
       </c>
       <c r="R166" t="n">
-        <v>6834873</v>
+        <v>6835005</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17624,69 +17637,57 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129476562</v>
+        <v>129476546</v>
       </c>
       <c r="B167" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493676</v>
+        <v>493733</v>
       </c>
       <c r="R167" t="n">
-        <v>6834974</v>
+        <v>6834961</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17727,7 +17728,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17746,10 +17746,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476531</v>
+        <v>129476581</v>
       </c>
       <c r="B168" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17757,21 +17757,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17781,10 +17781,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493636</v>
+        <v>493677</v>
       </c>
       <c r="R168" t="n">
-        <v>6834906</v>
+        <v>6834943</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17843,7 +17843,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129476581</v>
+        <v>129476575</v>
       </c>
       <c r="B169" t="n">
         <v>79044</v>
@@ -17878,10 +17878,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493677</v>
+        <v>493728</v>
       </c>
       <c r="R169" t="n">
-        <v>6834943</v>
+        <v>6834886</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17940,7 +17940,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129476575</v>
+        <v>129476570</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -17975,10 +17975,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493728</v>
+        <v>493628</v>
       </c>
       <c r="R170" t="n">
-        <v>6834886</v>
+        <v>6834790</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18037,45 +18037,54 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476570</v>
+        <v>129456373</v>
       </c>
       <c r="B171" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493628</v>
+        <v>493796</v>
       </c>
       <c r="R171" t="n">
-        <v>6834790</v>
+        <v>6834937</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18122,22 +18131,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476587</v>
+        <v>129476531</v>
       </c>
       <c r="B172" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18145,21 +18154,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18169,10 +18178,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493659</v>
+        <v>493636</v>
       </c>
       <c r="R172" t="n">
-        <v>6834945</v>
+        <v>6834906</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18231,54 +18240,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129459653</v>
+        <v>129476587</v>
       </c>
       <c r="B173" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493740</v>
+        <v>493659</v>
       </c>
       <c r="R173" t="n">
-        <v>6834887</v>
+        <v>6834945</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18325,19 +18325,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129459536</v>
+        <v>129459653</v>
       </c>
       <c r="B174" t="n">
         <v>98727</v>
@@ -18365,17 +18365,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493723</v>
+        <v>493740</v>
       </c>
       <c r="R174" t="n">
-        <v>6834898</v>
+        <v>6834887</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18434,7 +18443,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129456373</v>
+        <v>129459536</v>
       </c>
       <c r="B175" t="n">
         <v>98727</v>
@@ -18462,26 +18471,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493796</v>
+        <v>493723</v>
       </c>
       <c r="R175" t="n">
-        <v>6834937</v>
+        <v>6834898</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19043,45 +19043,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129459964</v>
+        <v>129476561</v>
       </c>
       <c r="B181" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493726</v>
+        <v>493634</v>
       </c>
       <c r="R181" t="n">
-        <v>6834867</v>
+        <v>6834985</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19128,57 +19128,57 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129476551</v>
+        <v>129459964</v>
       </c>
       <c r="B182" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493632</v>
+        <v>493726</v>
       </c>
       <c r="R182" t="n">
-        <v>6834827</v>
+        <v>6834867</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19225,22 +19225,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129476561</v>
+        <v>129476551</v>
       </c>
       <c r="B183" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19248,21 +19248,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19272,10 +19272,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493634</v>
+        <v>493632</v>
       </c>
       <c r="R183" t="n">
-        <v>6834985</v>
+        <v>6834827</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19731,45 +19731,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129525456</v>
+        <v>129525479</v>
       </c>
       <c r="B188" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>493893</v>
+        <v>493825</v>
       </c>
       <c r="R188" t="n">
-        <v>6834612</v>
+        <v>6834594</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19816,57 +19816,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129525479</v>
+        <v>129525456</v>
       </c>
       <c r="B189" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>493825</v>
+        <v>493893</v>
       </c>
       <c r="R189" t="n">
-        <v>6834594</v>
+        <v>6834612</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19913,12 +19913,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -20331,7 +20331,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129525020</v>
+        <v>129525370</v>
       </c>
       <c r="B194" t="n">
         <v>98727</v>
@@ -20359,26 +20359,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>493860</v>
+        <v>493942</v>
       </c>
       <c r="R194" t="n">
-        <v>6834704</v>
+        <v>6834657</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20425,19 +20416,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129525370</v>
+        <v>129525020</v>
       </c>
       <c r="B195" t="n">
         <v>98727</v>
@@ -20465,17 +20456,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>493942</v>
+        <v>493860</v>
       </c>
       <c r="R195" t="n">
-        <v>6834657</v>
+        <v>6834704</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20522,12 +20522,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -21037,45 +21037,54 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129525470</v>
+        <v>129525496</v>
       </c>
       <c r="B201" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>493900</v>
+        <v>493821</v>
       </c>
       <c r="R201" t="n">
-        <v>6834623</v>
+        <v>6834572</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21122,66 +21131,57 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129525496</v>
+        <v>129525470</v>
       </c>
       <c r="B202" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>493821</v>
+        <v>493900</v>
       </c>
       <c r="R202" t="n">
-        <v>6834572</v>
+        <v>6834623</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21228,19 +21228,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129525041</v>
+        <v>129525012</v>
       </c>
       <c r="B203" t="n">
         <v>98727</v>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -21280,14 +21280,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>493881</v>
+        <v>493866</v>
       </c>
       <c r="R203" t="n">
-        <v>6834662</v>
+        <v>6834688</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21334,19 +21334,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129525012</v>
+        <v>129525041</v>
       </c>
       <c r="B204" t="n">
         <v>98727</v>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -21386,14 +21386,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>493866</v>
+        <v>493881</v>
       </c>
       <c r="R204" t="n">
-        <v>6834688</v>
+        <v>6834662</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21440,12 +21440,12 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
@@ -21761,45 +21761,54 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129525320</v>
+        <v>129525477</v>
       </c>
       <c r="B208" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493859</v>
+        <v>493823</v>
       </c>
       <c r="R208" t="n">
-        <v>6834674</v>
+        <v>6834595</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21832,11 +21841,6 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22075,54 +22079,45 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525477</v>
+        <v>129525320</v>
       </c>
       <c r="B211" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493823</v>
+        <v>493859</v>
       </c>
       <c r="R211" t="n">
-        <v>6834595</v>
+        <v>6834674</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22155,6 +22150,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22181,54 +22181,45 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525001</v>
+        <v>129525462</v>
       </c>
       <c r="B212" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493870</v>
+        <v>493832</v>
       </c>
       <c r="R212" t="n">
-        <v>6834690</v>
+        <v>6834595</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22287,32 +22278,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525451</v>
+        <v>129525429</v>
       </c>
       <c r="B213" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22384,45 +22375,54 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525462</v>
+        <v>129525001</v>
       </c>
       <c r="B214" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>493832</v>
+        <v>493870</v>
       </c>
       <c r="R214" t="n">
-        <v>6834595</v>
+        <v>6834690</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22481,32 +22481,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129525429</v>
+        <v>129525451</v>
       </c>
       <c r="B215" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,10 +8179,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476572</v>
+        <v>129476556</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8190,21 +8190,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493675</v>
+        <v>493810</v>
       </c>
       <c r="R72" t="n">
-        <v>6834825</v>
+        <v>6834883</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,45 +8276,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129460134</v>
+        <v>129476586</v>
       </c>
       <c r="B73" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493738</v>
+        <v>493684</v>
       </c>
       <c r="R73" t="n">
-        <v>6834870</v>
+        <v>6834869</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,57 +8361,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460004</v>
+        <v>129476572</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493728</v>
+        <v>493675</v>
       </c>
       <c r="R74" t="n">
-        <v>6834868</v>
+        <v>6834825</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,19 +8458,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129460228</v>
+        <v>129460134</v>
       </c>
       <c r="B75" t="n">
         <v>98727</v>
@@ -8498,26 +8498,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493736</v>
+        <v>493738</v>
       </c>
       <c r="R75" t="n">
-        <v>6834865</v>
+        <v>6834870</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,45 +8567,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129476556</v>
+        <v>129460004</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493810</v>
+        <v>493728</v>
       </c>
       <c r="R76" t="n">
-        <v>6834883</v>
+        <v>6834868</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8661,57 +8652,66 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129476586</v>
+        <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493684</v>
+        <v>493736</v>
       </c>
       <c r="R77" t="n">
-        <v>6834869</v>
+        <v>6834865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,22 +8758,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129461154</v>
+        <v>129476585</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8781,34 +8781,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493629</v>
+        <v>493700</v>
       </c>
       <c r="R78" t="n">
-        <v>6834827</v>
+        <v>6834837</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8855,12 +8855,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8964,54 +8964,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129476554</v>
+        <v>129460662</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493648</v>
+        <v>493658</v>
       </c>
       <c r="R80" t="n">
-        <v>6834929</v>
+        <v>6834840</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9052,73 +9043,72 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129456176</v>
+        <v>129476554</v>
       </c>
       <c r="B81" t="n">
-        <v>98727</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493813</v>
+        <v>493648</v>
       </c>
       <c r="R81" t="n">
-        <v>6834955</v>
+        <v>6834929</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9159,63 +9149,73 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129460662</v>
+        <v>129456176</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493658</v>
+        <v>493813</v>
       </c>
       <c r="R82" t="n">
-        <v>6834840</v>
+        <v>6834955</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9274,45 +9274,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129476585</v>
+        <v>129457973</v>
       </c>
       <c r="B83" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493700</v>
+        <v>493684</v>
       </c>
       <c r="R83" t="n">
-        <v>6834837</v>
+        <v>6834986</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9359,66 +9368,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129457973</v>
+        <v>129461154</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493684</v>
+        <v>493629</v>
       </c>
       <c r="R84" t="n">
-        <v>6834986</v>
+        <v>6834827</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9671,32 +9671,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129476547</v>
+        <v>129476579</v>
       </c>
       <c r="B87" t="n">
-        <v>79068</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493722</v>
+        <v>493687</v>
       </c>
       <c r="R87" t="n">
-        <v>6834900</v>
+        <v>6834917</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9768,32 +9768,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129476579</v>
+        <v>129476547</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>79068</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493687</v>
+        <v>493722</v>
       </c>
       <c r="R88" t="n">
-        <v>6834917</v>
+        <v>6834900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10174,45 +10174,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129476583</v>
+        <v>129476555</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>493664</v>
+        <v>493666</v>
       </c>
       <c r="R92" t="n">
-        <v>6834992</v>
+        <v>6834982</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10253,6 +10262,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10465,54 +10475,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476555</v>
+        <v>129476532</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493666</v>
+        <v>493619</v>
       </c>
       <c r="R95" t="n">
-        <v>6834982</v>
+        <v>6834843</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10553,7 +10554,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10572,10 +10572,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476532</v>
+        <v>129476583</v>
       </c>
       <c r="B96" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493619</v>
+        <v>493664</v>
       </c>
       <c r="R96" t="n">
-        <v>6834843</v>
+        <v>6834992</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476560</v>
+        <v>129476537</v>
       </c>
       <c r="B98" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10777,41 +10777,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493684</v>
+        <v>493659</v>
       </c>
       <c r="R98" t="n">
-        <v>6834860</v>
+        <v>6834945</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10852,7 +10845,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10871,10 +10863,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129476569</v>
+        <v>129476560</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10882,34 +10874,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493626</v>
+        <v>493684</v>
       </c>
       <c r="R99" t="n">
-        <v>6834837</v>
+        <v>6834860</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10950,6 +10949,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10968,7 +10968,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476578</v>
+        <v>129476569</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493718</v>
+        <v>493626</v>
       </c>
       <c r="R100" t="n">
-        <v>6834894</v>
+        <v>6834837</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11065,7 +11065,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129455841</v>
+        <v>129476578</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11096,14 +11096,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493803</v>
+        <v>493718</v>
       </c>
       <c r="R101" t="n">
-        <v>6834901</v>
+        <v>6834894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11150,22 +11150,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476544</v>
+        <v>129455841</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11173,42 +11173,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493634</v>
+        <v>493803</v>
       </c>
       <c r="R102" t="n">
-        <v>6834983</v>
+        <v>6834901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11255,22 +11247,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476537</v>
+        <v>129476544</v>
       </c>
       <c r="B103" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11278,34 +11270,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493659</v>
+        <v>493634</v>
       </c>
       <c r="R103" t="n">
-        <v>6834945</v>
+        <v>6834983</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11673,45 +11673,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129458915</v>
+        <v>129456312</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493698</v>
+        <v>493787</v>
       </c>
       <c r="R107" t="n">
-        <v>6834942</v>
+        <v>6834957</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11867,54 +11876,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129456312</v>
+        <v>129458915</v>
       </c>
       <c r="B109" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493787</v>
+        <v>493698</v>
       </c>
       <c r="R109" t="n">
-        <v>6834957</v>
+        <v>6834942</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11973,7 +11973,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129458436</v>
+        <v>129456198</v>
       </c>
       <c r="B110" t="n">
         <v>98727</v>
@@ -12001,17 +12001,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>493653</v>
+        <v>493810</v>
       </c>
       <c r="R110" t="n">
-        <v>6835020</v>
+        <v>6834955</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12070,45 +12079,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129476538</v>
+        <v>129458436</v>
       </c>
       <c r="B111" t="n">
-        <v>79634</v>
+        <v>98727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493627</v>
+        <v>493653</v>
       </c>
       <c r="R111" t="n">
-        <v>6834986</v>
+        <v>6835020</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12155,12 +12164,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12361,54 +12370,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129456198</v>
+        <v>129476538</v>
       </c>
       <c r="B114" t="n">
-        <v>98727</v>
+        <v>79634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493810</v>
+        <v>493627</v>
       </c>
       <c r="R114" t="n">
-        <v>6834955</v>
+        <v>6834986</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,22 +12455,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129476558</v>
+        <v>129460271</v>
       </c>
       <c r="B115" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12478,34 +12478,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493629</v>
+        <v>493731</v>
       </c>
       <c r="R115" t="n">
-        <v>6834823</v>
+        <v>6834853</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12552,19 +12552,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129460271</v>
+        <v>129476584</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12595,14 +12595,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493731</v>
+        <v>493670</v>
       </c>
       <c r="R116" t="n">
-        <v>6834853</v>
+        <v>6834995</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12649,22 +12649,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129476584</v>
+        <v>129476558</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12672,21 +12672,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12696,10 +12696,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493670</v>
+        <v>493629</v>
       </c>
       <c r="R117" t="n">
-        <v>6834995</v>
+        <v>6834823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13067,32 +13067,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129476590</v>
+        <v>129476541</v>
       </c>
       <c r="B121" t="n">
-        <v>92835</v>
+        <v>91553</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493628</v>
+        <v>493780</v>
       </c>
       <c r="R121" t="n">
-        <v>6834891</v>
+        <v>6834984</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13164,32 +13164,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476541</v>
+        <v>129476590</v>
       </c>
       <c r="B122" t="n">
-        <v>91553</v>
+        <v>92835</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493780</v>
+        <v>493628</v>
       </c>
       <c r="R122" t="n">
-        <v>6834984</v>
+        <v>6834891</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129456013</v>
+        <v>129461070</v>
       </c>
       <c r="B124" t="n">
         <v>98727</v>
@@ -13394,26 +13394,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493806</v>
+        <v>493629</v>
       </c>
       <c r="R124" t="n">
-        <v>6834935</v>
+        <v>6834827</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13472,7 +13463,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129456404</v>
+        <v>129457707</v>
       </c>
       <c r="B125" t="n">
         <v>98727</v>
@@ -13500,26 +13491,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493780</v>
+        <v>493815</v>
       </c>
       <c r="R125" t="n">
-        <v>6834929</v>
+        <v>6834917</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13578,7 +13560,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129456103</v>
+        <v>129456013</v>
       </c>
       <c r="B126" t="n">
         <v>98727</v>
@@ -13608,7 +13590,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13622,10 +13604,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493817</v>
+        <v>493806</v>
       </c>
       <c r="R126" t="n">
-        <v>6834939</v>
+        <v>6834935</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13684,7 +13666,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129461070</v>
+        <v>129456404</v>
       </c>
       <c r="B127" t="n">
         <v>98727</v>
@@ -13712,17 +13694,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493629</v>
+        <v>493780</v>
       </c>
       <c r="R127" t="n">
-        <v>6834827</v>
+        <v>6834929</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13781,7 +13772,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129457707</v>
+        <v>129456103</v>
       </c>
       <c r="B128" t="n">
         <v>98727</v>
@@ -13809,17 +13800,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493815</v>
+        <v>493817</v>
       </c>
       <c r="R128" t="n">
-        <v>6834917</v>
+        <v>6834939</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129458645</v>
+        <v>129476530</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,34 +13889,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493662</v>
+        <v>493705</v>
       </c>
       <c r="R129" t="n">
-        <v>6834952</v>
+        <v>6834890</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13963,12 +13963,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14072,45 +14072,54 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129476550</v>
+        <v>129456470</v>
       </c>
       <c r="B131" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493625</v>
+        <v>493783</v>
       </c>
       <c r="R131" t="n">
-        <v>6834820</v>
+        <v>6834931</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,60 +14166,60 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129476530</v>
+        <v>129458700</v>
       </c>
       <c r="B132" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493705</v>
+        <v>493675</v>
       </c>
       <c r="R132" t="n">
-        <v>6834890</v>
+        <v>6834963</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14254,66 +14263,57 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129456470</v>
+        <v>129476550</v>
       </c>
       <c r="B133" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493783</v>
+        <v>493625</v>
       </c>
       <c r="R133" t="n">
-        <v>6834931</v>
+        <v>6834820</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14360,44 +14360,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129458700</v>
+        <v>129458645</v>
       </c>
       <c r="B134" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14407,13 +14407,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493675</v>
+        <v>493662</v>
       </c>
       <c r="R134" t="n">
-        <v>6834963</v>
+        <v>6834952</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476548</v>
+        <v>129476588</v>
       </c>
       <c r="B135" t="n">
-        <v>91606</v>
+        <v>78710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493687</v>
+        <v>493619</v>
       </c>
       <c r="R135" t="n">
-        <v>6834930</v>
+        <v>6834998</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,10 +14566,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476588</v>
+        <v>129476548</v>
       </c>
       <c r="B136" t="n">
-        <v>78710</v>
+        <v>91606</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493619</v>
+        <v>493687</v>
       </c>
       <c r="R136" t="n">
-        <v>6834998</v>
+        <v>6834930</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15255,54 +15255,53 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129458085</v>
+        <v>129476543</v>
       </c>
       <c r="B143" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493690</v>
+        <v>493676</v>
       </c>
       <c r="R143" t="n">
-        <v>6834972</v>
+        <v>6834800</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,19 +15348,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129459852</v>
+        <v>129457830</v>
       </c>
       <c r="B144" t="n">
         <v>98727</v>
@@ -15389,17 +15388,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493730</v>
+        <v>493676</v>
       </c>
       <c r="R144" t="n">
-        <v>6834877</v>
+        <v>6835001</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15458,7 +15466,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129460207</v>
+        <v>129458085</v>
       </c>
       <c r="B145" t="n">
         <v>98727</v>
@@ -15486,17 +15494,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493738</v>
+        <v>493690</v>
       </c>
       <c r="R145" t="n">
-        <v>6834861</v>
+        <v>6834972</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15555,53 +15572,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129476543</v>
+        <v>129459852</v>
       </c>
       <c r="B146" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493676</v>
+        <v>493730</v>
       </c>
       <c r="R146" t="n">
-        <v>6834800</v>
+        <v>6834877</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15648,44 +15657,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129458803</v>
+        <v>129460207</v>
       </c>
       <c r="B147" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15695,10 +15704,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493683</v>
+        <v>493738</v>
       </c>
       <c r="R147" t="n">
-        <v>6834951</v>
+        <v>6834861</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15854,54 +15863,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129457830</v>
+        <v>129458803</v>
       </c>
       <c r="B149" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493676</v>
+        <v>493683</v>
       </c>
       <c r="R149" t="n">
-        <v>6835001</v>
+        <v>6834951</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15960,10 +15960,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476535</v>
+        <v>129476539</v>
       </c>
       <c r="B150" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15971,21 +15971,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493703</v>
+        <v>493652</v>
       </c>
       <c r="R150" t="n">
-        <v>6834865</v>
+        <v>6834985</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16057,10 +16057,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476539</v>
+        <v>129476535</v>
       </c>
       <c r="B151" t="n">
-        <v>90585</v>
+        <v>79663</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16068,21 +16068,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493652</v>
+        <v>493703</v>
       </c>
       <c r="R151" t="n">
-        <v>6834985</v>
+        <v>6834865</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16445,45 +16445,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129476576</v>
+        <v>129460288</v>
       </c>
       <c r="B155" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493725</v>
+        <v>493733</v>
       </c>
       <c r="R155" t="n">
-        <v>6834888</v>
+        <v>6834848</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16530,19 +16530,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129460288</v>
+        <v>129458972</v>
       </c>
       <c r="B156" t="n">
         <v>98727</v>
@@ -16570,17 +16570,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493733</v>
+        <v>493700</v>
       </c>
       <c r="R156" t="n">
-        <v>6834848</v>
+        <v>6834942</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16639,54 +16648,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129458972</v>
+        <v>129476576</v>
       </c>
       <c r="B157" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493700</v>
+        <v>493725</v>
       </c>
       <c r="R157" t="n">
-        <v>6834942</v>
+        <v>6834888</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16733,22 +16733,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129459208</v>
+        <v>129476546</v>
       </c>
       <c r="B158" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16756,34 +16756,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493698</v>
+        <v>493733</v>
       </c>
       <c r="R158" t="n">
-        <v>6834943</v>
+        <v>6834961</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16830,22 +16830,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129457857</v>
+        <v>129476549</v>
       </c>
       <c r="B159" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16853,34 +16853,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493676</v>
+        <v>493677</v>
       </c>
       <c r="R159" t="n">
-        <v>6835001</v>
+        <v>6835005</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16927,22 +16927,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129458226</v>
+        <v>129476533</v>
       </c>
       <c r="B160" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16950,34 +16950,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493670</v>
+        <v>493678</v>
       </c>
       <c r="R160" t="n">
-        <v>6834981</v>
+        <v>6834780</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17024,22 +17024,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129476533</v>
+        <v>129459208</v>
       </c>
       <c r="B161" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17047,34 +17047,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>493678</v>
+        <v>493698</v>
       </c>
       <c r="R161" t="n">
-        <v>6834780</v>
+        <v>6834943</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17121,12 +17121,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17230,57 +17230,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129476562</v>
+        <v>129458226</v>
       </c>
       <c r="B163" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493676</v>
+        <v>493670</v>
       </c>
       <c r="R163" t="n">
-        <v>6834974</v>
+        <v>6834981</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17321,19 +17309,18 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17552,10 +17539,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129476549</v>
+        <v>129457857</v>
       </c>
       <c r="B166" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17563,34 +17550,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493677</v>
+        <v>493676</v>
       </c>
       <c r="R166" t="n">
-        <v>6835005</v>
+        <v>6835001</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17637,57 +17624,69 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129476546</v>
+        <v>129476562</v>
       </c>
       <c r="B167" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>493733</v>
+        <v>493676</v>
       </c>
       <c r="R167" t="n">
-        <v>6834961</v>
+        <v>6834974</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17728,6 +17727,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17746,10 +17746,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476581</v>
+        <v>129476587</v>
       </c>
       <c r="B168" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17757,21 +17757,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17781,10 +17781,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493677</v>
+        <v>493659</v>
       </c>
       <c r="R168" t="n">
-        <v>6834943</v>
+        <v>6834945</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17843,7 +17843,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129476575</v>
+        <v>129476581</v>
       </c>
       <c r="B169" t="n">
         <v>79044</v>
@@ -17878,10 +17878,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493728</v>
+        <v>493677</v>
       </c>
       <c r="R169" t="n">
-        <v>6834886</v>
+        <v>6834943</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17940,7 +17940,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129476570</v>
+        <v>129476575</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -17975,10 +17975,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493628</v>
+        <v>493728</v>
       </c>
       <c r="R170" t="n">
-        <v>6834790</v>
+        <v>6834886</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18037,54 +18037,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129456373</v>
+        <v>129476570</v>
       </c>
       <c r="B171" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493796</v>
+        <v>493628</v>
       </c>
       <c r="R171" t="n">
-        <v>6834937</v>
+        <v>6834790</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18131,12 +18122,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18240,45 +18231,54 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129476587</v>
+        <v>129459653</v>
       </c>
       <c r="B173" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493659</v>
+        <v>493740</v>
       </c>
       <c r="R173" t="n">
-        <v>6834945</v>
+        <v>6834887</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18325,19 +18325,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129459653</v>
+        <v>129459536</v>
       </c>
       <c r="B174" t="n">
         <v>98727</v>
@@ -18365,26 +18365,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493740</v>
+        <v>493723</v>
       </c>
       <c r="R174" t="n">
-        <v>6834887</v>
+        <v>6834898</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18443,7 +18434,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129459536</v>
+        <v>129456373</v>
       </c>
       <c r="B175" t="n">
         <v>98727</v>
@@ -18471,17 +18462,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493723</v>
+        <v>493796</v>
       </c>
       <c r="R175" t="n">
-        <v>6834898</v>
+        <v>6834937</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18540,45 +18540,54 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129459599</v>
+        <v>129456055</v>
       </c>
       <c r="B176" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493726</v>
+        <v>493817</v>
       </c>
       <c r="R176" t="n">
-        <v>6834891</v>
+        <v>6834930</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,32 +18646,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129460260</v>
+        <v>129459676</v>
       </c>
       <c r="B177" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18672,10 +18681,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493731</v>
+        <v>493727</v>
       </c>
       <c r="R177" t="n">
-        <v>6834851</v>
+        <v>6834879</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18734,7 +18743,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129456055</v>
+        <v>129458467</v>
       </c>
       <c r="B178" t="n">
         <v>98727</v>
@@ -18764,7 +18773,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -18778,10 +18787,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493817</v>
+        <v>493646</v>
       </c>
       <c r="R178" t="n">
-        <v>6834930</v>
+        <v>6835015</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18840,32 +18849,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129459676</v>
+        <v>129459599</v>
       </c>
       <c r="B179" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18875,10 +18884,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493727</v>
+        <v>493726</v>
       </c>
       <c r="R179" t="n">
-        <v>6834879</v>
+        <v>6834891</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18937,54 +18946,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129458467</v>
+        <v>129460260</v>
       </c>
       <c r="B180" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493646</v>
+        <v>493731</v>
       </c>
       <c r="R180" t="n">
-        <v>6835015</v>
+        <v>6834851</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19043,45 +19043,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129476561</v>
+        <v>129459964</v>
       </c>
       <c r="B181" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493634</v>
+        <v>493726</v>
       </c>
       <c r="R181" t="n">
-        <v>6834985</v>
+        <v>6834867</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19128,57 +19128,57 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129459964</v>
+        <v>129476551</v>
       </c>
       <c r="B182" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493726</v>
+        <v>493632</v>
       </c>
       <c r="R182" t="n">
-        <v>6834867</v>
+        <v>6834827</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19225,22 +19225,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129476551</v>
+        <v>129476561</v>
       </c>
       <c r="B183" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19248,21 +19248,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19272,10 +19272,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493632</v>
+        <v>493634</v>
       </c>
       <c r="R183" t="n">
-        <v>6834827</v>
+        <v>6834985</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19731,45 +19731,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129525479</v>
+        <v>129525456</v>
       </c>
       <c r="B188" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>493825</v>
+        <v>493893</v>
       </c>
       <c r="R188" t="n">
-        <v>6834594</v>
+        <v>6834612</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19816,57 +19816,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129525456</v>
+        <v>129525479</v>
       </c>
       <c r="B189" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>493893</v>
+        <v>493825</v>
       </c>
       <c r="R189" t="n">
-        <v>6834612</v>
+        <v>6834594</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19913,19 +19913,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129525603</v>
+        <v>129525395</v>
       </c>
       <c r="B190" t="n">
         <v>98727</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -19965,14 +19965,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>493825</v>
+        <v>493923</v>
       </c>
       <c r="R190" t="n">
-        <v>6834572</v>
+        <v>6834647</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20019,19 +20019,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129525395</v>
+        <v>129525603</v>
       </c>
       <c r="B191" t="n">
         <v>98727</v>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -20071,14 +20071,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>493923</v>
+        <v>493825</v>
       </c>
       <c r="R191" t="n">
-        <v>6834647</v>
+        <v>6834572</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20125,12 +20125,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -20834,7 +20834,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129525089</v>
+        <v>129525466</v>
       </c>
       <c r="B199" t="n">
         <v>98727</v>
@@ -20862,26 +20862,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>493895</v>
+        <v>493832</v>
       </c>
       <c r="R199" t="n">
-        <v>6834684</v>
+        <v>6834595</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20928,19 +20919,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129525466</v>
+        <v>129525089</v>
       </c>
       <c r="B200" t="n">
         <v>98727</v>
@@ -20968,17 +20959,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>493832</v>
+        <v>493895</v>
       </c>
       <c r="R200" t="n">
-        <v>6834595</v>
+        <v>6834684</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21025,66 +21025,57 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129525496</v>
+        <v>129525470</v>
       </c>
       <c r="B201" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>493821</v>
+        <v>493900</v>
       </c>
       <c r="R201" t="n">
-        <v>6834572</v>
+        <v>6834623</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21131,57 +21122,66 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129525470</v>
+        <v>129525496</v>
       </c>
       <c r="B202" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>493900</v>
+        <v>493821</v>
       </c>
       <c r="R202" t="n">
-        <v>6834623</v>
+        <v>6834572</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21228,19 +21228,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129525012</v>
+        <v>129525041</v>
       </c>
       <c r="B203" t="n">
         <v>98727</v>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -21280,14 +21280,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>493866</v>
+        <v>493881</v>
       </c>
       <c r="R203" t="n">
-        <v>6834688</v>
+        <v>6834662</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21334,19 +21334,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129525041</v>
+        <v>129525012</v>
       </c>
       <c r="B204" t="n">
         <v>98727</v>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -21386,14 +21386,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>493881</v>
+        <v>493866</v>
       </c>
       <c r="R204" t="n">
-        <v>6834662</v>
+        <v>6834688</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21440,19 +21440,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129525474</v>
+        <v>129525022</v>
       </c>
       <c r="B205" t="n">
         <v>98727</v>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>493908</v>
+        <v>493867</v>
       </c>
       <c r="R205" t="n">
-        <v>6834595</v>
+        <v>6834661</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21558,7 +21558,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129525022</v>
+        <v>129525474</v>
       </c>
       <c r="B206" t="n">
         <v>98727</v>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>493867</v>
+        <v>493908</v>
       </c>
       <c r="R206" t="n">
-        <v>6834661</v>
+        <v>6834595</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21664,45 +21664,54 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525442</v>
+        <v>129525477</v>
       </c>
       <c r="B207" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493925</v>
+        <v>493823</v>
       </c>
       <c r="R207" t="n">
-        <v>6834617</v>
+        <v>6834595</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21749,19 +21758,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129525477</v>
+        <v>129524983</v>
       </c>
       <c r="B208" t="n">
         <v>98727</v>
@@ -21791,7 +21800,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -21801,14 +21810,14 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493823</v>
+        <v>493871</v>
       </c>
       <c r="R208" t="n">
-        <v>6834595</v>
+        <v>6834690</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21855,66 +21864,57 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129525078</v>
+        <v>129525320</v>
       </c>
       <c r="B209" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>493886</v>
+        <v>493859</v>
       </c>
       <c r="R209" t="n">
-        <v>6834673</v>
+        <v>6834674</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21949,6 +21949,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
@@ -21961,66 +21966,57 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129524983</v>
+        <v>129525442</v>
       </c>
       <c r="B210" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493871</v>
+        <v>493925</v>
       </c>
       <c r="R210" t="n">
-        <v>6834690</v>
+        <v>6834617</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22079,45 +22075,54 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525320</v>
+        <v>129525078</v>
       </c>
       <c r="B211" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493859</v>
+        <v>493886</v>
       </c>
       <c r="R211" t="n">
-        <v>6834674</v>
+        <v>6834673</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22152,11 +22157,6 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
@@ -22169,44 +22169,44 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525462</v>
+        <v>129525429</v>
       </c>
       <c r="B212" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22216,10 +22216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493832</v>
+        <v>493788</v>
       </c>
       <c r="R212" t="n">
-        <v>6834595</v>
+        <v>6834656</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22278,45 +22278,54 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525429</v>
+        <v>129525001</v>
       </c>
       <c r="B213" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>493788</v>
+        <v>493870</v>
       </c>
       <c r="R213" t="n">
-        <v>6834656</v>
+        <v>6834690</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22375,7 +22384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525001</v>
+        <v>129525451</v>
       </c>
       <c r="B214" t="n">
         <v>98727</v>
@@ -22403,26 +22412,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>493870</v>
+        <v>493788</v>
       </c>
       <c r="R214" t="n">
-        <v>6834690</v>
+        <v>6834656</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22481,32 +22481,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129525451</v>
+        <v>129525462</v>
       </c>
       <c r="B215" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22516,10 +22516,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>493788</v>
+        <v>493832</v>
       </c>
       <c r="R215" t="n">
-        <v>6834656</v>
+        <v>6834595</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,10 +8179,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476556</v>
+        <v>129476572</v>
       </c>
       <c r="B72" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8190,21 +8190,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493810</v>
+        <v>493675</v>
       </c>
       <c r="R72" t="n">
-        <v>6834883</v>
+        <v>6834825</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129476586</v>
+        <v>129476556</v>
       </c>
       <c r="B73" t="n">
-        <v>78710</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493684</v>
+        <v>493810</v>
       </c>
       <c r="R73" t="n">
-        <v>6834869</v>
+        <v>6834883</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8373,45 +8373,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129476572</v>
+        <v>129460134</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493675</v>
+        <v>493738</v>
       </c>
       <c r="R74" t="n">
-        <v>6834825</v>
+        <v>6834870</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,57 +8458,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129460134</v>
+        <v>129476586</v>
       </c>
       <c r="B75" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493738</v>
+        <v>493684</v>
       </c>
       <c r="R75" t="n">
-        <v>6834870</v>
+        <v>6834869</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8555,12 +8555,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8867,45 +8867,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129460036</v>
+        <v>129457973</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493728</v>
+        <v>493684</v>
       </c>
       <c r="R79" t="n">
-        <v>6834868</v>
+        <v>6834986</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8964,45 +8973,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129460662</v>
+        <v>129456176</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493658</v>
+        <v>493813</v>
       </c>
       <c r="R80" t="n">
-        <v>6834840</v>
+        <v>6834955</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9061,54 +9079,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129476554</v>
+        <v>129461154</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493648</v>
+        <v>493629</v>
       </c>
       <c r="R81" t="n">
-        <v>6834929</v>
+        <v>6834827</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9149,73 +9158,63 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129456176</v>
+        <v>129460036</v>
       </c>
       <c r="B82" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493813</v>
+        <v>493728</v>
       </c>
       <c r="R82" t="n">
-        <v>6834955</v>
+        <v>6834868</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9274,54 +9273,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129457973</v>
+        <v>129460662</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493684</v>
+        <v>493658</v>
       </c>
       <c r="R83" t="n">
-        <v>6834986</v>
+        <v>6834840</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9380,45 +9370,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129461154</v>
+        <v>129476554</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493629</v>
+        <v>493648</v>
       </c>
       <c r="R84" t="n">
-        <v>6834827</v>
+        <v>6834929</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9459,50 +9458,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129476589</v>
+        <v>129476579</v>
       </c>
       <c r="B85" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9512,10 +9512,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493641</v>
+        <v>493687</v>
       </c>
       <c r="R85" t="n">
-        <v>6834918</v>
+        <v>6834917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9574,45 +9574,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129457992</v>
+        <v>129476589</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493684</v>
+        <v>493641</v>
       </c>
       <c r="R86" t="n">
-        <v>6834988</v>
+        <v>6834918</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9659,19 +9659,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129476579</v>
+        <v>129457992</v>
       </c>
       <c r="B87" t="n">
         <v>79044</v>
@@ -9702,14 +9702,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493687</v>
+        <v>493684</v>
       </c>
       <c r="R87" t="n">
-        <v>6834917</v>
+        <v>6834988</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9756,12 +9756,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129457913</v>
+        <v>129457745</v>
       </c>
       <c r="B89" t="n">
         <v>98727</v>
@@ -9893,17 +9893,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493686</v>
+        <v>493678</v>
       </c>
       <c r="R89" t="n">
-        <v>6834989</v>
+        <v>6835020</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10068,7 +10077,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129457745</v>
+        <v>129457913</v>
       </c>
       <c r="B91" t="n">
         <v>98727</v>
@@ -10096,26 +10105,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>493678</v>
+        <v>493686</v>
       </c>
       <c r="R91" t="n">
-        <v>6835020</v>
+        <v>6834989</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10281,7 +10281,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476566</v>
+        <v>129476583</v>
       </c>
       <c r="B93" t="n">
         <v>79044</v>
@@ -10316,10 +10316,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493646</v>
+        <v>493664</v>
       </c>
       <c r="R93" t="n">
-        <v>6834937</v>
+        <v>6834992</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10378,10 +10378,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476574</v>
+        <v>129476532</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10389,21 +10389,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10413,10 +10413,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493702</v>
+        <v>493619</v>
       </c>
       <c r="R94" t="n">
-        <v>6834858</v>
+        <v>6834843</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10475,10 +10475,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476532</v>
+        <v>129476566</v>
       </c>
       <c r="B95" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10486,21 +10486,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493619</v>
+        <v>493646</v>
       </c>
       <c r="R95" t="n">
-        <v>6834843</v>
+        <v>6834937</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10572,7 +10572,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476583</v>
+        <v>129476574</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493664</v>
+        <v>493702</v>
       </c>
       <c r="R96" t="n">
-        <v>6834992</v>
+        <v>6834858</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10766,45 +10766,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476537</v>
+        <v>129458098</v>
       </c>
       <c r="B98" t="n">
-        <v>79634</v>
+        <v>98727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493659</v>
+        <v>493682</v>
       </c>
       <c r="R98" t="n">
-        <v>6834945</v>
+        <v>6834975</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10851,64 +10860,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129476560</v>
+        <v>129458908</v>
       </c>
       <c r="B99" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493684</v>
+        <v>493702</v>
       </c>
       <c r="R99" t="n">
-        <v>6834860</v>
+        <v>6834942</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10949,29 +10951,28 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476569</v>
+        <v>129476537</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10979,21 +10980,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11003,10 +11004,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493626</v>
+        <v>493659</v>
       </c>
       <c r="R100" t="n">
-        <v>6834837</v>
+        <v>6834945</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11065,10 +11066,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129476578</v>
+        <v>129476560</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11076,34 +11077,41 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493718</v>
+        <v>493684</v>
       </c>
       <c r="R101" t="n">
-        <v>6834894</v>
+        <v>6834860</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11144,6 +11152,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11162,7 +11171,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129455841</v>
+        <v>129476569</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11193,14 +11202,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493803</v>
+        <v>493626</v>
       </c>
       <c r="R102" t="n">
-        <v>6834901</v>
+        <v>6834837</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11247,22 +11256,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476544</v>
+        <v>129476578</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11270,42 +11279,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493634</v>
+        <v>493718</v>
       </c>
       <c r="R103" t="n">
-        <v>6834983</v>
+        <v>6834894</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11364,54 +11365,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129455942</v>
+        <v>129455841</v>
       </c>
       <c r="B104" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493802</v>
+        <v>493803</v>
       </c>
       <c r="R104" t="n">
-        <v>6834925</v>
+        <v>6834901</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11470,45 +11462,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129458908</v>
+        <v>129476544</v>
       </c>
       <c r="B105" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493702</v>
+        <v>493634</v>
       </c>
       <c r="R105" t="n">
-        <v>6834942</v>
+        <v>6834983</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,19 +11555,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129458098</v>
+        <v>129455942</v>
       </c>
       <c r="B106" t="n">
         <v>98727</v>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -11611,10 +11611,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493682</v>
+        <v>493802</v>
       </c>
       <c r="R106" t="n">
-        <v>6834975</v>
+        <v>6834925</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11673,54 +11673,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129456312</v>
+        <v>129458915</v>
       </c>
       <c r="B107" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493787</v>
+        <v>493698</v>
       </c>
       <c r="R107" t="n">
-        <v>6834957</v>
+        <v>6834942</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11876,45 +11867,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129458915</v>
+        <v>129456312</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493698</v>
+        <v>493787</v>
       </c>
       <c r="R109" t="n">
-        <v>6834942</v>
+        <v>6834957</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12079,45 +12079,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129458436</v>
+        <v>129476568</v>
       </c>
       <c r="B111" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493653</v>
+        <v>493619</v>
       </c>
       <c r="R111" t="n">
-        <v>6835020</v>
+        <v>6834841</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12164,19 +12164,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129476568</v>
+        <v>129461581</v>
       </c>
       <c r="B112" t="n">
         <v>79044</v>
@@ -12207,14 +12207,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493619</v>
+        <v>493634</v>
       </c>
       <c r="R112" t="n">
-        <v>6834841</v>
+        <v>6834920</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12261,44 +12261,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129461581</v>
+        <v>129458436</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12308,10 +12308,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493634</v>
+        <v>493653</v>
       </c>
       <c r="R113" t="n">
-        <v>6834920</v>
+        <v>6835020</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12467,45 +12467,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129460271</v>
+        <v>129459731</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493731</v>
+        <v>493725</v>
       </c>
       <c r="R115" t="n">
-        <v>6834853</v>
+        <v>6834883</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12564,10 +12573,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476584</v>
+        <v>129476558</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12575,21 +12584,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12599,10 +12608,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493670</v>
+        <v>493629</v>
       </c>
       <c r="R116" t="n">
-        <v>6834995</v>
+        <v>6834823</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12661,10 +12670,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129476558</v>
+        <v>129460271</v>
       </c>
       <c r="B117" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12672,34 +12681,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493629</v>
+        <v>493731</v>
       </c>
       <c r="R117" t="n">
-        <v>6834823</v>
+        <v>6834853</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12746,66 +12755,57 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129459731</v>
+        <v>129476584</v>
       </c>
       <c r="B118" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>493725</v>
+        <v>493670</v>
       </c>
       <c r="R118" t="n">
-        <v>6834883</v>
+        <v>6834995</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12852,19 +12852,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129459774</v>
+        <v>129459508</v>
       </c>
       <c r="B119" t="n">
         <v>98727</v>
@@ -12892,16 +12892,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
@@ -12911,7 +12902,7 @@
         <v>493729</v>
       </c>
       <c r="R119" t="n">
-        <v>6834877</v>
+        <v>6834899</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12970,7 +12961,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129459508</v>
+        <v>129459774</v>
       </c>
       <c r="B120" t="n">
         <v>98727</v>
@@ -12998,7 +12989,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
@@ -13008,7 +13008,7 @@
         <v>493729</v>
       </c>
       <c r="R120" t="n">
-        <v>6834899</v>
+        <v>6834877</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13067,45 +13067,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129476541</v>
+        <v>129461070</v>
       </c>
       <c r="B121" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493780</v>
+        <v>493629</v>
       </c>
       <c r="R121" t="n">
-        <v>6834984</v>
+        <v>6834827</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13152,57 +13152,66 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476590</v>
+        <v>129456404</v>
       </c>
       <c r="B122" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493628</v>
+        <v>493780</v>
       </c>
       <c r="R122" t="n">
-        <v>6834891</v>
+        <v>6834929</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13249,12 +13258,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13366,45 +13375,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129461070</v>
+        <v>129476541</v>
       </c>
       <c r="B124" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493629</v>
+        <v>493780</v>
       </c>
       <c r="R124" t="n">
-        <v>6834827</v>
+        <v>6834984</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13451,57 +13460,57 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129457707</v>
+        <v>129476590</v>
       </c>
       <c r="B125" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493815</v>
+        <v>493628</v>
       </c>
       <c r="R125" t="n">
-        <v>6834917</v>
+        <v>6834891</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13548,19 +13557,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129456013</v>
+        <v>129457707</v>
       </c>
       <c r="B126" t="n">
         <v>98727</v>
@@ -13588,26 +13597,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493806</v>
+        <v>493815</v>
       </c>
       <c r="R126" t="n">
-        <v>6834935</v>
+        <v>6834917</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13666,7 +13666,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129456404</v>
+        <v>129456013</v>
       </c>
       <c r="B127" t="n">
         <v>98727</v>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493780</v>
+        <v>493806</v>
       </c>
       <c r="R127" t="n">
-        <v>6834929</v>
+        <v>6834935</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129476530</v>
+        <v>129458645</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,34 +13889,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493705</v>
+        <v>493662</v>
       </c>
       <c r="R129" t="n">
-        <v>6834890</v>
+        <v>6834952</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13963,12 +13963,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14072,54 +14072,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129456470</v>
+        <v>129476530</v>
       </c>
       <c r="B131" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493783</v>
+        <v>493705</v>
       </c>
       <c r="R131" t="n">
-        <v>6834931</v>
+        <v>6834890</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14166,19 +14157,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129458700</v>
+        <v>129456470</v>
       </c>
       <c r="B132" t="n">
         <v>98727</v>
@@ -14206,20 +14197,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493675</v>
+        <v>493783</v>
       </c>
       <c r="R132" t="n">
-        <v>6834963</v>
+        <v>6834931</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14275,48 +14275,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129476550</v>
+        <v>129458700</v>
       </c>
       <c r="B133" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493625</v>
+        <v>493675</v>
       </c>
       <c r="R133" t="n">
-        <v>6834820</v>
+        <v>6834963</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14360,22 +14360,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129458645</v>
+        <v>129476550</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14383,34 +14383,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493662</v>
+        <v>493625</v>
       </c>
       <c r="R134" t="n">
-        <v>6834952</v>
+        <v>6834820</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14457,22 +14457,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476588</v>
+        <v>129476548</v>
       </c>
       <c r="B135" t="n">
-        <v>78710</v>
+        <v>91606</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493619</v>
+        <v>493687</v>
       </c>
       <c r="R135" t="n">
-        <v>6834998</v>
+        <v>6834930</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,10 +14566,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476548</v>
+        <v>129476588</v>
       </c>
       <c r="B136" t="n">
-        <v>91606</v>
+        <v>78710</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493687</v>
+        <v>493619</v>
       </c>
       <c r="R136" t="n">
-        <v>6834930</v>
+        <v>6834998</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14663,45 +14663,54 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476573</v>
+        <v>129476553</v>
       </c>
       <c r="B137" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493661</v>
+        <v>493591</v>
       </c>
       <c r="R137" t="n">
-        <v>6834848</v>
+        <v>6835008</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14742,6 +14751,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14760,32 +14770,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129459901</v>
+        <v>129458414</v>
       </c>
       <c r="B138" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14795,10 +14805,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493734</v>
+        <v>493670</v>
       </c>
       <c r="R138" t="n">
-        <v>6834875</v>
+        <v>6834981</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14857,7 +14867,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476580</v>
+        <v>129476573</v>
       </c>
       <c r="B139" t="n">
         <v>79044</v>
@@ -14892,10 +14902,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493675</v>
+        <v>493661</v>
       </c>
       <c r="R139" t="n">
-        <v>6834937</v>
+        <v>6834848</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14954,54 +14964,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129476553</v>
+        <v>129459901</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493591</v>
+        <v>493734</v>
       </c>
       <c r="R140" t="n">
-        <v>6835008</v>
+        <v>6834875</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15042,64 +15043,63 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129458414</v>
+        <v>129476580</v>
       </c>
       <c r="B141" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493670</v>
+        <v>493675</v>
       </c>
       <c r="R141" t="n">
-        <v>6834981</v>
+        <v>6834937</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15146,12 +15146,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15255,10 +15255,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129476543</v>
+        <v>129476540</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15266,42 +15266,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>493676</v>
+        <v>493723</v>
       </c>
       <c r="R143" t="n">
-        <v>6834800</v>
+        <v>6834965</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15360,54 +15352,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129457830</v>
+        <v>129458803</v>
       </c>
       <c r="B144" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493676</v>
+        <v>493683</v>
       </c>
       <c r="R144" t="n">
-        <v>6835001</v>
+        <v>6834951</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15466,54 +15449,53 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129458085</v>
+        <v>129476543</v>
       </c>
       <c r="B145" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493690</v>
+        <v>493676</v>
       </c>
       <c r="R145" t="n">
-        <v>6834972</v>
+        <v>6834800</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15560,12 +15542,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15669,7 +15651,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129460207</v>
+        <v>129458085</v>
       </c>
       <c r="B147" t="n">
         <v>98727</v>
@@ -15697,17 +15679,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493738</v>
+        <v>493690</v>
       </c>
       <c r="R147" t="n">
-        <v>6834861</v>
+        <v>6834972</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15766,45 +15757,54 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129476540</v>
+        <v>129457830</v>
       </c>
       <c r="B148" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493723</v>
+        <v>493676</v>
       </c>
       <c r="R148" t="n">
-        <v>6834965</v>
+        <v>6835001</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15851,44 +15851,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129458803</v>
+        <v>129460207</v>
       </c>
       <c r="B149" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15898,10 +15898,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493683</v>
+        <v>493738</v>
       </c>
       <c r="R149" t="n">
-        <v>6834951</v>
+        <v>6834861</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15960,10 +15960,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476539</v>
+        <v>129476535</v>
       </c>
       <c r="B150" t="n">
-        <v>90585</v>
+        <v>79663</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15971,21 +15971,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493652</v>
+        <v>493703</v>
       </c>
       <c r="R150" t="n">
-        <v>6834985</v>
+        <v>6834865</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16057,10 +16057,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476535</v>
+        <v>129476539</v>
       </c>
       <c r="B151" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16068,21 +16068,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493703</v>
+        <v>493652</v>
       </c>
       <c r="R151" t="n">
-        <v>6834865</v>
+        <v>6834985</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16445,45 +16445,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129460288</v>
+        <v>129476576</v>
       </c>
       <c r="B155" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493733</v>
+        <v>493725</v>
       </c>
       <c r="R155" t="n">
-        <v>6834848</v>
+        <v>6834888</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16530,19 +16530,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129458972</v>
+        <v>129460288</v>
       </c>
       <c r="B156" t="n">
         <v>98727</v>
@@ -16570,26 +16570,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493700</v>
+        <v>493733</v>
       </c>
       <c r="R156" t="n">
-        <v>6834942</v>
+        <v>6834848</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16648,45 +16639,54 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129476576</v>
+        <v>129458972</v>
       </c>
       <c r="B157" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493725</v>
+        <v>493700</v>
       </c>
       <c r="R157" t="n">
-        <v>6834888</v>
+        <v>6834942</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16733,22 +16733,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129476546</v>
+        <v>129476549</v>
       </c>
       <c r="B158" t="n">
-        <v>91851</v>
+        <v>91606</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16756,21 +16756,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16780,10 +16780,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493733</v>
+        <v>493677</v>
       </c>
       <c r="R158" t="n">
-        <v>6834961</v>
+        <v>6835005</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16842,45 +16842,54 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129476549</v>
+        <v>129459953</v>
       </c>
       <c r="B159" t="n">
-        <v>91606</v>
+        <v>98727</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493677</v>
+        <v>493729</v>
       </c>
       <c r="R159" t="n">
-        <v>6835005</v>
+        <v>6834873</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16927,12 +16936,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -17230,7 +17239,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129458226</v>
+        <v>129457857</v>
       </c>
       <c r="B163" t="n">
         <v>79044</v>
@@ -17265,10 +17274,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493670</v>
+        <v>493676</v>
       </c>
       <c r="R163" t="n">
-        <v>6834981</v>
+        <v>6835001</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17327,54 +17336,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129459449</v>
+        <v>129458226</v>
       </c>
       <c r="B164" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493720</v>
+        <v>493670</v>
       </c>
       <c r="R164" t="n">
-        <v>6834910</v>
+        <v>6834981</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17433,54 +17433,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129459953</v>
+        <v>129476546</v>
       </c>
       <c r="B165" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493729</v>
+        <v>493733</v>
       </c>
       <c r="R165" t="n">
-        <v>6834873</v>
+        <v>6834961</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17527,57 +17518,66 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129457857</v>
+        <v>129459449</v>
       </c>
       <c r="B166" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493676</v>
+        <v>493720</v>
       </c>
       <c r="R166" t="n">
-        <v>6835001</v>
+        <v>6834910</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17746,10 +17746,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476587</v>
+        <v>129476531</v>
       </c>
       <c r="B168" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17757,21 +17757,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17781,10 +17781,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493659</v>
+        <v>493636</v>
       </c>
       <c r="R168" t="n">
-        <v>6834945</v>
+        <v>6834906</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18134,45 +18134,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476531</v>
+        <v>129459536</v>
       </c>
       <c r="B172" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493636</v>
+        <v>493723</v>
       </c>
       <c r="R172" t="n">
-        <v>6834906</v>
+        <v>6834898</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18219,66 +18219,57 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129459653</v>
+        <v>129476587</v>
       </c>
       <c r="B173" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493740</v>
+        <v>493659</v>
       </c>
       <c r="R173" t="n">
-        <v>6834887</v>
+        <v>6834945</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18325,19 +18316,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129459536</v>
+        <v>129459653</v>
       </c>
       <c r="B174" t="n">
         <v>98727</v>
@@ -18365,17 +18356,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493723</v>
+        <v>493740</v>
       </c>
       <c r="R174" t="n">
-        <v>6834898</v>
+        <v>6834887</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18540,54 +18540,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129456055</v>
+        <v>129459599</v>
       </c>
       <c r="B176" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493817</v>
+        <v>493726</v>
       </c>
       <c r="R176" t="n">
-        <v>6834930</v>
+        <v>6834891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18646,32 +18637,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129459676</v>
+        <v>129460260</v>
       </c>
       <c r="B177" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18681,10 +18672,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493727</v>
+        <v>493731</v>
       </c>
       <c r="R177" t="n">
-        <v>6834879</v>
+        <v>6834851</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18743,7 +18734,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129458467</v>
+        <v>129459676</v>
       </c>
       <c r="B178" t="n">
         <v>98727</v>
@@ -18771,26 +18762,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493646</v>
+        <v>493727</v>
       </c>
       <c r="R178" t="n">
-        <v>6835015</v>
+        <v>6834879</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18849,45 +18831,54 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129459599</v>
+        <v>129458467</v>
       </c>
       <c r="B179" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493726</v>
+        <v>493646</v>
       </c>
       <c r="R179" t="n">
-        <v>6834891</v>
+        <v>6835015</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18946,45 +18937,54 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129460260</v>
+        <v>129456055</v>
       </c>
       <c r="B180" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493731</v>
+        <v>493817</v>
       </c>
       <c r="R180" t="n">
-        <v>6834851</v>
+        <v>6834930</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19043,45 +19043,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129459964</v>
+        <v>129476551</v>
       </c>
       <c r="B181" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493726</v>
+        <v>493632</v>
       </c>
       <c r="R181" t="n">
-        <v>6834867</v>
+        <v>6834827</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19128,22 +19128,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129476551</v>
+        <v>129476561</v>
       </c>
       <c r="B182" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19151,21 +19151,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19175,10 +19175,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>493632</v>
+        <v>493634</v>
       </c>
       <c r="R182" t="n">
-        <v>6834827</v>
+        <v>6834985</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19237,45 +19237,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129476561</v>
+        <v>129459964</v>
       </c>
       <c r="B183" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493634</v>
+        <v>493726</v>
       </c>
       <c r="R183" t="n">
-        <v>6834985</v>
+        <v>6834867</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19322,12 +19322,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19431,45 +19431,54 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129525028</v>
+        <v>129525359</v>
       </c>
       <c r="B185" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>493857</v>
+        <v>493934</v>
       </c>
       <c r="R185" t="n">
-        <v>6834694</v>
+        <v>6834670</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19516,66 +19525,57 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129525359</v>
+        <v>129525028</v>
       </c>
       <c r="B186" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>493934</v>
+        <v>493857</v>
       </c>
       <c r="R186" t="n">
-        <v>6834670</v>
+        <v>6834694</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19622,12 +19622,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
@@ -19925,7 +19925,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129525395</v>
+        <v>129525603</v>
       </c>
       <c r="B190" t="n">
         <v>98727</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -19965,14 +19965,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>493923</v>
+        <v>493825</v>
       </c>
       <c r="R190" t="n">
-        <v>6834647</v>
+        <v>6834572</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20019,19 +20019,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129525603</v>
+        <v>129525395</v>
       </c>
       <c r="B191" t="n">
         <v>98727</v>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -20071,14 +20071,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>493825</v>
+        <v>493923</v>
       </c>
       <c r="R191" t="n">
-        <v>6834572</v>
+        <v>6834647</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20125,12 +20125,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -20534,45 +20534,54 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129525895</v>
+        <v>129525059</v>
       </c>
       <c r="B196" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>493792</v>
+        <v>493851</v>
       </c>
       <c r="R196" t="n">
-        <v>6834620</v>
+        <v>6834680</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20631,54 +20640,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129525059</v>
+        <v>129525895</v>
       </c>
       <c r="B197" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>493851</v>
+        <v>493792</v>
       </c>
       <c r="R197" t="n">
-        <v>6834680</v>
+        <v>6834620</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20834,7 +20834,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129525466</v>
+        <v>129525089</v>
       </c>
       <c r="B199" t="n">
         <v>98727</v>
@@ -20862,17 +20862,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>493832</v>
+        <v>493895</v>
       </c>
       <c r="R199" t="n">
-        <v>6834595</v>
+        <v>6834684</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20919,19 +20928,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129525089</v>
+        <v>129525466</v>
       </c>
       <c r="B200" t="n">
         <v>98727</v>
@@ -20959,26 +20968,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>493895</v>
+        <v>493832</v>
       </c>
       <c r="R200" t="n">
-        <v>6834684</v>
+        <v>6834595</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21025,12 +21025,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
@@ -21240,7 +21240,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129525041</v>
+        <v>129525012</v>
       </c>
       <c r="B203" t="n">
         <v>98727</v>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -21280,14 +21280,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>493881</v>
+        <v>493866</v>
       </c>
       <c r="R203" t="n">
-        <v>6834662</v>
+        <v>6834688</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21334,19 +21334,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129525012</v>
+        <v>129525041</v>
       </c>
       <c r="B204" t="n">
         <v>98727</v>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -21386,14 +21386,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>493866</v>
+        <v>493881</v>
       </c>
       <c r="R204" t="n">
-        <v>6834688</v>
+        <v>6834662</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21440,19 +21440,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129525022</v>
+        <v>129525474</v>
       </c>
       <c r="B205" t="n">
         <v>98727</v>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>493867</v>
+        <v>493908</v>
       </c>
       <c r="R205" t="n">
-        <v>6834661</v>
+        <v>6834595</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21558,7 +21558,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129525474</v>
+        <v>129525022</v>
       </c>
       <c r="B206" t="n">
         <v>98727</v>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>493908</v>
+        <v>493867</v>
       </c>
       <c r="R206" t="n">
-        <v>6834595</v>
+        <v>6834661</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21664,54 +21664,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525477</v>
+        <v>129525320</v>
       </c>
       <c r="B207" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493823</v>
+        <v>493859</v>
       </c>
       <c r="R207" t="n">
-        <v>6834595</v>
+        <v>6834674</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21744,6 +21735,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21876,10 +21872,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129525320</v>
+        <v>129525442</v>
       </c>
       <c r="B209" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21887,34 +21883,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>493859</v>
+        <v>493925</v>
       </c>
       <c r="R209" t="n">
-        <v>6834674</v>
+        <v>6834617</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21949,11 +21945,6 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
@@ -21966,57 +21957,66 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129525442</v>
+        <v>129525477</v>
       </c>
       <c r="B210" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493925</v>
+        <v>493823</v>
       </c>
       <c r="R210" t="n">
-        <v>6834617</v>
+        <v>6834595</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22063,12 +22063,12 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
@@ -22181,32 +22181,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525429</v>
+        <v>129525462</v>
       </c>
       <c r="B212" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22216,10 +22216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493788</v>
+        <v>493832</v>
       </c>
       <c r="R212" t="n">
-        <v>6834656</v>
+        <v>6834595</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22481,32 +22481,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129525462</v>
+        <v>129525429</v>
       </c>
       <c r="B215" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22516,10 +22516,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>493832</v>
+        <v>493788</v>
       </c>
       <c r="R215" t="n">
-        <v>6834595</v>
+        <v>6834656</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23178,45 +23178,54 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129525680</v>
+        <v>129525347</v>
       </c>
       <c r="B222" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>493840</v>
+        <v>493915</v>
       </c>
       <c r="R222" t="n">
-        <v>6834519</v>
+        <v>6834671</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23263,66 +23272,57 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129525347</v>
+        <v>129525680</v>
       </c>
       <c r="B223" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>493915</v>
+        <v>493840</v>
       </c>
       <c r="R223" t="n">
-        <v>6834671</v>
+        <v>6834519</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23369,12 +23369,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,10 +8179,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476572</v>
+        <v>129476586</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8190,21 +8190,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493675</v>
+        <v>493684</v>
       </c>
       <c r="R72" t="n">
-        <v>6834825</v>
+        <v>6834869</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129476556</v>
+        <v>129476572</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493810</v>
+        <v>493675</v>
       </c>
       <c r="R73" t="n">
-        <v>6834883</v>
+        <v>6834825</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8373,45 +8373,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460134</v>
+        <v>129476556</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493738</v>
+        <v>493810</v>
       </c>
       <c r="R74" t="n">
-        <v>6834870</v>
+        <v>6834883</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,57 +8458,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476586</v>
+        <v>129460134</v>
       </c>
       <c r="B75" t="n">
-        <v>78710</v>
+        <v>98756</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493684</v>
+        <v>493738</v>
       </c>
       <c r="R75" t="n">
-        <v>6834869</v>
+        <v>6834870</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8555,12 +8555,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8570,7 +8570,7 @@
         <v>129460004</v>
       </c>
       <c r="B76" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>129476585</v>
       </c>
       <c r="B78" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8867,54 +8867,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129457973</v>
+        <v>129461154</v>
       </c>
       <c r="B79" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493684</v>
+        <v>493629</v>
       </c>
       <c r="R79" t="n">
-        <v>6834986</v>
+        <v>6834827</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8973,54 +8964,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129456176</v>
+        <v>129460036</v>
       </c>
       <c r="B80" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493813</v>
+        <v>493728</v>
       </c>
       <c r="R80" t="n">
-        <v>6834955</v>
+        <v>6834868</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9079,10 +9061,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129461154</v>
+        <v>129460662</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9114,10 +9096,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493629</v>
+        <v>493658</v>
       </c>
       <c r="R81" t="n">
-        <v>6834827</v>
+        <v>6834840</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9176,45 +9158,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129460036</v>
+        <v>129476554</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493728</v>
+        <v>493648</v>
       </c>
       <c r="R82" t="n">
-        <v>6834868</v>
+        <v>6834929</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9255,63 +9246,73 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129460662</v>
+        <v>129456176</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493658</v>
+        <v>493813</v>
       </c>
       <c r="R83" t="n">
-        <v>6834840</v>
+        <v>6834955</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9370,54 +9371,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129476554</v>
+        <v>129457973</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>98756</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493648</v>
+        <v>493684</v>
       </c>
       <c r="R84" t="n">
-        <v>6834929</v>
+        <v>6834986</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9458,64 +9459,63 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129476579</v>
+        <v>129457913</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493687</v>
+        <v>493686</v>
       </c>
       <c r="R85" t="n">
-        <v>6834917</v>
+        <v>6834989</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9562,60 +9562,69 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129476589</v>
+        <v>129460883</v>
       </c>
       <c r="B86" t="n">
-        <v>92835</v>
+        <v>98756</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493641</v>
+        <v>493637</v>
       </c>
       <c r="R86" t="n">
-        <v>6834918</v>
+        <v>6834831</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9659,57 +9668,66 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129457992</v>
+        <v>129457745</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493684</v>
+        <v>493678</v>
       </c>
       <c r="R87" t="n">
-        <v>6834988</v>
+        <v>6835020</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9768,45 +9786,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129476547</v>
+        <v>129457992</v>
       </c>
       <c r="B88" t="n">
-        <v>79068</v>
+        <v>79070</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493722</v>
+        <v>493684</v>
       </c>
       <c r="R88" t="n">
-        <v>6834900</v>
+        <v>6834988</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9853,66 +9871,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129457745</v>
+        <v>129476547</v>
       </c>
       <c r="B89" t="n">
-        <v>98727</v>
+        <v>79094</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493678</v>
+        <v>493722</v>
       </c>
       <c r="R89" t="n">
-        <v>6835020</v>
+        <v>6834900</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9959,69 +9968,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129460883</v>
+        <v>129476579</v>
       </c>
       <c r="B90" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493637</v>
+        <v>493687</v>
       </c>
       <c r="R90" t="n">
-        <v>6834831</v>
+        <v>6834917</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10065,57 +10065,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129457913</v>
+        <v>129476589</v>
       </c>
       <c r="B91" t="n">
-        <v>98727</v>
+        <v>92863</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>493686</v>
+        <v>493641</v>
       </c>
       <c r="R91" t="n">
-        <v>6834989</v>
+        <v>6834918</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10162,66 +10162,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129476555</v>
+        <v>129476583</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>493666</v>
+        <v>493664</v>
       </c>
       <c r="R92" t="n">
-        <v>6834982</v>
+        <v>6834992</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10262,7 +10253,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10281,10 +10271,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476583</v>
+        <v>129476532</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10292,21 +10282,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10316,10 +10306,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493664</v>
+        <v>493619</v>
       </c>
       <c r="R93" t="n">
-        <v>6834992</v>
+        <v>6834843</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10378,10 +10368,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476532</v>
+        <v>129476566</v>
       </c>
       <c r="B94" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10389,21 +10379,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10413,10 +10403,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493619</v>
+        <v>493646</v>
       </c>
       <c r="R94" t="n">
-        <v>6834843</v>
+        <v>6834937</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10475,10 +10465,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476566</v>
+        <v>129476574</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10510,10 +10500,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493646</v>
+        <v>493702</v>
       </c>
       <c r="R95" t="n">
-        <v>6834937</v>
+        <v>6834858</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10572,45 +10562,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476574</v>
+        <v>129476555</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493702</v>
+        <v>493666</v>
       </c>
       <c r="R96" t="n">
-        <v>6834858</v>
+        <v>6834982</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10651,6 +10650,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>129476571</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10766,54 +10766,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129458098</v>
+        <v>129476544</v>
       </c>
       <c r="B98" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493682</v>
+        <v>493634</v>
       </c>
       <c r="R98" t="n">
-        <v>6834975</v>
+        <v>6834983</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10860,22 +10859,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129458908</v>
+        <v>129455942</v>
       </c>
       <c r="B99" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10900,17 +10899,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493702</v>
+        <v>493802</v>
       </c>
       <c r="R99" t="n">
-        <v>6834942</v>
+        <v>6834925</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10969,45 +10977,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476537</v>
+        <v>129458908</v>
       </c>
       <c r="B100" t="n">
-        <v>79634</v>
+        <v>98756</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493659</v>
+        <v>493702</v>
       </c>
       <c r="R100" t="n">
-        <v>6834945</v>
+        <v>6834942</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11054,64 +11062,66 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129476560</v>
+        <v>129458098</v>
       </c>
       <c r="B101" t="n">
-        <v>78801</v>
+        <v>98756</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493684</v>
+        <v>493682</v>
       </c>
       <c r="R101" t="n">
-        <v>6834860</v>
+        <v>6834975</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11152,29 +11162,28 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476569</v>
+        <v>129476537</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>79660</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11182,21 +11191,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11206,10 +11215,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493626</v>
+        <v>493659</v>
       </c>
       <c r="R102" t="n">
-        <v>6834837</v>
+        <v>6834945</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11268,10 +11277,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476578</v>
+        <v>129476560</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>78827</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11279,34 +11288,41 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493718</v>
+        <v>493684</v>
       </c>
       <c r="R103" t="n">
-        <v>6834894</v>
+        <v>6834860</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11347,6 +11363,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11365,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129455841</v>
+        <v>129476569</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11396,14 +11413,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493803</v>
+        <v>493626</v>
       </c>
       <c r="R104" t="n">
-        <v>6834901</v>
+        <v>6834837</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11450,22 +11467,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129476544</v>
+        <v>129476578</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11473,42 +11490,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493634</v>
+        <v>493718</v>
       </c>
       <c r="R105" t="n">
-        <v>6834983</v>
+        <v>6834894</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11567,54 +11576,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129455942</v>
+        <v>129455841</v>
       </c>
       <c r="B106" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493802</v>
+        <v>493803</v>
       </c>
       <c r="R106" t="n">
-        <v>6834925</v>
+        <v>6834901</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11676,7 +11676,7 @@
         <v>129458915</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>129476577</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>129456312</v>
       </c>
       <c r="B109" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>129456198</v>
       </c>
       <c r="B110" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12079,45 +12079,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129476568</v>
+        <v>129458436</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493619</v>
+        <v>493653</v>
       </c>
       <c r="R111" t="n">
-        <v>6834841</v>
+        <v>6835020</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12164,22 +12164,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129461581</v>
+        <v>129476538</v>
       </c>
       <c r="B112" t="n">
-        <v>79044</v>
+        <v>79660</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12187,34 +12187,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>493634</v>
+        <v>493627</v>
       </c>
       <c r="R112" t="n">
-        <v>6834920</v>
+        <v>6834986</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12261,57 +12261,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129458436</v>
+        <v>129476568</v>
       </c>
       <c r="B113" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493653</v>
+        <v>493619</v>
       </c>
       <c r="R113" t="n">
-        <v>6835020</v>
+        <v>6834841</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12358,22 +12358,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129476538</v>
+        <v>129461581</v>
       </c>
       <c r="B114" t="n">
-        <v>79634</v>
+        <v>79070</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12381,34 +12381,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493627</v>
+        <v>493634</v>
       </c>
       <c r="R114" t="n">
-        <v>6834986</v>
+        <v>6834920</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12455,66 +12455,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129459731</v>
+        <v>129476558</v>
       </c>
       <c r="B115" t="n">
-        <v>98727</v>
+        <v>78827</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493725</v>
+        <v>493629</v>
       </c>
       <c r="R115" t="n">
-        <v>6834883</v>
+        <v>6834823</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12561,22 +12552,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476558</v>
+        <v>129460271</v>
       </c>
       <c r="B116" t="n">
-        <v>78801</v>
+        <v>79070</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12584,34 +12575,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493629</v>
+        <v>493731</v>
       </c>
       <c r="R116" t="n">
-        <v>6834823</v>
+        <v>6834853</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12658,22 +12649,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129460271</v>
+        <v>129476584</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12701,14 +12692,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493731</v>
+        <v>493670</v>
       </c>
       <c r="R117" t="n">
-        <v>6834853</v>
+        <v>6834995</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12755,57 +12746,57 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129476584</v>
+        <v>129459508</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>493670</v>
+        <v>493729</v>
       </c>
       <c r="R118" t="n">
-        <v>6834995</v>
+        <v>6834899</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12852,22 +12843,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129459508</v>
+        <v>129459731</v>
       </c>
       <c r="B119" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12892,17 +12883,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>493729</v>
+        <v>493725</v>
       </c>
       <c r="R119" t="n">
-        <v>6834899</v>
+        <v>6834883</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12964,7 +12964,7 @@
         <v>129459774</v>
       </c>
       <c r="B120" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13067,45 +13067,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129461070</v>
+        <v>129476541</v>
       </c>
       <c r="B121" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493629</v>
+        <v>493780</v>
       </c>
       <c r="R121" t="n">
-        <v>6834827</v>
+        <v>6834984</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13152,66 +13152,64 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129456404</v>
+        <v>129476559</v>
       </c>
       <c r="B122" t="n">
-        <v>98727</v>
+        <v>78827</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493780</v>
+        <v>493626</v>
       </c>
       <c r="R122" t="n">
-        <v>6834929</v>
+        <v>6834843</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13252,70 +13250,64 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129476559</v>
+        <v>129476590</v>
       </c>
       <c r="B123" t="n">
-        <v>78801</v>
+        <v>92863</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493626</v>
+        <v>493628</v>
       </c>
       <c r="R123" t="n">
-        <v>6834843</v>
+        <v>6834891</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13356,7 +13348,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13375,45 +13366,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129476541</v>
+        <v>129461070</v>
       </c>
       <c r="B124" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493780</v>
+        <v>493629</v>
       </c>
       <c r="R124" t="n">
-        <v>6834984</v>
+        <v>6834827</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13460,57 +13451,57 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129476590</v>
+        <v>129457707</v>
       </c>
       <c r="B125" t="n">
-        <v>92835</v>
+        <v>98756</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493628</v>
+        <v>493815</v>
       </c>
       <c r="R125" t="n">
-        <v>6834891</v>
+        <v>6834917</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13557,22 +13548,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129457707</v>
+        <v>129456013</v>
       </c>
       <c r="B126" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13597,17 +13588,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493815</v>
+        <v>493806</v>
       </c>
       <c r="R126" t="n">
-        <v>6834917</v>
+        <v>6834935</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13666,10 +13666,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129456013</v>
+        <v>129456404</v>
       </c>
       <c r="B127" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493806</v>
+        <v>493780</v>
       </c>
       <c r="R127" t="n">
-        <v>6834935</v>
+        <v>6834929</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13775,7 +13775,7 @@
         <v>129456103</v>
       </c>
       <c r="B128" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129458645</v>
+        <v>129476550</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,34 +13889,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493662</v>
+        <v>493625</v>
       </c>
       <c r="R129" t="n">
-        <v>6834952</v>
+        <v>6834820</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13963,22 +13963,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129455888</v>
+        <v>129476530</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>79102</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13986,34 +13986,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493811</v>
+        <v>493705</v>
       </c>
       <c r="R130" t="n">
-        <v>6834925</v>
+        <v>6834890</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14060,22 +14060,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129476530</v>
+        <v>129458645</v>
       </c>
       <c r="B131" t="n">
-        <v>79076</v>
+        <v>79070</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14083,34 +14083,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493705</v>
+        <v>493662</v>
       </c>
       <c r="R131" t="n">
-        <v>6834890</v>
+        <v>6834952</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,66 +14157,57 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129456470</v>
+        <v>129455888</v>
       </c>
       <c r="B132" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493783</v>
+        <v>493811</v>
       </c>
       <c r="R132" t="n">
-        <v>6834931</v>
+        <v>6834925</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14275,10 +14266,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129458700</v>
+        <v>129456470</v>
       </c>
       <c r="B133" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14303,20 +14294,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>493675</v>
+        <v>493783</v>
       </c>
       <c r="R133" t="n">
-        <v>6834963</v>
+        <v>6834931</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14372,48 +14372,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129476550</v>
+        <v>129458700</v>
       </c>
       <c r="B134" t="n">
-        <v>78802</v>
+        <v>98756</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>493625</v>
+        <v>493675</v>
       </c>
       <c r="R134" t="n">
-        <v>6834820</v>
+        <v>6834963</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14457,22 +14457,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476548</v>
+        <v>129476552</v>
       </c>
       <c r="B135" t="n">
-        <v>91606</v>
+        <v>78828</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493687</v>
+        <v>493629</v>
       </c>
       <c r="R135" t="n">
-        <v>6834930</v>
+        <v>6834831</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,10 +14566,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476588</v>
+        <v>129476548</v>
       </c>
       <c r="B136" t="n">
-        <v>78710</v>
+        <v>91634</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493619</v>
+        <v>493687</v>
       </c>
       <c r="R136" t="n">
-        <v>6834998</v>
+        <v>6834930</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14663,54 +14663,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476553</v>
+        <v>129476588</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>78736</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493591</v>
+        <v>493619</v>
       </c>
       <c r="R137" t="n">
-        <v>6835008</v>
+        <v>6834998</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14751,7 +14742,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14770,45 +14760,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129458414</v>
+        <v>129476573</v>
       </c>
       <c r="B138" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>493670</v>
+        <v>493661</v>
       </c>
       <c r="R138" t="n">
-        <v>6834981</v>
+        <v>6834848</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14855,22 +14845,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129476573</v>
+        <v>129459901</v>
       </c>
       <c r="B139" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14898,14 +14888,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>493661</v>
+        <v>493734</v>
       </c>
       <c r="R139" t="n">
-        <v>6834848</v>
+        <v>6834875</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14952,22 +14942,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129459901</v>
+        <v>129476580</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14995,14 +14985,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493734</v>
+        <v>493675</v>
       </c>
       <c r="R140" t="n">
-        <v>6834875</v>
+        <v>6834937</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,57 +15039,57 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476580</v>
+        <v>129458414</v>
       </c>
       <c r="B141" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493675</v>
+        <v>493670</v>
       </c>
       <c r="R141" t="n">
-        <v>6834937</v>
+        <v>6834981</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15146,57 +15136,66 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129476552</v>
+        <v>129476553</v>
       </c>
       <c r="B142" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493629</v>
+        <v>493591</v>
       </c>
       <c r="R142" t="n">
-        <v>6834831</v>
+        <v>6835008</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15237,6 +15236,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>129476540</v>
       </c>
       <c r="B143" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>129458803</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>129476543</v>
       </c>
       <c r="B145" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15554,10 +15554,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129459852</v>
+        <v>129457830</v>
       </c>
       <c r="B146" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15582,17 +15582,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493730</v>
+        <v>493676</v>
       </c>
       <c r="R146" t="n">
-        <v>6834877</v>
+        <v>6835001</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15654,7 +15663,7 @@
         <v>129458085</v>
       </c>
       <c r="B147" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15757,10 +15766,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129457830</v>
+        <v>129459852</v>
       </c>
       <c r="B148" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15785,26 +15794,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493676</v>
+        <v>493730</v>
       </c>
       <c r="R148" t="n">
-        <v>6835001</v>
+        <v>6834877</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15866,7 +15866,7 @@
         <v>129460207</v>
       </c>
       <c r="B149" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15960,45 +15960,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476535</v>
+        <v>129460421</v>
       </c>
       <c r="B150" t="n">
-        <v>79663</v>
+        <v>98756</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493703</v>
+        <v>493728</v>
       </c>
       <c r="R150" t="n">
-        <v>6834865</v>
+        <v>6834848</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16045,22 +16045,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476539</v>
+        <v>129476535</v>
       </c>
       <c r="B151" t="n">
-        <v>90585</v>
+        <v>79689</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16068,21 +16068,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493652</v>
+        <v>493703</v>
       </c>
       <c r="R151" t="n">
-        <v>6834985</v>
+        <v>6834865</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16154,45 +16154,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129460421</v>
+        <v>129476539</v>
       </c>
       <c r="B152" t="n">
-        <v>98727</v>
+        <v>90613</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>493728</v>
+        <v>493652</v>
       </c>
       <c r="R152" t="n">
-        <v>6834848</v>
+        <v>6834985</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16239,12 +16239,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16254,7 +16254,7 @@
         <v>129460467</v>
       </c>
       <c r="B153" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>129476567</v>
       </c>
       <c r="B154" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>129476576</v>
       </c>
       <c r="B155" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>129460288</v>
       </c>
       <c r="B156" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>129458972</v>
       </c>
       <c r="B157" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16745,10 +16745,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129476549</v>
+        <v>129476546</v>
       </c>
       <c r="B158" t="n">
-        <v>91606</v>
+        <v>91879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16756,21 +16756,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16780,10 +16780,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>493677</v>
+        <v>493733</v>
       </c>
       <c r="R158" t="n">
-        <v>6835005</v>
+        <v>6834961</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16842,54 +16842,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129459953</v>
+        <v>129476533</v>
       </c>
       <c r="B159" t="n">
-        <v>98727</v>
+        <v>79689</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493729</v>
+        <v>493678</v>
       </c>
       <c r="R159" t="n">
-        <v>6834873</v>
+        <v>6834780</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16936,22 +16927,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129476533</v>
+        <v>129459208</v>
       </c>
       <c r="B160" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16959,34 +16950,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>493678</v>
+        <v>493698</v>
       </c>
       <c r="R160" t="n">
-        <v>6834780</v>
+        <v>6834943</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17033,22 +17024,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129459208</v>
+        <v>129476536</v>
       </c>
       <c r="B161" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17056,34 +17047,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>493698</v>
+        <v>493642</v>
       </c>
       <c r="R161" t="n">
-        <v>6834943</v>
+        <v>6834998</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17130,22 +17121,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129476536</v>
+        <v>129457857</v>
       </c>
       <c r="B162" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17153,34 +17144,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493642</v>
+        <v>493676</v>
       </c>
       <c r="R162" t="n">
-        <v>6834998</v>
+        <v>6835001</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17227,22 +17218,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129457857</v>
+        <v>129458226</v>
       </c>
       <c r="B163" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17274,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493676</v>
+        <v>493670</v>
       </c>
       <c r="R163" t="n">
-        <v>6835001</v>
+        <v>6834981</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17336,10 +17327,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129458226</v>
+        <v>129476549</v>
       </c>
       <c r="B164" t="n">
-        <v>79044</v>
+        <v>91634</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17347,34 +17338,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493670</v>
+        <v>493677</v>
       </c>
       <c r="R164" t="n">
-        <v>6834981</v>
+        <v>6835005</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17421,57 +17412,66 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129476546</v>
+        <v>129459449</v>
       </c>
       <c r="B165" t="n">
-        <v>91851</v>
+        <v>98756</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493733</v>
+        <v>493720</v>
       </c>
       <c r="R165" t="n">
-        <v>6834961</v>
+        <v>6834910</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17518,22 +17518,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129459449</v>
+        <v>129459953</v>
       </c>
       <c r="B166" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>493720</v>
+        <v>493729</v>
       </c>
       <c r="R166" t="n">
-        <v>6834910</v>
+        <v>6834873</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17639,7 +17639,7 @@
         <v>129476562</v>
       </c>
       <c r="B167" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17746,45 +17746,54 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476531</v>
+        <v>129459653</v>
       </c>
       <c r="B168" t="n">
-        <v>79663</v>
+        <v>98756</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493636</v>
+        <v>493740</v>
       </c>
       <c r="R168" t="n">
-        <v>6834906</v>
+        <v>6834887</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17831,57 +17840,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129476581</v>
+        <v>129459536</v>
       </c>
       <c r="B169" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493677</v>
+        <v>493723</v>
       </c>
       <c r="R169" t="n">
-        <v>6834943</v>
+        <v>6834898</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17928,57 +17937,66 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129476575</v>
+        <v>129456373</v>
       </c>
       <c r="B170" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493728</v>
+        <v>493796</v>
       </c>
       <c r="R170" t="n">
-        <v>6834886</v>
+        <v>6834937</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18025,22 +18043,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476570</v>
+        <v>129476531</v>
       </c>
       <c r="B171" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18048,21 +18066,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18072,10 +18090,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493628</v>
+        <v>493636</v>
       </c>
       <c r="R171" t="n">
-        <v>6834790</v>
+        <v>6834906</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18134,45 +18152,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129459536</v>
+        <v>129476575</v>
       </c>
       <c r="B172" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493723</v>
+        <v>493728</v>
       </c>
       <c r="R172" t="n">
-        <v>6834898</v>
+        <v>6834886</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18219,12 +18237,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
@@ -18234,7 +18252,7 @@
         <v>129476587</v>
       </c>
       <c r="B173" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18328,54 +18346,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129459653</v>
+        <v>129476570</v>
       </c>
       <c r="B174" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493740</v>
+        <v>493628</v>
       </c>
       <c r="R174" t="n">
-        <v>6834887</v>
+        <v>6834790</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18422,66 +18431,57 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129456373</v>
+        <v>129476581</v>
       </c>
       <c r="B175" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493796</v>
+        <v>493677</v>
       </c>
       <c r="R175" t="n">
-        <v>6834937</v>
+        <v>6834943</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,12 +18528,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -18543,7 +18543,7 @@
         <v>129459599</v>
       </c>
       <c r="B176" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>129460260</v>
       </c>
       <c r="B177" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18734,10 +18734,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129459676</v>
+        <v>129456055</v>
       </c>
       <c r="B178" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18762,17 +18762,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493727</v>
+        <v>493817</v>
       </c>
       <c r="R178" t="n">
-        <v>6834879</v>
+        <v>6834930</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18831,10 +18840,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129458467</v>
+        <v>129459676</v>
       </c>
       <c r="B179" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18859,26 +18868,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493646</v>
+        <v>493727</v>
       </c>
       <c r="R179" t="n">
-        <v>6835015</v>
+        <v>6834879</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18937,10 +18937,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129456055</v>
+        <v>129458467</v>
       </c>
       <c r="B180" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -18981,10 +18981,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493817</v>
+        <v>493646</v>
       </c>
       <c r="R180" t="n">
-        <v>6834930</v>
+        <v>6835015</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19043,45 +19043,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129476551</v>
+        <v>129459964</v>
       </c>
       <c r="B181" t="n">
-        <v>78802</v>
+        <v>98756</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493632</v>
+        <v>493726</v>
       </c>
       <c r="R181" t="n">
-        <v>6834827</v>
+        <v>6834867</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19128,12 +19128,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
         <v>129476561</v>
       </c>
       <c r="B182" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19237,45 +19237,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129459964</v>
+        <v>129476551</v>
       </c>
       <c r="B183" t="n">
-        <v>98727</v>
+        <v>78828</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493726</v>
+        <v>493632</v>
       </c>
       <c r="R183" t="n">
-        <v>6834867</v>
+        <v>6834827</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19322,12 +19322,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19337,7 +19337,7 @@
         <v>129459836</v>
       </c>
       <c r="B184" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19431,54 +19431,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129525359</v>
+        <v>129525028</v>
       </c>
       <c r="B185" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>493934</v>
+        <v>493857</v>
       </c>
       <c r="R185" t="n">
-        <v>6834670</v>
+        <v>6834694</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19525,57 +19516,66 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129525028</v>
+        <v>129525359</v>
       </c>
       <c r="B186" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>493857</v>
+        <v>493934</v>
       </c>
       <c r="R186" t="n">
-        <v>6834694</v>
+        <v>6834670</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19622,22 +19622,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129525566</v>
+        <v>129525456</v>
       </c>
       <c r="B187" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19669,10 +19669,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>493930</v>
+        <v>493893</v>
       </c>
       <c r="R187" t="n">
-        <v>6834516</v>
+        <v>6834612</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19731,10 +19731,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129525456</v>
+        <v>129525566</v>
       </c>
       <c r="B188" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19766,10 +19766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>493893</v>
+        <v>493930</v>
       </c>
       <c r="R188" t="n">
-        <v>6834612</v>
+        <v>6834516</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19831,7 +19831,7 @@
         <v>129525479</v>
       </c>
       <c r="B189" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>129525603</v>
       </c>
       <c r="B190" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>129525395</v>
       </c>
       <c r="B191" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>129525463</v>
       </c>
       <c r="B192" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>129525450</v>
       </c>
       <c r="B193" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>129525370</v>
       </c>
       <c r="B194" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>129525020</v>
       </c>
       <c r="B195" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20534,54 +20534,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129525059</v>
+        <v>129525895</v>
       </c>
       <c r="B196" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>493851</v>
+        <v>493792</v>
       </c>
       <c r="R196" t="n">
-        <v>6834680</v>
+        <v>6834620</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20640,45 +20631,54 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129525895</v>
+        <v>129525059</v>
       </c>
       <c r="B197" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>493792</v>
+        <v>493851</v>
       </c>
       <c r="R197" t="n">
-        <v>6834620</v>
+        <v>6834680</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20737,45 +20737,54 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129525351</v>
+        <v>129525089</v>
       </c>
       <c r="B198" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>493874</v>
+        <v>493895</v>
       </c>
       <c r="R198" t="n">
-        <v>6834658</v>
+        <v>6834684</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20822,22 +20831,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129525089</v>
+        <v>129525466</v>
       </c>
       <c r="B199" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20862,26 +20871,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>493895</v>
+        <v>493832</v>
       </c>
       <c r="R199" t="n">
-        <v>6834684</v>
+        <v>6834595</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20928,44 +20928,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129525466</v>
+        <v>129525351</v>
       </c>
       <c r="B200" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20975,10 +20975,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>493832</v>
+        <v>493874</v>
       </c>
       <c r="R200" t="n">
-        <v>6834595</v>
+        <v>6834658</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21040,7 +21040,7 @@
         <v>129525470</v>
       </c>
       <c r="B201" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>129525496</v>
       </c>
       <c r="B202" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>129525012</v>
       </c>
       <c r="B203" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>129525041</v>
       </c>
       <c r="B204" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>129525474</v>
       </c>
       <c r="B205" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>129525022</v>
       </c>
       <c r="B206" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>129525320</v>
       </c>
       <c r="B207" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21766,54 +21766,45 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129524983</v>
+        <v>129525442</v>
       </c>
       <c r="B208" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493871</v>
+        <v>493925</v>
       </c>
       <c r="R208" t="n">
-        <v>6834690</v>
+        <v>6834617</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21872,45 +21863,54 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129525442</v>
+        <v>129525477</v>
       </c>
       <c r="B209" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>493925</v>
+        <v>493823</v>
       </c>
       <c r="R209" t="n">
-        <v>6834617</v>
+        <v>6834595</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21957,22 +21957,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129525477</v>
+        <v>129525078</v>
       </c>
       <c r="B210" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -22009,14 +22009,14 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493823</v>
+        <v>493886</v>
       </c>
       <c r="R210" t="n">
-        <v>6834595</v>
+        <v>6834673</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22063,22 +22063,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525078</v>
+        <v>129524983</v>
       </c>
       <c r="B211" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22119,10 +22119,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493886</v>
+        <v>493871</v>
       </c>
       <c r="R211" t="n">
-        <v>6834673</v>
+        <v>6834690</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22184,7 +22184,7 @@
         <v>129525462</v>
       </c>
       <c r="B212" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22278,54 +22278,45 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525001</v>
+        <v>129525429</v>
       </c>
       <c r="B213" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>493870</v>
+        <v>493788</v>
       </c>
       <c r="R213" t="n">
-        <v>6834690</v>
+        <v>6834656</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22384,10 +22375,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525451</v>
+        <v>129525001</v>
       </c>
       <c r="B214" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22412,17 +22403,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>493788</v>
+        <v>493870</v>
       </c>
       <c r="R214" t="n">
-        <v>6834656</v>
+        <v>6834690</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22481,32 +22481,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129525429</v>
+        <v>129525451</v>
       </c>
       <c r="B215" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22581,7 +22581,7 @@
         <v>129525529</v>
       </c>
       <c r="B216" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>129525382</v>
       </c>
       <c r="B217" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>129525489</v>
       </c>
       <c r="B218" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>129525130</v>
       </c>
       <c r="B219" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>129525418</v>
       </c>
       <c r="B220" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>129525528</v>
       </c>
       <c r="B221" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23178,54 +23178,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129525347</v>
+        <v>129525680</v>
       </c>
       <c r="B222" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>493915</v>
+        <v>493840</v>
       </c>
       <c r="R222" t="n">
-        <v>6834671</v>
+        <v>6834519</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23272,57 +23263,66 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129525680</v>
+        <v>129525347</v>
       </c>
       <c r="B223" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>493840</v>
+        <v>493915</v>
       </c>
       <c r="R223" t="n">
-        <v>6834519</v>
+        <v>6834671</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23369,12 +23369,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
@@ -23384,7 +23384,7 @@
         <v>129525601</v>
       </c>
       <c r="B224" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>129525445</v>
       </c>
       <c r="B225" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,45 +8179,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129476586</v>
+        <v>129460134</v>
       </c>
       <c r="B72" t="n">
-        <v>78736</v>
+        <v>98756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493684</v>
+        <v>493738</v>
       </c>
       <c r="R72" t="n">
-        <v>6834869</v>
+        <v>6834870</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8264,57 +8264,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129476572</v>
+        <v>129460004</v>
       </c>
       <c r="B73" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493675</v>
+        <v>493728</v>
       </c>
       <c r="R73" t="n">
-        <v>6834825</v>
+        <v>6834868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,57 +8361,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129476556</v>
+        <v>129460228</v>
       </c>
       <c r="B74" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493810</v>
+        <v>493736</v>
       </c>
       <c r="R74" t="n">
-        <v>6834883</v>
+        <v>6834865</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,57 +8467,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129460134</v>
+        <v>129476572</v>
       </c>
       <c r="B75" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493738</v>
+        <v>493675</v>
       </c>
       <c r="R75" t="n">
-        <v>6834870</v>
+        <v>6834825</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8555,57 +8564,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129460004</v>
+        <v>129476556</v>
       </c>
       <c r="B76" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493728</v>
+        <v>493810</v>
       </c>
       <c r="R76" t="n">
-        <v>6834868</v>
+        <v>6834883</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8652,66 +8661,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129460228</v>
+        <v>129476586</v>
       </c>
       <c r="B77" t="n">
-        <v>98756</v>
+        <v>78736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493736</v>
+        <v>493684</v>
       </c>
       <c r="R77" t="n">
-        <v>6834865</v>
+        <v>6834869</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,22 +8758,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129476585</v>
+        <v>129461154</v>
       </c>
       <c r="B78" t="n">
-        <v>78736</v>
+        <v>79070</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8781,34 +8781,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493700</v>
+        <v>493629</v>
       </c>
       <c r="R78" t="n">
-        <v>6834837</v>
+        <v>6834827</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8855,19 +8855,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129461154</v>
+        <v>129460036</v>
       </c>
       <c r="B79" t="n">
         <v>79070</v>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493629</v>
+        <v>493728</v>
       </c>
       <c r="R79" t="n">
-        <v>6834827</v>
+        <v>6834868</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129460036</v>
+        <v>129460662</v>
       </c>
       <c r="B80" t="n">
         <v>79070</v>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493728</v>
+        <v>493658</v>
       </c>
       <c r="R80" t="n">
-        <v>6834868</v>
+        <v>6834840</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9061,10 +9061,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129460662</v>
+        <v>129476585</v>
       </c>
       <c r="B81" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9072,34 +9072,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493658</v>
+        <v>493700</v>
       </c>
       <c r="R81" t="n">
-        <v>6834840</v>
+        <v>6834837</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9146,12 +9146,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476544</v>
+        <v>129476560</v>
       </c>
       <c r="B98" t="n">
-        <v>57730</v>
+        <v>78827</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10777,29 +10777,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -10809,10 +10808,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493634</v>
+        <v>493684</v>
       </c>
       <c r="R98" t="n">
-        <v>6834983</v>
+        <v>6834860</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10853,6 +10852,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10871,54 +10871,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129455942</v>
+        <v>129476569</v>
       </c>
       <c r="B99" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493802</v>
+        <v>493626</v>
       </c>
       <c r="R99" t="n">
-        <v>6834925</v>
+        <v>6834837</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10965,57 +10956,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129458908</v>
+        <v>129476578</v>
       </c>
       <c r="B100" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493702</v>
+        <v>493718</v>
       </c>
       <c r="R100" t="n">
-        <v>6834942</v>
+        <v>6834894</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11062,66 +11053,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129458098</v>
+        <v>129455841</v>
       </c>
       <c r="B101" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493682</v>
+        <v>493803</v>
       </c>
       <c r="R101" t="n">
-        <v>6834975</v>
+        <v>6834901</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11180,10 +11162,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476537</v>
+        <v>129476544</v>
       </c>
       <c r="B102" t="n">
-        <v>79660</v>
+        <v>57730</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11191,34 +11173,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493659</v>
+        <v>493634</v>
       </c>
       <c r="R102" t="n">
-        <v>6834945</v>
+        <v>6834983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11277,10 +11267,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476560</v>
+        <v>129476537</v>
       </c>
       <c r="B103" t="n">
-        <v>78827</v>
+        <v>79660</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11288,41 +11278,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493684</v>
+        <v>493659</v>
       </c>
       <c r="R103" t="n">
-        <v>6834860</v>
+        <v>6834945</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11363,7 +11346,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11382,45 +11364,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129476569</v>
+        <v>129455942</v>
       </c>
       <c r="B104" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493626</v>
+        <v>493802</v>
       </c>
       <c r="R104" t="n">
-        <v>6834837</v>
+        <v>6834925</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11467,57 +11458,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129476578</v>
+        <v>129458908</v>
       </c>
       <c r="B105" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493718</v>
+        <v>493702</v>
       </c>
       <c r="R105" t="n">
-        <v>6834894</v>
+        <v>6834942</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11564,57 +11555,66 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129455841</v>
+        <v>129458098</v>
       </c>
       <c r="B106" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493803</v>
+        <v>493682</v>
       </c>
       <c r="R106" t="n">
-        <v>6834901</v>
+        <v>6834975</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12467,10 +12467,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129476558</v>
+        <v>129476584</v>
       </c>
       <c r="B115" t="n">
-        <v>78827</v>
+        <v>79070</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12478,21 +12478,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12502,10 +12502,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493629</v>
+        <v>493670</v>
       </c>
       <c r="R115" t="n">
-        <v>6834823</v>
+        <v>6834995</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12564,10 +12564,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129460271</v>
+        <v>129476558</v>
       </c>
       <c r="B116" t="n">
-        <v>79070</v>
+        <v>78827</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12575,34 +12575,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493731</v>
+        <v>493629</v>
       </c>
       <c r="R116" t="n">
-        <v>6834853</v>
+        <v>6834823</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12649,19 +12649,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129476584</v>
+        <v>129460271</v>
       </c>
       <c r="B117" t="n">
         <v>79070</v>
@@ -12692,14 +12692,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493670</v>
+        <v>493731</v>
       </c>
       <c r="R117" t="n">
-        <v>6834995</v>
+        <v>6834853</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12746,12 +12746,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476552</v>
+        <v>129476548</v>
       </c>
       <c r="B135" t="n">
-        <v>78828</v>
+        <v>91634</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493629</v>
+        <v>493687</v>
       </c>
       <c r="R135" t="n">
-        <v>6834831</v>
+        <v>6834930</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,45 +14566,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129476548</v>
+        <v>129458414</v>
       </c>
       <c r="B136" t="n">
-        <v>91634</v>
+        <v>98756</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493687</v>
+        <v>493670</v>
       </c>
       <c r="R136" t="n">
-        <v>6834930</v>
+        <v>6834981</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14651,12 +14651,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15051,45 +15051,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129458414</v>
+        <v>129476552</v>
       </c>
       <c r="B141" t="n">
-        <v>98756</v>
+        <v>78828</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493670</v>
+        <v>493629</v>
       </c>
       <c r="R141" t="n">
-        <v>6834981</v>
+        <v>6834831</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15136,12 +15136,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15352,45 +15352,54 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129458803</v>
+        <v>129457830</v>
       </c>
       <c r="B144" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493683</v>
+        <v>493676</v>
       </c>
       <c r="R144" t="n">
-        <v>6834951</v>
+        <v>6835001</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15449,53 +15458,54 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129476543</v>
+        <v>129458085</v>
       </c>
       <c r="B145" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493676</v>
+        <v>493690</v>
       </c>
       <c r="R145" t="n">
-        <v>6834800</v>
+        <v>6834972</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15542,19 +15552,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129457830</v>
+        <v>129459852</v>
       </c>
       <c r="B146" t="n">
         <v>98756</v>
@@ -15582,26 +15592,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493676</v>
+        <v>493730</v>
       </c>
       <c r="R146" t="n">
-        <v>6835001</v>
+        <v>6834877</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15660,7 +15661,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129458085</v>
+        <v>129460207</v>
       </c>
       <c r="B147" t="n">
         <v>98756</v>
@@ -15688,26 +15689,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493690</v>
+        <v>493738</v>
       </c>
       <c r="R147" t="n">
-        <v>6834972</v>
+        <v>6834861</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15766,32 +15758,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129459852</v>
+        <v>129458803</v>
       </c>
       <c r="B148" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15801,10 +15793,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493730</v>
+        <v>493683</v>
       </c>
       <c r="R148" t="n">
-        <v>6834877</v>
+        <v>6834951</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15863,45 +15855,53 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129460207</v>
+        <v>129476543</v>
       </c>
       <c r="B149" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493738</v>
+        <v>493676</v>
       </c>
       <c r="R149" t="n">
-        <v>6834861</v>
+        <v>6834800</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,57 +15948,57 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129460421</v>
+        <v>129476535</v>
       </c>
       <c r="B150" t="n">
-        <v>98756</v>
+        <v>79689</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493728</v>
+        <v>493703</v>
       </c>
       <c r="R150" t="n">
-        <v>6834848</v>
+        <v>6834865</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16045,57 +16045,57 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129476535</v>
+        <v>129460421</v>
       </c>
       <c r="B151" t="n">
-        <v>79689</v>
+        <v>98756</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493703</v>
+        <v>493728</v>
       </c>
       <c r="R151" t="n">
-        <v>6834865</v>
+        <v>6834848</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16142,12 +16142,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -17746,54 +17746,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129459653</v>
+        <v>129476531</v>
       </c>
       <c r="B168" t="n">
-        <v>98756</v>
+        <v>79689</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493740</v>
+        <v>493636</v>
       </c>
       <c r="R168" t="n">
-        <v>6834887</v>
+        <v>6834906</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17840,57 +17831,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129459536</v>
+        <v>129476581</v>
       </c>
       <c r="B169" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>493723</v>
+        <v>493677</v>
       </c>
       <c r="R169" t="n">
-        <v>6834898</v>
+        <v>6834943</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17937,66 +17928,57 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129456373</v>
+        <v>129476575</v>
       </c>
       <c r="B170" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>493796</v>
+        <v>493728</v>
       </c>
       <c r="R170" t="n">
-        <v>6834937</v>
+        <v>6834886</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18043,22 +18025,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129476531</v>
+        <v>129476570</v>
       </c>
       <c r="B171" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18066,21 +18048,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18090,10 +18072,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>493636</v>
+        <v>493628</v>
       </c>
       <c r="R171" t="n">
-        <v>6834906</v>
+        <v>6834790</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18152,10 +18134,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476575</v>
+        <v>129476587</v>
       </c>
       <c r="B172" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18163,21 +18145,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18187,10 +18169,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493728</v>
+        <v>493659</v>
       </c>
       <c r="R172" t="n">
-        <v>6834886</v>
+        <v>6834945</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18249,45 +18231,54 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129476587</v>
+        <v>129459653</v>
       </c>
       <c r="B173" t="n">
-        <v>78736</v>
+        <v>98756</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>493659</v>
+        <v>493740</v>
       </c>
       <c r="R173" t="n">
-        <v>6834945</v>
+        <v>6834887</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18334,57 +18325,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129476570</v>
+        <v>129459536</v>
       </c>
       <c r="B174" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>493628</v>
+        <v>493723</v>
       </c>
       <c r="R174" t="n">
-        <v>6834790</v>
+        <v>6834898</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18431,57 +18422,66 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129476581</v>
+        <v>129456373</v>
       </c>
       <c r="B175" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>493677</v>
+        <v>493796</v>
       </c>
       <c r="R175" t="n">
-        <v>6834943</v>
+        <v>6834937</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,57 +18528,66 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129459599</v>
+        <v>129456055</v>
       </c>
       <c r="B176" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493726</v>
+        <v>493817</v>
       </c>
       <c r="R176" t="n">
-        <v>6834891</v>
+        <v>6834930</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,45 +18646,54 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129460260</v>
+        <v>129458467</v>
       </c>
       <c r="B177" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493731</v>
+        <v>493646</v>
       </c>
       <c r="R177" t="n">
-        <v>6834851</v>
+        <v>6835015</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18734,54 +18752,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129456055</v>
+        <v>129459599</v>
       </c>
       <c r="B178" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493817</v>
+        <v>493726</v>
       </c>
       <c r="R178" t="n">
-        <v>6834930</v>
+        <v>6834891</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18840,32 +18849,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129459676</v>
+        <v>129460260</v>
       </c>
       <c r="B179" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18875,10 +18884,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493727</v>
+        <v>493731</v>
       </c>
       <c r="R179" t="n">
-        <v>6834879</v>
+        <v>6834851</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18937,7 +18946,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129458467</v>
+        <v>129459676</v>
       </c>
       <c r="B180" t="n">
         <v>98756</v>
@@ -18965,26 +18974,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493646</v>
+        <v>493727</v>
       </c>
       <c r="R180" t="n">
-        <v>6835015</v>
+        <v>6834879</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21664,45 +21664,54 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525320</v>
+        <v>129525477</v>
       </c>
       <c r="B207" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493859</v>
+        <v>493823</v>
       </c>
       <c r="R207" t="n">
-        <v>6834674</v>
+        <v>6834595</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21735,11 +21744,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21766,45 +21770,54 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129525442</v>
+        <v>129525078</v>
       </c>
       <c r="B208" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493925</v>
+        <v>493886</v>
       </c>
       <c r="R208" t="n">
-        <v>6834617</v>
+        <v>6834673</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21863,7 +21876,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129525477</v>
+        <v>129524983</v>
       </c>
       <c r="B209" t="n">
         <v>98756</v>
@@ -21893,7 +21906,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -21903,14 +21916,14 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>493823</v>
+        <v>493871</v>
       </c>
       <c r="R209" t="n">
-        <v>6834595</v>
+        <v>6834690</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21957,66 +21970,57 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129525078</v>
+        <v>129525442</v>
       </c>
       <c r="B210" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493886</v>
+        <v>493925</v>
       </c>
       <c r="R210" t="n">
-        <v>6834673</v>
+        <v>6834617</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22075,54 +22079,45 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129524983</v>
+        <v>129525320</v>
       </c>
       <c r="B211" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493871</v>
+        <v>493859</v>
       </c>
       <c r="R211" t="n">
-        <v>6834690</v>
+        <v>6834674</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22157,6 +22152,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
@@ -22169,12 +22169,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
@@ -22675,45 +22675,54 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129525382</v>
+        <v>129525489</v>
       </c>
       <c r="B217" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>493822</v>
+        <v>493817</v>
       </c>
       <c r="R217" t="n">
-        <v>6834648</v>
+        <v>6834579</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22772,54 +22781,45 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129525489</v>
+        <v>129525382</v>
       </c>
       <c r="B218" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>493817</v>
+        <v>493822</v>
       </c>
       <c r="R218" t="n">
-        <v>6834579</v>
+        <v>6834648</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8182,7 +8182,7 @@
         <v>129460134</v>
       </c>
       <c r="B72" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>129460004</v>
       </c>
       <c r="B73" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129460228</v>
       </c>
       <c r="B74" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8479,10 +8479,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476572</v>
+        <v>129476586</v>
       </c>
       <c r="B75" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8490,21 +8490,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493675</v>
+        <v>493684</v>
       </c>
       <c r="R75" t="n">
-        <v>6834825</v>
+        <v>6834869</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8579,7 +8579,7 @@
         <v>129476556</v>
       </c>
       <c r="B76" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8673,10 +8673,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129476586</v>
+        <v>129476572</v>
       </c>
       <c r="B77" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,21 +8684,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493684</v>
+        <v>493675</v>
       </c>
       <c r="R77" t="n">
-        <v>6834869</v>
+        <v>6834825</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8770,45 +8770,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129461154</v>
+        <v>129456176</v>
       </c>
       <c r="B78" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493629</v>
+        <v>493813</v>
       </c>
       <c r="R78" t="n">
-        <v>6834827</v>
+        <v>6834955</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8867,45 +8876,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129460036</v>
+        <v>129457973</v>
       </c>
       <c r="B79" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493728</v>
+        <v>493684</v>
       </c>
       <c r="R79" t="n">
-        <v>6834868</v>
+        <v>6834986</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8964,45 +8982,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129460662</v>
+        <v>129476554</v>
       </c>
       <c r="B80" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493658</v>
+        <v>493648</v>
       </c>
       <c r="R80" t="n">
-        <v>6834840</v>
+        <v>6834929</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9043,18 +9070,19 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9064,7 +9092,7 @@
         <v>129476585</v>
       </c>
       <c r="B81" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9158,54 +9186,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129476554</v>
+        <v>129461154</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493648</v>
+        <v>493629</v>
       </c>
       <c r="R82" t="n">
-        <v>6834929</v>
+        <v>6834827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9246,73 +9265,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129456176</v>
+        <v>129460036</v>
       </c>
       <c r="B83" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493813</v>
+        <v>493728</v>
       </c>
       <c r="R83" t="n">
-        <v>6834955</v>
+        <v>6834868</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9371,54 +9380,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129457973</v>
+        <v>129460662</v>
       </c>
       <c r="B84" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493684</v>
+        <v>493658</v>
       </c>
       <c r="R84" t="n">
-        <v>6834986</v>
+        <v>6834840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9477,32 +9477,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129457913</v>
+        <v>129457992</v>
       </c>
       <c r="B85" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9512,10 +9512,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493686</v>
+        <v>493684</v>
       </c>
       <c r="R85" t="n">
-        <v>6834989</v>
+        <v>6834988</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9574,57 +9574,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129460883</v>
+        <v>129476547</v>
       </c>
       <c r="B86" t="n">
-        <v>98756</v>
+        <v>79099</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493637</v>
+        <v>493722</v>
       </c>
       <c r="R86" t="n">
-        <v>6834831</v>
+        <v>6834900</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9668,66 +9659,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129457745</v>
+        <v>129476579</v>
       </c>
       <c r="B87" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493678</v>
+        <v>493687</v>
       </c>
       <c r="R87" t="n">
-        <v>6835020</v>
+        <v>6834917</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9774,57 +9756,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129457992</v>
+        <v>129476589</v>
       </c>
       <c r="B88" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493684</v>
+        <v>493641</v>
       </c>
       <c r="R88" t="n">
-        <v>6834988</v>
+        <v>6834918</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9871,57 +9853,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129476547</v>
+        <v>129457913</v>
       </c>
       <c r="B89" t="n">
-        <v>79094</v>
+        <v>98768</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493722</v>
+        <v>493686</v>
       </c>
       <c r="R89" t="n">
-        <v>6834900</v>
+        <v>6834989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9968,60 +9950,69 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129476579</v>
+        <v>129460883</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493687</v>
+        <v>493637</v>
       </c>
       <c r="R90" t="n">
-        <v>6834917</v>
+        <v>6834831</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10065,57 +10056,66 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129476589</v>
+        <v>129457745</v>
       </c>
       <c r="B91" t="n">
-        <v>92863</v>
+        <v>98768</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>493641</v>
+        <v>493678</v>
       </c>
       <c r="R91" t="n">
-        <v>6834918</v>
+        <v>6835020</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10162,22 +10162,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129476583</v>
+        <v>129476532</v>
       </c>
       <c r="B92" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>493664</v>
+        <v>493619</v>
       </c>
       <c r="R92" t="n">
-        <v>6834992</v>
+        <v>6834843</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10271,45 +10271,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129476532</v>
+        <v>129476555</v>
       </c>
       <c r="B93" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493619</v>
+        <v>493666</v>
       </c>
       <c r="R93" t="n">
-        <v>6834843</v>
+        <v>6834982</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10350,6 +10359,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10368,10 +10378,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129476566</v>
+        <v>129476583</v>
       </c>
       <c r="B94" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10403,10 +10413,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493646</v>
+        <v>493664</v>
       </c>
       <c r="R94" t="n">
-        <v>6834937</v>
+        <v>6834992</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10465,10 +10475,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129476574</v>
+        <v>129476566</v>
       </c>
       <c r="B95" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10500,10 +10510,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493702</v>
+        <v>493646</v>
       </c>
       <c r="R95" t="n">
-        <v>6834858</v>
+        <v>6834937</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10562,54 +10572,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129476555</v>
+        <v>129476574</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493666</v>
+        <v>493702</v>
       </c>
       <c r="R96" t="n">
-        <v>6834982</v>
+        <v>6834858</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10650,7 +10651,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>129476571</v>
       </c>
       <c r="B97" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>129476560</v>
       </c>
       <c r="B98" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10871,45 +10871,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129476569</v>
+        <v>129455942</v>
       </c>
       <c r="B99" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493626</v>
+        <v>493802</v>
       </c>
       <c r="R99" t="n">
-        <v>6834837</v>
+        <v>6834925</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10956,57 +10965,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129476578</v>
+        <v>129458908</v>
       </c>
       <c r="B100" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493718</v>
+        <v>493702</v>
       </c>
       <c r="R100" t="n">
-        <v>6834894</v>
+        <v>6834942</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11053,57 +11062,66 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129455841</v>
+        <v>129458098</v>
       </c>
       <c r="B101" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493803</v>
+        <v>493682</v>
       </c>
       <c r="R101" t="n">
-        <v>6834901</v>
+        <v>6834975</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11162,10 +11180,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476544</v>
+        <v>129476569</v>
       </c>
       <c r="B102" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11173,42 +11191,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493634</v>
+        <v>493626</v>
       </c>
       <c r="R102" t="n">
-        <v>6834983</v>
+        <v>6834837</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11267,10 +11277,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476537</v>
+        <v>129476578</v>
       </c>
       <c r="B103" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11278,21 +11288,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11302,10 +11312,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493659</v>
+        <v>493718</v>
       </c>
       <c r="R103" t="n">
-        <v>6834945</v>
+        <v>6834894</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11364,54 +11374,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129455942</v>
+        <v>129455841</v>
       </c>
       <c r="B104" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493802</v>
+        <v>493803</v>
       </c>
       <c r="R104" t="n">
-        <v>6834925</v>
+        <v>6834901</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11470,45 +11471,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129458908</v>
+        <v>129476544</v>
       </c>
       <c r="B105" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493702</v>
+        <v>493634</v>
       </c>
       <c r="R105" t="n">
-        <v>6834942</v>
+        <v>6834983</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,66 +11564,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129458098</v>
+        <v>129476537</v>
       </c>
       <c r="B106" t="n">
-        <v>98756</v>
+        <v>79665</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493682</v>
+        <v>493659</v>
       </c>
       <c r="R106" t="n">
-        <v>6834975</v>
+        <v>6834945</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11661,57 +11661,66 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129458915</v>
+        <v>129456312</v>
       </c>
       <c r="B107" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493698</v>
+        <v>493787</v>
       </c>
       <c r="R107" t="n">
-        <v>6834942</v>
+        <v>6834957</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11770,10 +11779,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129476577</v>
+        <v>129458915</v>
       </c>
       <c r="B108" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11801,14 +11810,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493707</v>
+        <v>493698</v>
       </c>
       <c r="R108" t="n">
-        <v>6834895</v>
+        <v>6834942</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11855,66 +11864,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129456312</v>
+        <v>129476577</v>
       </c>
       <c r="B109" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493787</v>
+        <v>493707</v>
       </c>
       <c r="R109" t="n">
-        <v>6834957</v>
+        <v>6834895</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11961,12 +11961,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
         <v>129456198</v>
       </c>
       <c r="B110" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>129458436</v>
       </c>
       <c r="B111" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>129476538</v>
       </c>
       <c r="B112" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>129476568</v>
       </c>
       <c r="B113" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>129461581</v>
       </c>
       <c r="B114" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12467,10 +12467,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129476584</v>
+        <v>129460271</v>
       </c>
       <c r="B115" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12498,14 +12498,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493670</v>
+        <v>493731</v>
       </c>
       <c r="R115" t="n">
-        <v>6834995</v>
+        <v>6834853</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12552,22 +12552,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476558</v>
+        <v>129476584</v>
       </c>
       <c r="B116" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12575,21 +12575,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12599,10 +12599,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493629</v>
+        <v>493670</v>
       </c>
       <c r="R116" t="n">
-        <v>6834823</v>
+        <v>6834995</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12661,10 +12661,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129460271</v>
+        <v>129476558</v>
       </c>
       <c r="B117" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12672,34 +12672,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493731</v>
+        <v>493629</v>
       </c>
       <c r="R117" t="n">
-        <v>6834853</v>
+        <v>6834823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12746,12 +12746,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12761,7 +12761,7 @@
         <v>129459508</v>
       </c>
       <c r="B118" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>129459731</v>
       </c>
       <c r="B119" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>129459774</v>
       </c>
       <c r="B120" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>129476541</v>
       </c>
       <c r="B121" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13164,52 +13164,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476559</v>
+        <v>129476590</v>
       </c>
       <c r="B122" t="n">
-        <v>78827</v>
+        <v>92869</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493626</v>
+        <v>493628</v>
       </c>
       <c r="R122" t="n">
-        <v>6834843</v>
+        <v>6834891</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13250,7 +13243,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13269,45 +13261,52 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129476590</v>
+        <v>129476559</v>
       </c>
       <c r="B123" t="n">
-        <v>92863</v>
+        <v>78832</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493628</v>
+        <v>493626</v>
       </c>
       <c r="R123" t="n">
-        <v>6834891</v>
+        <v>6834843</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13348,6 +13347,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13369,7 +13369,7 @@
         <v>129461070</v>
       </c>
       <c r="B124" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>129457707</v>
       </c>
       <c r="B125" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>129456013</v>
       </c>
       <c r="B126" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>129456404</v>
       </c>
       <c r="B127" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>129456103</v>
       </c>
       <c r="B128" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>129476550</v>
       </c>
       <c r="B129" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>129476530</v>
       </c>
       <c r="B130" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>129458645</v>
       </c>
       <c r="B131" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>129455888</v>
       </c>
       <c r="B132" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>129456470</v>
       </c>
       <c r="B133" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>129458700</v>
       </c>
       <c r="B134" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129476548</v>
+        <v>129476588</v>
       </c>
       <c r="B135" t="n">
-        <v>91634</v>
+        <v>78741</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>493687</v>
+        <v>493619</v>
       </c>
       <c r="R135" t="n">
-        <v>6834930</v>
+        <v>6834998</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14566,45 +14566,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129458414</v>
+        <v>129476548</v>
       </c>
       <c r="B136" t="n">
-        <v>98756</v>
+        <v>91640</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>493670</v>
+        <v>493687</v>
       </c>
       <c r="R136" t="n">
-        <v>6834981</v>
+        <v>6834930</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14651,22 +14651,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129476588</v>
+        <v>129476552</v>
       </c>
       <c r="B137" t="n">
-        <v>78736</v>
+        <v>78833</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14674,21 +14674,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>493619</v>
+        <v>493629</v>
       </c>
       <c r="R137" t="n">
-        <v>6834998</v>
+        <v>6834831</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14763,7 +14763,7 @@
         <v>129476573</v>
       </c>
       <c r="B138" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>129459901</v>
       </c>
       <c r="B139" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>129476580</v>
       </c>
       <c r="B140" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15051,45 +15051,54 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129476552</v>
+        <v>129476553</v>
       </c>
       <c r="B141" t="n">
-        <v>78828</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>493629</v>
+        <v>493591</v>
       </c>
       <c r="R141" t="n">
-        <v>6834831</v>
+        <v>6835008</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15130,6 +15139,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15148,54 +15158,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129476553</v>
+        <v>129458414</v>
       </c>
       <c r="B142" t="n">
-        <v>8450</v>
+        <v>98768</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>493591</v>
+        <v>493670</v>
       </c>
       <c r="R142" t="n">
-        <v>6835008</v>
+        <v>6834981</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15236,19 +15237,18 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15258,7 +15258,7 @@
         <v>129476540</v>
       </c>
       <c r="B143" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15352,54 +15352,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129457830</v>
+        <v>129458803</v>
       </c>
       <c r="B144" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>493676</v>
+        <v>493683</v>
       </c>
       <c r="R144" t="n">
-        <v>6835001</v>
+        <v>6834951</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15458,54 +15449,53 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129458085</v>
+        <v>129476543</v>
       </c>
       <c r="B145" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>493690</v>
+        <v>493676</v>
       </c>
       <c r="R145" t="n">
-        <v>6834972</v>
+        <v>6834800</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15552,22 +15542,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129459852</v>
+        <v>129457830</v>
       </c>
       <c r="B146" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15592,17 +15582,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>493730</v>
+        <v>493676</v>
       </c>
       <c r="R146" t="n">
-        <v>6834877</v>
+        <v>6835001</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15661,10 +15660,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129460207</v>
+        <v>129458085</v>
       </c>
       <c r="B147" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15689,17 +15688,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>493738</v>
+        <v>493690</v>
       </c>
       <c r="R147" t="n">
-        <v>6834861</v>
+        <v>6834972</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15758,32 +15766,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129458803</v>
+        <v>129459852</v>
       </c>
       <c r="B148" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15793,10 +15801,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493683</v>
+        <v>493730</v>
       </c>
       <c r="R148" t="n">
-        <v>6834951</v>
+        <v>6834877</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15855,53 +15863,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129476543</v>
+        <v>129460207</v>
       </c>
       <c r="B149" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493676</v>
+        <v>493738</v>
       </c>
       <c r="R149" t="n">
-        <v>6834800</v>
+        <v>6834861</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,22 +15948,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129476535</v>
+        <v>129476539</v>
       </c>
       <c r="B150" t="n">
-        <v>79689</v>
+        <v>90619</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15971,21 +15971,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493703</v>
+        <v>493652</v>
       </c>
       <c r="R150" t="n">
-        <v>6834865</v>
+        <v>6834985</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16057,45 +16057,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129460421</v>
+        <v>129476535</v>
       </c>
       <c r="B151" t="n">
-        <v>98756</v>
+        <v>79694</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493728</v>
+        <v>493703</v>
       </c>
       <c r="R151" t="n">
-        <v>6834848</v>
+        <v>6834865</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16142,57 +16142,57 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129476539</v>
+        <v>129460421</v>
       </c>
       <c r="B152" t="n">
-        <v>90613</v>
+        <v>98768</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>493652</v>
+        <v>493728</v>
       </c>
       <c r="R152" t="n">
-        <v>6834985</v>
+        <v>6834848</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16239,44 +16239,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129460467</v>
+        <v>129460288</v>
       </c>
       <c r="B153" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16286,10 +16286,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493728</v>
+        <v>493733</v>
       </c>
       <c r="R153" t="n">
-        <v>6834842</v>
+        <v>6834848</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16348,45 +16348,54 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129476567</v>
+        <v>129458972</v>
       </c>
       <c r="B154" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>493634</v>
+        <v>493700</v>
       </c>
       <c r="R154" t="n">
-        <v>6834889</v>
+        <v>6834942</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16433,22 +16442,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129476576</v>
+        <v>129460467</v>
       </c>
       <c r="B155" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16476,14 +16485,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493725</v>
+        <v>493728</v>
       </c>
       <c r="R155" t="n">
-        <v>6834888</v>
+        <v>6834842</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16530,57 +16539,57 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129460288</v>
+        <v>129476567</v>
       </c>
       <c r="B156" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493733</v>
+        <v>493634</v>
       </c>
       <c r="R156" t="n">
-        <v>6834848</v>
+        <v>6834889</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16627,66 +16636,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129458972</v>
+        <v>129476576</v>
       </c>
       <c r="B157" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493700</v>
+        <v>493725</v>
       </c>
       <c r="R157" t="n">
-        <v>6834942</v>
+        <v>6834888</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16733,12 +16733,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16748,7 +16748,7 @@
         <v>129476546</v>
       </c>
       <c r="B158" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129476533</v>
+        <v>129476549</v>
       </c>
       <c r="B159" t="n">
-        <v>79689</v>
+        <v>91640</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16853,21 +16853,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>493678</v>
+        <v>493677</v>
       </c>
       <c r="R159" t="n">
-        <v>6834780</v>
+        <v>6835005</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16942,7 +16942,7 @@
         <v>129459208</v>
       </c>
       <c r="B160" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17036,10 +17036,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129476536</v>
+        <v>129457857</v>
       </c>
       <c r="B161" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17047,34 +17047,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>493642</v>
+        <v>493676</v>
       </c>
       <c r="R161" t="n">
-        <v>6834998</v>
+        <v>6835001</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17121,22 +17121,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129457857</v>
+        <v>129458226</v>
       </c>
       <c r="B162" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493676</v>
+        <v>493670</v>
       </c>
       <c r="R162" t="n">
-        <v>6835001</v>
+        <v>6834981</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17230,10 +17230,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129458226</v>
+        <v>129476533</v>
       </c>
       <c r="B163" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17241,34 +17241,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>493670</v>
+        <v>493678</v>
       </c>
       <c r="R163" t="n">
-        <v>6834981</v>
+        <v>6834780</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17315,22 +17315,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129476549</v>
+        <v>129476536</v>
       </c>
       <c r="B164" t="n">
-        <v>91634</v>
+        <v>79694</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,21 +17338,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17362,10 +17362,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493677</v>
+        <v>493642</v>
       </c>
       <c r="R164" t="n">
-        <v>6835005</v>
+        <v>6834998</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17427,7 +17427,7 @@
         <v>129459449</v>
       </c>
       <c r="B165" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>129459953</v>
       </c>
       <c r="B166" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>129476562</v>
       </c>
       <c r="B167" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17746,10 +17746,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129476531</v>
+        <v>129476587</v>
       </c>
       <c r="B168" t="n">
-        <v>79689</v>
+        <v>78741</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17757,21 +17757,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17781,10 +17781,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>493636</v>
+        <v>493659</v>
       </c>
       <c r="R168" t="n">
-        <v>6834906</v>
+        <v>6834945</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17846,7 +17846,7 @@
         <v>129476581</v>
       </c>
       <c r="B169" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>129476575</v>
       </c>
       <c r="B170" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>129476570</v>
       </c>
       <c r="B171" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18134,10 +18134,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129476587</v>
+        <v>129476531</v>
       </c>
       <c r="B172" t="n">
-        <v>78736</v>
+        <v>79694</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18145,21 +18145,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18169,10 +18169,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>493659</v>
+        <v>493636</v>
       </c>
       <c r="R172" t="n">
-        <v>6834945</v>
+        <v>6834906</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18234,7 +18234,7 @@
         <v>129459653</v>
       </c>
       <c r="B173" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>129459536</v>
       </c>
       <c r="B174" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>129456373</v>
       </c>
       <c r="B175" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18540,54 +18540,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129456055</v>
+        <v>129459599</v>
       </c>
       <c r="B176" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493817</v>
+        <v>493726</v>
       </c>
       <c r="R176" t="n">
-        <v>6834930</v>
+        <v>6834891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18646,54 +18637,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129458467</v>
+        <v>129460260</v>
       </c>
       <c r="B177" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493646</v>
+        <v>493731</v>
       </c>
       <c r="R177" t="n">
-        <v>6835015</v>
+        <v>6834851</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18752,45 +18734,54 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129459599</v>
+        <v>129456055</v>
       </c>
       <c r="B178" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>493726</v>
+        <v>493817</v>
       </c>
       <c r="R178" t="n">
-        <v>6834891</v>
+        <v>6834930</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18849,32 +18840,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129460260</v>
+        <v>129459676</v>
       </c>
       <c r="B179" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18884,10 +18875,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>493731</v>
+        <v>493727</v>
       </c>
       <c r="R179" t="n">
-        <v>6834851</v>
+        <v>6834879</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18946,10 +18937,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129459676</v>
+        <v>129458467</v>
       </c>
       <c r="B180" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18974,17 +18965,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>493727</v>
+        <v>493646</v>
       </c>
       <c r="R180" t="n">
-        <v>6834879</v>
+        <v>6835015</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19043,45 +19043,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129459964</v>
+        <v>129476551</v>
       </c>
       <c r="B181" t="n">
-        <v>98756</v>
+        <v>78833</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>493726</v>
+        <v>493632</v>
       </c>
       <c r="R181" t="n">
-        <v>6834867</v>
+        <v>6834827</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19128,12 +19128,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
         <v>129476561</v>
       </c>
       <c r="B182" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19237,45 +19237,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129476551</v>
+        <v>129459964</v>
       </c>
       <c r="B183" t="n">
-        <v>78828</v>
+        <v>98768</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>493632</v>
+        <v>493726</v>
       </c>
       <c r="R183" t="n">
-        <v>6834827</v>
+        <v>6834867</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19322,12 +19322,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19337,7 +19337,7 @@
         <v>129459836</v>
       </c>
       <c r="B184" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>129525028</v>
       </c>
       <c r="B185" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>129525359</v>
       </c>
       <c r="B186" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>129525456</v>
       </c>
       <c r="B187" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>129525566</v>
       </c>
       <c r="B188" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>129525479</v>
       </c>
       <c r="B189" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19925,10 +19925,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129525603</v>
+        <v>129525395</v>
       </c>
       <c r="B190" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -19965,14 +19965,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>493825</v>
+        <v>493923</v>
       </c>
       <c r="R190" t="n">
-        <v>6834572</v>
+        <v>6834647</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20019,22 +20019,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129525395</v>
+        <v>129525603</v>
       </c>
       <c r="B191" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -20071,14 +20071,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>493923</v>
+        <v>493825</v>
       </c>
       <c r="R191" t="n">
-        <v>6834647</v>
+        <v>6834572</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20125,12 +20125,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -20140,7 +20140,7 @@
         <v>129525463</v>
       </c>
       <c r="B192" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>129525450</v>
       </c>
       <c r="B193" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>129525370</v>
       </c>
       <c r="B194" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>129525020</v>
       </c>
       <c r="B195" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>129525895</v>
       </c>
       <c r="B196" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>129525059</v>
       </c>
       <c r="B197" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20737,54 +20737,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129525089</v>
+        <v>129525351</v>
       </c>
       <c r="B198" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>493895</v>
+        <v>493874</v>
       </c>
       <c r="R198" t="n">
-        <v>6834684</v>
+        <v>6834658</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20831,12 +20822,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
@@ -20846,7 +20837,7 @@
         <v>129525466</v>
       </c>
       <c r="B199" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20940,45 +20931,54 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129525351</v>
+        <v>129525089</v>
       </c>
       <c r="B200" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>493874</v>
+        <v>493895</v>
       </c>
       <c r="R200" t="n">
-        <v>6834658</v>
+        <v>6834684</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21025,57 +21025,66 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129525470</v>
+        <v>129525496</v>
       </c>
       <c r="B201" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>493900</v>
+        <v>493821</v>
       </c>
       <c r="R201" t="n">
-        <v>6834623</v>
+        <v>6834572</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21122,66 +21131,57 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129525496</v>
+        <v>129525470</v>
       </c>
       <c r="B202" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>493821</v>
+        <v>493900</v>
       </c>
       <c r="R202" t="n">
-        <v>6834572</v>
+        <v>6834623</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21228,22 +21228,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129525012</v>
+        <v>129525041</v>
       </c>
       <c r="B203" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -21280,14 +21280,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>493866</v>
+        <v>493881</v>
       </c>
       <c r="R203" t="n">
-        <v>6834688</v>
+        <v>6834662</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21334,22 +21334,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129525041</v>
+        <v>129525012</v>
       </c>
       <c r="B204" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -21386,14 +21386,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>493881</v>
+        <v>493866</v>
       </c>
       <c r="R204" t="n">
-        <v>6834662</v>
+        <v>6834688</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21440,22 +21440,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129525474</v>
+        <v>129525022</v>
       </c>
       <c r="B205" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>493908</v>
+        <v>493867</v>
       </c>
       <c r="R205" t="n">
-        <v>6834595</v>
+        <v>6834661</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21558,10 +21558,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129525022</v>
+        <v>129525474</v>
       </c>
       <c r="B206" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>493867</v>
+        <v>493908</v>
       </c>
       <c r="R206" t="n">
-        <v>6834661</v>
+        <v>6834595</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21664,54 +21664,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129525477</v>
+        <v>129525442</v>
       </c>
       <c r="B207" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>493823</v>
+        <v>493925</v>
       </c>
       <c r="R207" t="n">
-        <v>6834595</v>
+        <v>6834617</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21758,66 +21749,57 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129525078</v>
+        <v>129525320</v>
       </c>
       <c r="B208" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493886</v>
+        <v>493859</v>
       </c>
       <c r="R208" t="n">
-        <v>6834673</v>
+        <v>6834674</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21852,6 +21834,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
@@ -21864,12 +21851,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
@@ -21879,7 +21866,7 @@
         <v>129524983</v>
       </c>
       <c r="B209" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21982,45 +21969,54 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129525442</v>
+        <v>129525477</v>
       </c>
       <c r="B210" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>493925</v>
+        <v>493823</v>
       </c>
       <c r="R210" t="n">
-        <v>6834617</v>
+        <v>6834595</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22067,57 +22063,66 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129525320</v>
+        <v>129525078</v>
       </c>
       <c r="B211" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>493859</v>
+        <v>493886</v>
       </c>
       <c r="R211" t="n">
-        <v>6834674</v>
+        <v>6834673</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22152,11 +22157,6 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
@@ -22169,44 +22169,44 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129525462</v>
+        <v>129525429</v>
       </c>
       <c r="B212" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22216,10 +22216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>493832</v>
+        <v>493788</v>
       </c>
       <c r="R212" t="n">
-        <v>6834595</v>
+        <v>6834656</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22278,45 +22278,54 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129525429</v>
+        <v>129525001</v>
       </c>
       <c r="B213" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>493788</v>
+        <v>493870</v>
       </c>
       <c r="R213" t="n">
-        <v>6834656</v>
+        <v>6834690</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22375,10 +22384,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129525001</v>
+        <v>129525451</v>
       </c>
       <c r="B214" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22403,26 +22412,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>493870</v>
+        <v>493788</v>
       </c>
       <c r="R214" t="n">
-        <v>6834690</v>
+        <v>6834656</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22481,32 +22481,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129525451</v>
+        <v>129525462</v>
       </c>
       <c r="B215" t="n">
-        <v>98756</v>
+        <v>92869</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22516,10 +22516,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>493788</v>
+        <v>493832</v>
       </c>
       <c r="R215" t="n">
-        <v>6834656</v>
+        <v>6834595</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22581,7 +22581,7 @@
         <v>129525529</v>
       </c>
       <c r="B216" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22675,54 +22675,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129525489</v>
+        <v>129525382</v>
       </c>
       <c r="B217" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>493817</v>
+        <v>493822</v>
       </c>
       <c r="R217" t="n">
-        <v>6834579</v>
+        <v>6834648</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22781,45 +22772,54 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129525382</v>
+        <v>129525489</v>
       </c>
       <c r="B218" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>493822</v>
+        <v>493817</v>
       </c>
       <c r="R218" t="n">
-        <v>6834648</v>
+        <v>6834579</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22881,7 +22881,7 @@
         <v>129525130</v>
       </c>
       <c r="B219" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>129525418</v>
       </c>
       <c r="B220" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>129525528</v>
       </c>
       <c r="B221" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>129525680</v>
       </c>
       <c r="B222" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>129525347</v>
       </c>
       <c r="B223" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>129525601</v>
       </c>
       <c r="B224" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>129525445</v>
       </c>
       <c r="B225" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>

--- a/artfynd/A 52437-2025 artfynd.xlsx
+++ b/artfynd/A 52437-2025 artfynd.xlsx
@@ -8179,45 +8179,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129460134</v>
+        <v>129476586</v>
       </c>
       <c r="B72" t="n">
-        <v>98768</v>
+        <v>78742</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493738</v>
+        <v>493684</v>
       </c>
       <c r="R72" t="n">
-        <v>6834870</v>
+        <v>6834869</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8264,57 +8264,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129460004</v>
+        <v>129476572</v>
       </c>
       <c r="B73" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493728</v>
+        <v>493675</v>
       </c>
       <c r="R73" t="n">
-        <v>6834868</v>
+        <v>6834825</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,66 +8361,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129460228</v>
+        <v>129476556</v>
       </c>
       <c r="B74" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493736</v>
+        <v>493810</v>
       </c>
       <c r="R74" t="n">
-        <v>6834865</v>
+        <v>6834883</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,57 +8458,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129476586</v>
+        <v>129460134</v>
       </c>
       <c r="B75" t="n">
-        <v>78741</v>
+        <v>98769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493684</v>
+        <v>493738</v>
       </c>
       <c r="R75" t="n">
-        <v>6834869</v>
+        <v>6834870</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8564,57 +8555,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129476556</v>
+        <v>129460004</v>
       </c>
       <c r="B76" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>493810</v>
+        <v>493728</v>
       </c>
       <c r="R76" t="n">
-        <v>6834883</v>
+        <v>6834868</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8661,57 +8652,66 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129476572</v>
+        <v>129460228</v>
       </c>
       <c r="B77" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>493675</v>
+        <v>493736</v>
       </c>
       <c r="R77" t="n">
-        <v>6834825</v>
+        <v>6834865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,66 +8758,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129456176</v>
+        <v>129461154</v>
       </c>
       <c r="B78" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>493813</v>
+        <v>493629</v>
       </c>
       <c r="R78" t="n">
-        <v>6834955</v>
+        <v>6834827</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8876,54 +8867,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129457973</v>
+        <v>129460036</v>
       </c>
       <c r="B79" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>493684</v>
+        <v>493728</v>
       </c>
       <c r="R79" t="n">
-        <v>6834986</v>
+        <v>6834868</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8982,54 +8964,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129476554</v>
+        <v>129460662</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>493648</v>
+        <v>493658</v>
       </c>
       <c r="R80" t="n">
-        <v>6834929</v>
+        <v>6834840</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9070,64 +9043,72 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129476585</v>
+        <v>129476554</v>
       </c>
       <c r="B81" t="n">
-        <v>78741</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>493700</v>
+        <v>493648</v>
       </c>
       <c r="R81" t="n">
-        <v>6834837</v>
+        <v>6834929</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9168,6 +9149,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9186,10 +9168,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129461154</v>
+        <v>129476585</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9197,34 +9179,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493629</v>
+        <v>493700</v>
       </c>
       <c r="R82" t="n">
-        <v>6834827</v>
+        <v>6834837</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9271,57 +9253,66 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129460036</v>
+        <v>129456176</v>
       </c>
       <c r="B83" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493728</v>
+        <v>493813</v>
       </c>
       <c r="R83" t="n">
-        <v>6834868</v>
+        <v>6834955</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9380,45 +9371,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129460662</v>
+        <v>129457973</v>
       </c>
       <c r="B84" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493658</v>
+        <v>493684</v>
       </c>
       <c r="R84" t="n">
-        <v>6834840</v>
+        <v>6834986</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9477,45 +9477,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129457992</v>
+        <v>129457745</v>
       </c>
       <c r="B85" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493684</v>
+        <v>493678</v>
       </c>
       <c r="R85" t="n">
-        <v>6834988</v>
+        <v>6835020</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9574,10 +9583,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129476547</v>
+        <v>129476589</v>
       </c>
       <c r="B86" t="n">
-        <v>79099</v>
+        <v>92870</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9585,21 +9594,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9609,10 +9618,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493722</v>
+        <v>493641</v>
       </c>
       <c r="R86" t="n">
-        <v>6834900</v>
+        <v>6834918</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9671,10 +9680,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129476579</v>
+        <v>129457992</v>
       </c>
       <c r="B87" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9702,14 +9711,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493687</v>
+        <v>493684</v>
       </c>
       <c r="R87" t="n">
-        <v>6834917</v>
+        <v>6834988</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9756,22 +9765,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129476589</v>
+        <v>129476547</v>
       </c>
       <c r="B88" t="n">
-        <v>92869</v>
+        <v>79100</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9779,21 +9788,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9803,10 +9812,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>493641</v>
+        <v>493722</v>
       </c>
       <c r="R88" t="n">
-        <v>6834918</v>
+        <v>6834900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9865,45 +9874,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129457913</v>
+        <v>129476579</v>
       </c>
       <c r="B89" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>493686</v>
+        <v>493687</v>
       </c>
       <c r="R89" t="n">
-        <v>6834989</v>
+        <v>6834917</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9950,22 +9959,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129460883</v>
+        <v>129457913</v>
       </c>
       <c r="B90" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9990,29 +9999,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>493637</v>
+        <v>493686</v>
       </c>
       <c r="R90" t="n">
-        <v>6834831</v>
+        <v>6834989</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10068,10 +10068,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129457745</v>
+        <v>129460883</v>
       </c>
       <c r="B91" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10112,13 +10112,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>493678</v>
+        <v>493637</v>
       </c>
       <c r="R91" t="n">
-        <v>6835020</v>
+        <v>6834831</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>129476532</v>
       </c>
       <c r="B92" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>129476583</v>
       </c>
       <c r="B94" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>129476566</v>
       </c>
       <c r="B95" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>129476574</v>
       </c>
       <c r="B96" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>129476571</v>
       </c>
       <c r="B97" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129476560</v>
+        <v>129476544</v>
       </c>
       <c r="B98" t="n">
-        <v>78832</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10777,28 +10777,29 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -10808,10 +10809,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493684</v>
+        <v>493634</v>
       </c>
       <c r="R98" t="n">
-        <v>6834860</v>
+        <v>6834983</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10852,7 +10853,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10871,54 +10871,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129455942</v>
+        <v>129476537</v>
       </c>
       <c r="B99" t="n">
-        <v>98768</v>
+        <v>79666</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493802</v>
+        <v>493659</v>
       </c>
       <c r="R99" t="n">
-        <v>6834925</v>
+        <v>6834945</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10965,57 +10956,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129458908</v>
+        <v>129476569</v>
       </c>
       <c r="B100" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493702</v>
+        <v>493626</v>
       </c>
       <c r="R100" t="n">
-        <v>6834942</v>
+        <v>6834837</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11062,66 +11053,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129458098</v>
+        <v>129476578</v>
       </c>
       <c r="B101" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493682</v>
+        <v>493718</v>
       </c>
       <c r="R101" t="n">
-        <v>6834975</v>
+        <v>6834894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11168,22 +11150,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129476569</v>
+        <v>129455841</v>
       </c>
       <c r="B102" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11211,14 +11193,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493626</v>
+        <v>493803</v>
       </c>
       <c r="R102" t="n">
-        <v>6834837</v>
+        <v>6834901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11265,22 +11247,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129476578</v>
+        <v>129476560</v>
       </c>
       <c r="B103" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11288,34 +11270,41 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493718</v>
+        <v>493684</v>
       </c>
       <c r="R103" t="n">
-        <v>6834894</v>
+        <v>6834860</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11356,6 +11345,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11374,45 +11364,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129455841</v>
+        <v>129455942</v>
       </c>
       <c r="B104" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493803</v>
+        <v>493802</v>
       </c>
       <c r="R104" t="n">
-        <v>6834901</v>
+        <v>6834925</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11471,53 +11470,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129476544</v>
+        <v>129458908</v>
       </c>
       <c r="B105" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493634</v>
+        <v>493702</v>
       </c>
       <c r="R105" t="n">
-        <v>6834983</v>
+        <v>6834942</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11564,57 +11555,66 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129476537</v>
+        <v>129458098</v>
       </c>
       <c r="B106" t="n">
-        <v>79665</v>
+        <v>98769</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493659</v>
+        <v>493682</v>
       </c>
       <c r="R106" t="n">
-        <v>6834945</v>
+        <v>6834975</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11661,66 +11661,57 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129456312</v>
+        <v>129458915</v>
       </c>
       <c r="B107" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493787</v>
+        <v>493698</v>
       </c>
       <c r="R107" t="n">
-        <v>6834957</v>
+        <v>6834942</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11779,10 +11770,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129458915</v>
+        <v>129476577</v>
       </c>
       <c r="B108" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11810,14 +11801,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>493698</v>
+        <v>493707</v>
       </c>
       <c r="R108" t="n">
-        <v>6834942</v>
+        <v>6834895</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11864,57 +11855,66 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129476577</v>
+        <v>129456312</v>
       </c>
       <c r="B109" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>493707</v>
+        <v>493787</v>
       </c>
       <c r="R109" t="n">
-        <v>6834895</v>
+        <v>6834957</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11961,66 +11961,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129456198</v>
+        <v>129476568</v>
       </c>
       <c r="B110" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>493810</v>
+        <v>493619</v>
       </c>
       <c r="R110" t="n">
-        <v>6834955</v>
+        <v>6834841</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12067,44 +12058,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129458436</v>
+        <v>129461581</v>
       </c>
       <c r="B111" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12114,10 +12105,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>493653</v>
+        <v>493634</v>
       </c>
       <c r="R111" t="n">
-        <v>6835020</v>
+        <v>6834920</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12179,7 +12170,7 @@
         <v>129476538</v>
       </c>
       <c r="B112" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12273,45 +12264,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129476568</v>
+        <v>129456198</v>
       </c>
       <c r="B113" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>493619</v>
+        <v>493810</v>
       </c>
       <c r="R113" t="n">
-        <v>6834841</v>
+        <v>6834955</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12358,44 +12358,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129461581</v>
+        <v>129458436</v>
       </c>
       <c r="B114" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12405,10 +12405,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>493634</v>
+        <v>493653</v>
       </c>
       <c r="R114" t="n">
-        <v>6834920</v>
+        <v>6835020</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12467,10 +12467,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129460271</v>
+        <v>129476558</v>
       </c>
       <c r="B115" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12478,34 +12478,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>493731</v>
+        <v>493629</v>
       </c>
       <c r="R115" t="n">
-        <v>6834853</v>
+        <v>6834823</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12552,22 +12552,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129476584</v>
+        <v>129460271</v>
       </c>
       <c r="B116" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12595,14 +12595,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>493670</v>
+        <v>493731</v>
       </c>
       <c r="R116" t="n">
-        <v>6834995</v>
+        <v>6834853</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12649,22 +12649,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129476558</v>
+        <v>129476584</v>
       </c>
       <c r="B117" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12672,21 +12672,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12696,10 +12696,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>493629</v>
+        <v>493670</v>
       </c>
       <c r="R117" t="n">
-        <v>6834823</v>
+        <v>6834995</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12761,7 +12761,7 @@
         <v>129459508</v>
       </c>
       <c r="B118" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>129459731</v>
       </c>
       <c r="B119" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>129459774</v>
       </c>
       <c r="B120" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13067,32 +13067,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129476541</v>
+        <v>129476590</v>
       </c>
       <c r="B121" t="n">
-        <v>91587</v>
+        <v>92870</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>493780</v>
+        <v>493628</v>
       </c>
       <c r="R121" t="n">
-        <v>6834984</v>
+        <v>6834891</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13164,45 +13164,52 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129476590</v>
+        <v>129476559</v>
       </c>
       <c r="B122" t="n">
-        <v>92869</v>
+        <v>78833</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>493628</v>
+        <v>493626</v>
       </c>
       <c r="R122" t="n">
-        <v>6834891</v>
+        <v>6834843</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13243,6 +13250,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13261,52 +13269,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129476559</v>
+        <v>129461070</v>
       </c>
       <c r="B123" t="n">
-        <v>78832</v>
+        <v>98769</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>493626</v>
+        <v>493629</v>
       </c>
       <c r="R123" t="n">
-        <v>6834843</v>
+        <v>6834827</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13347,29 +13348,28 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129461070</v>
+        <v>129457707</v>
       </c>
       <c r="B124" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13401,10 +13401,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>493629</v>
+        <v>493815</v>
       </c>
       <c r="R124" t="n">
-        <v>6834827</v>
+        <v>6834917</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13463,10 +13463,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129457707</v>
+        <v>129456013</v>
       </c>
       <c r="B125" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13491,17 +13491,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>493815</v>
+        <v>493806</v>
       </c>
       <c r="R125" t="n">
-        <v>6834917</v>
+        <v>6834935</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13560,10 +13569,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129456013</v>
+        <v>129456404</v>
       </c>
       <c r="B126" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13590,7 +13599,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13604,10 +13613,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493806</v>
+        <v>493780</v>
       </c>
       <c r="R126" t="n">
-        <v>6834935</v>
+        <v>6834929</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13666,10 +13675,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129456404</v>
+        <v>129456103</v>
       </c>
       <c r="B127" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13696,7 +13705,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13710,10 +13719,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493780</v>
+        <v>493817</v>
       </c>
       <c r="R127" t="n">
-        <v>6834929</v>
+        <v>6834939</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13772,54 +13781,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129456103</v>
+        <v>129476541</v>
       </c>
       <c r="B128" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>493817</v>
+        <v>493780</v>
       </c>
       <c r="R128" t="n">
-        <v>6834939</v>
+        <v>6834984</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13866,22 +13866,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129476550</v>
+        <v>129476530</v>
       </c>
       <c r="B129" t="n">
-        <v>78833</v>
+        <v>79108</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13889,21 +13889,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>493625</v>
+        <v>493705</v>
       </c>
       <c r="R129" t="n">
-        <v>6834820</v>
+        <v>6834890</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13975,10 +13975,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129476530</v>
+        <v>129458645</v>
       </c>
       <c r="B130" t="n">
-        <v>79107</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13986,34 +13986,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>493705</v>
+        <v>493662</v>
       </c>
       <c r="R130" t="n">
-        <v>6834890</v>
+        <v>6834952</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14060,22 +14060,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129458645</v>
+        <v>129455888</v>
       </c>
       <c r="B131" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14107,10 +14107,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>493662</v>
+        <v>493811</v>
       </c>
       <c r="R131" t="n">
-        <v>6834952</v>
+        <v>6834925</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14169,10 +14169,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129455888</v>
+        <v>129476550</v>
       </c>
       <c r="B132" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14180,34 +14180,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>493811</v>
+        <v>493625</v>
       </c>
       <c r="R132" t="n">
-        <v>6834925</v>
+        <v>6834820</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14254,12 +14254,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="